--- a/Part2_analyses/All_stats_clean.xlsx
+++ b/Part2_analyses/All_stats_clean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\EHI_laterality\Part2_analyses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232898B4-404D-42AF-91AE-692EE252C7B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCC5936-6915-4CE1-8502-09427CA3AF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7155" yWindow="-13980" windowWidth="19425" windowHeight="10305" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="807" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="486">
   <si>
     <t>Regarding age</t>
   </si>
@@ -1484,6 +1484,9 @@
   </si>
   <si>
     <t>Repeat discarding people with no age or no sex</t>
+  </si>
+  <si>
+    <t>Controls NRH</t>
   </si>
 </sst>
 </file>
@@ -1741,7 +1744,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1863,6 +1866,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2384,18 +2390,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="14.26953125" customWidth="1"/>
+    <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:19" ht="18.5" x14ac:dyDescent="0.45">
       <c r="A1" s="40" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A3" s="1"/>
       <c r="B3" s="22" t="s">
         <v>110</v>
@@ -2403,24 +2410,27 @@
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
       <c r="E3" s="22"/>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="22"/>
+      <c r="G3" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-      <c r="J3" s="11" t="s">
+      <c r="J3" s="3"/>
+      <c r="K3" s="3"/>
+      <c r="L3" s="11" t="s">
         <v>106</v>
       </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="11"/>
       <c r="M3" s="11"/>
-      <c r="N3" s="60" t="s">
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="O3" s="60"/>
-    </row>
-    <row r="4" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+      <c r="R3" s="60"/>
+    </row>
+    <row r="4" spans="1:19" ht="58" x14ac:dyDescent="0.35">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -2434,43 +2444,52 @@
         <v>62</v>
       </c>
       <c r="E4" s="23" t="s">
+        <v>485</v>
+      </c>
+      <c r="F4" s="23" t="s">
         <v>63</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="H4" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="J4" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="K4" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="L4" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="M4" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="L4" s="12" t="s">
+      <c r="N4" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="O4" s="12" t="s">
+        <v>485</v>
+      </c>
+      <c r="P4" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="N4" s="15" t="s">
+      <c r="Q4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="O4" s="15" t="s">
+      <c r="R4" s="15" t="s">
         <v>471</v>
       </c>
-      <c r="P4" s="15" t="s">
+      <c r="S4" s="15" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>0</v>
       </c>
@@ -2483,44 +2502,49 @@
       <c r="D5" s="24" t="s">
         <v>149</v>
       </c>
-      <c r="E5" s="24" t="s">
+      <c r="E5" s="24">
+        <v>119</v>
+      </c>
+      <c r="F5" s="24" t="s">
         <v>150</v>
       </c>
-      <c r="F5" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="G5" s="9" t="s">
+      <c r="H5" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="I5" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="I5" s="9" t="s">
+      <c r="J5" s="9"/>
+      <c r="K5" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="L5" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="M5" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="L5" s="13" t="s">
+      <c r="N5" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="O5" s="13"/>
+      <c r="P5" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="N5" t="s">
-        <v>23</v>
-      </c>
-      <c r="O5" t="s">
-        <v>23</v>
-      </c>
-      <c r="P5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q5" t="s">
+        <v>23</v>
+      </c>
+      <c r="R5" t="s">
+        <v>23</v>
+      </c>
+      <c r="S5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -2533,44 +2557,49 @@
       <c r="D6" s="24" t="s">
         <v>146</v>
       </c>
-      <c r="E6" s="24" t="s">
+      <c r="E6" s="24">
+        <v>137</v>
+      </c>
+      <c r="F6" s="24" t="s">
         <v>147</v>
       </c>
-      <c r="F6" s="9" t="s">
+      <c r="G6" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="H6" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="I6" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="J6" s="9"/>
+      <c r="K6" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="L6" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="K6" s="13" t="s">
+      <c r="M6" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="L6" s="13" t="s">
+      <c r="N6" s="13" t="s">
         <v>92</v>
       </c>
-      <c r="M6" s="13" t="s">
+      <c r="O6" s="13"/>
+      <c r="P6" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="N6" t="s">
-        <v>23</v>
-      </c>
-      <c r="O6" t="s">
-        <v>23</v>
-      </c>
-      <c r="P6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="Q6" t="s">
+        <v>23</v>
+      </c>
+      <c r="R6" t="s">
+        <v>23</v>
+      </c>
+      <c r="S6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>33</v>
       </c>
@@ -2583,44 +2612,49 @@
       <c r="D7" s="24" t="s">
         <v>153</v>
       </c>
-      <c r="E7" s="24" t="s">
+      <c r="E7" s="24">
+        <v>178</v>
+      </c>
+      <c r="F7" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="F7" s="9" t="s">
+      <c r="G7" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="G7" s="9" t="s">
+      <c r="H7" s="9" t="s">
         <v>74</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="I7" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="I7" s="9" t="s">
+      <c r="J7" s="9"/>
+      <c r="K7" s="9" t="s">
         <v>76</v>
       </c>
-      <c r="J7" s="13" t="s">
+      <c r="L7" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="K7" s="13" t="s">
+      <c r="M7" s="13" t="s">
         <v>95</v>
       </c>
-      <c r="L7" s="13" t="s">
+      <c r="N7" s="13" t="s">
         <v>96</v>
       </c>
-      <c r="M7" s="13" t="s">
+      <c r="O7" s="13"/>
+      <c r="P7" s="13" t="s">
         <v>97</v>
       </c>
-      <c r="N7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O7" s="10">
+      <c r="Q7" t="s">
+        <v>23</v>
+      </c>
+      <c r="R7" s="10">
         <v>3.61E-2</v>
       </c>
-      <c r="P7" s="10">
+      <c r="S7" s="10">
         <v>1.627E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>42</v>
       </c>
@@ -2633,44 +2667,49 @@
       <c r="D8" s="24" t="s">
         <v>157</v>
       </c>
-      <c r="E8" s="24" t="s">
+      <c r="E8" s="24">
+        <v>450</v>
+      </c>
+      <c r="F8" s="24" t="s">
         <v>158</v>
       </c>
-      <c r="F8" s="9" t="s">
+      <c r="G8" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="G8" s="9" t="s">
+      <c r="H8" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="I8" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="I8" s="9" t="s">
+      <c r="J8" s="9"/>
+      <c r="K8" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="J8" s="13" t="s">
+      <c r="L8" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="K8" s="13" t="s">
+      <c r="M8" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="L8" s="13" t="s">
+      <c r="N8" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="M8" s="13" t="s">
+      <c r="O8" s="13"/>
+      <c r="P8" s="13" t="s">
         <v>101</v>
       </c>
-      <c r="N8" t="s">
-        <v>23</v>
-      </c>
-      <c r="O8" s="10">
+      <c r="Q8" t="s">
+        <v>23</v>
+      </c>
+      <c r="R8" s="10">
         <v>3.97E-4</v>
       </c>
-      <c r="P8" s="16">
+      <c r="S8" s="16">
         <v>8.5870000000000003E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>51</v>
       </c>
@@ -2683,52 +2722,57 @@
       <c r="D9" s="24" t="s">
         <v>161</v>
       </c>
-      <c r="E9" s="24" t="s">
+      <c r="E9" s="24">
+        <v>788</v>
+      </c>
+      <c r="F9" s="24" t="s">
         <v>162</v>
       </c>
-      <c r="F9" s="9" t="s">
+      <c r="G9" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="G9" s="9" t="s">
+      <c r="H9" s="9" t="s">
         <v>82</v>
       </c>
-      <c r="H9" s="9" t="s">
+      <c r="I9" s="9" t="s">
         <v>83</v>
       </c>
-      <c r="I9" s="9" t="s">
+      <c r="J9" s="9"/>
+      <c r="K9" s="9" t="s">
         <v>84</v>
       </c>
-      <c r="J9" s="13" t="s">
+      <c r="L9" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="M9" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="L9" s="13" t="s">
+      <c r="N9" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="M9" s="13" t="s">
+      <c r="O9" s="13"/>
+      <c r="P9" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="N9" t="s">
-        <v>23</v>
-      </c>
-      <c r="O9" s="10">
+      <c r="Q9" t="s">
+        <v>23</v>
+      </c>
+      <c r="R9" s="10">
         <v>6.7000000000000002E-4</v>
       </c>
-      <c r="P9" s="16">
+      <c r="S9" s="16">
         <v>3.8999999999999999E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
-      <c r="O10" s="10"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="R10" s="10"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>1</v>
@@ -2736,18 +2780,20 @@
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="2"/>
+      <c r="G13" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="G13" s="3"/>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="59" t="s">
+      <c r="J13" s="3"/>
+      <c r="K13" s="3"/>
+      <c r="L13" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="K13" s="59"/>
-    </row>
-    <row r="14" spans="1:16" ht="58" x14ac:dyDescent="0.35">
+      <c r="M13" s="59"/>
+    </row>
+    <row r="14" spans="1:19" ht="58" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
@@ -2760,32 +2806,35 @@
       <c r="D14" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="E14" s="5"/>
+      <c r="F14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="6" t="s">
+      <c r="G14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="H14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="I14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="J14" s="6"/>
+      <c r="K14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="L14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="K14" s="7" t="s">
+      <c r="M14" s="7" t="s">
         <v>471</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="N14" s="7" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="O14" s="68"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A15" s="1">
         <v>0</v>
       </c>
@@ -2798,32 +2847,34 @@
       <c r="D15" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E15" s="8" t="s">
+      <c r="E15" s="8"/>
+      <c r="F15" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="9" t="s">
+      <c r="G15" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="H15" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="I15" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="I15" s="9" t="s">
+      <c r="J15" s="9"/>
+      <c r="K15" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="J15" t="s">
-        <v>23</v>
-      </c>
-      <c r="K15" t="s">
-        <v>23</v>
-      </c>
       <c r="L15" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="M15" t="s">
+        <v>23</v>
+      </c>
+      <c r="N15" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
@@ -2836,32 +2887,34 @@
       <c r="D16" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="E16" s="8"/>
+      <c r="F16" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="F16" s="9" t="s">
+      <c r="G16" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="H16" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="I16" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="I16" s="9" t="s">
+      <c r="J16" s="9"/>
+      <c r="K16" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="J16" t="s">
-        <v>23</v>
-      </c>
-      <c r="K16" t="s">
-        <v>23</v>
-      </c>
       <c r="L16" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M16" t="s">
+        <v>23</v>
+      </c>
+      <c r="N16" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -2874,32 +2927,34 @@
       <c r="D17" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="E17" s="8" t="s">
+      <c r="E17" s="8"/>
+      <c r="F17" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="F17" s="9" t="s">
+      <c r="G17" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="H17" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="I17" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="I17" s="9" t="s">
+      <c r="J17" s="9"/>
+      <c r="K17" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="J17" t="s">
-        <v>23</v>
-      </c>
-      <c r="K17" t="s">
-        <v>23</v>
-      </c>
       <c r="L17" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="M17" t="s">
+        <v>23</v>
+      </c>
+      <c r="N17" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>42</v>
       </c>
@@ -2912,32 +2967,35 @@
       <c r="D18" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="E18" s="8" t="s">
+      <c r="E18" s="8"/>
+      <c r="F18" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="F18" s="9" t="s">
+      <c r="G18" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="H18" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="I18" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="J18" s="9"/>
+      <c r="K18" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="J18" t="s">
-        <v>23</v>
-      </c>
-      <c r="K18" s="10">
+      <c r="L18" t="s">
+        <v>23</v>
+      </c>
+      <c r="M18" s="10">
         <v>9.7999999999999997E-3</v>
       </c>
-      <c r="L18" s="10">
+      <c r="N18" s="10">
         <v>1.2710000000000001E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="O18" s="10"/>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -2950,35 +3008,38 @@
       <c r="D19" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="E19" s="8" t="s">
+      <c r="E19" s="8"/>
+      <c r="F19" s="8" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="9" t="s">
+      <c r="G19" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="H19" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="I19" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="J19" s="9"/>
+      <c r="K19" s="9" t="s">
         <v>59</v>
       </c>
-      <c r="J19" t="s">
-        <v>23</v>
-      </c>
-      <c r="K19" s="10">
+      <c r="L19" t="s">
+        <v>23</v>
+      </c>
+      <c r="M19" s="10">
         <v>4.2739999999999998E-8</v>
       </c>
-      <c r="L19" s="10">
+      <c r="N19" s="10">
         <v>1.7499999999999999E-7</v>
       </c>
+      <c r="O19" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="N3:O3"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="Q3:R3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4396,7 +4457,7 @@
       </c>
       <c r="K30" s="65"/>
     </row>
-    <row r="31" spans="1:18" ht="72.5" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:18" ht="58" x14ac:dyDescent="0.35">
       <c r="B31" s="45" t="s">
         <v>482</v>
       </c>

--- a/Part2_analyses/All_stats_clean.xlsx
+++ b/Part2_analyses/All_stats_clean.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Desktop\EHI_laterality\Part2_analyses\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CBM\Desktop\EHI_laterality\Part2_analyses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCC5936-6915-4CE1-8502-09427CA3AF9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="2" r:id="rId1"/>
@@ -29,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="810" uniqueCount="486">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="485">
   <si>
     <t>Regarding age</t>
   </si>
@@ -1481,9 +1480,6 @@
   </si>
   <si>
     <t>P-value of Sex in Lateralized</t>
-  </si>
-  <si>
-    <t>Repeat discarding people with no age or no sex</t>
   </si>
   <si>
     <t>Controls NRH</t>
@@ -1492,7 +1488,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
@@ -1840,6 +1836,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1866,9 +1865,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2156,29 +2152,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26077DA7-2E50-48B6-A1AA-431167BBBB60}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:E16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.81640625" customWidth="1"/>
-    <col min="2" max="4" width="19.1796875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.1796875" customWidth="1"/>
+    <col min="1" max="1" width="21.85546875" customWidth="1"/>
+    <col min="2" max="4" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
         <v>364</v>
       </c>
-      <c r="D1" s="14" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="D1" s="14"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
       <c r="B3" s="1" t="s">
         <v>108</v>
@@ -2193,7 +2187,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>141</v>
       </c>
@@ -2210,7 +2204,7 @@
         <v>0.16300000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>115</v>
       </c>
@@ -2227,7 +2221,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>120</v>
       </c>
@@ -2244,7 +2238,7 @@
         <v>8.2999999999999999E-9</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>142</v>
       </c>
@@ -2261,7 +2255,7 @@
         <v>7.1999999999999996E-13</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>143</v>
       </c>
@@ -2278,12 +2272,12 @@
         <v>5.5000000000000002E-5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="29" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="4" t="s">
         <v>130</v>
@@ -2298,7 +2292,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>133</v>
       </c>
@@ -2315,7 +2309,7 @@
         <v>0.67579999999999996</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>115</v>
       </c>
@@ -2332,7 +2326,7 @@
         <v>2.8678831295294999E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>120</v>
       </c>
@@ -2349,7 +2343,7 @@
         <v>3.2982903137362699E-2</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>142</v>
       </c>
@@ -2366,7 +2360,7 @@
         <v>1.7271311771889999E-4</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>143</v>
       </c>
@@ -2389,20 +2383,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.26953125" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="40" t="s">
         <v>365</v>
       </c>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="22" t="s">
         <v>110</v>
@@ -2425,12 +2419,12 @@
       <c r="N3" s="11"/>
       <c r="O3" s="11"/>
       <c r="P3" s="11"/>
-      <c r="Q3" s="60" t="s">
+      <c r="Q3" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="R3" s="60"/>
-    </row>
-    <row r="4" spans="1:19" ht="58" x14ac:dyDescent="0.35">
+      <c r="R3" s="61"/>
+    </row>
+    <row r="4" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
@@ -2444,7 +2438,7 @@
         <v>62</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>63</v>
@@ -2459,7 +2453,7 @@
         <v>62</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>63</v>
@@ -2474,7 +2468,7 @@
         <v>62</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="P4" s="12" t="s">
         <v>63</v>
@@ -2489,7 +2483,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>0</v>
       </c>
@@ -2544,7 +2538,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>24</v>
       </c>
@@ -2599,7 +2593,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>33</v>
       </c>
@@ -2654,7 +2648,7 @@
         <v>1.627E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>42</v>
       </c>
@@ -2709,7 +2703,7 @@
         <v>8.5870000000000003E-5</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>51</v>
       </c>
@@ -2764,15 +2758,15 @@
         <v>3.8999999999999999E-4</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="R10" s="10"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
         <v>1</v>
@@ -2788,12 +2782,12 @@
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="59" t="s">
+      <c r="L13" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="M13" s="59"/>
-    </row>
-    <row r="14" spans="1:19" ht="58" x14ac:dyDescent="0.35">
+      <c r="M13" s="60"/>
+    </row>
+    <row r="14" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
         <v>4</v>
       </c>
@@ -2832,9 +2826,9 @@
       <c r="N14" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="O14" s="68"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="O14" s="59"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>0</v>
       </c>
@@ -2874,7 +2868,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
@@ -2914,7 +2908,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>33</v>
       </c>
@@ -2954,7 +2948,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>42</v>
       </c>
@@ -2995,7 +2989,7 @@
       </c>
       <c r="O18" s="10"/>
     </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>51</v>
       </c>
@@ -3046,27 +3040,27 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6709A9E-694F-4F60-A025-0A348026BB4C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:S10"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="17" max="17" width="15.90625" customWidth="1"/>
+    <col min="17" max="17" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
         <v>366</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="39"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="46" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:19" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="25" t="s">
         <v>165</v>
@@ -3086,17 +3080,17 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
-      <c r="N4" s="61" t="s">
+      <c r="N4" s="62" t="s">
         <v>475</v>
       </c>
-      <c r="O4" s="62"/>
-      <c r="P4" s="62"/>
-      <c r="Q4" s="63" t="s">
+      <c r="O4" s="63"/>
+      <c r="P4" s="63"/>
+      <c r="Q4" s="64" t="s">
         <v>472</v>
       </c>
-      <c r="R4" s="63"/>
-    </row>
-    <row r="5" spans="1:19" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="R4" s="64"/>
+    </row>
+    <row r="5" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>167</v>
       </c>
@@ -3153,7 +3147,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>0</v>
       </c>
@@ -3210,7 +3204,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -3267,7 +3261,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>33</v>
       </c>
@@ -3324,7 +3318,7 @@
         <v>2.2700000000000001E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>42</v>
       </c>
@@ -3381,7 +3375,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>51</v>
       </c>
@@ -3448,21 +3442,21 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD91A86E-0EDA-4BE8-8B00-F593F17065C6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:R36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:18" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
         <v>367</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>236</v>
       </c>
     </row>
-    <row r="4" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="28" t="s">
         <v>237</v>
@@ -3482,17 +3476,17 @@
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
-      <c r="N4" s="60" t="s">
+      <c r="N4" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="O4" s="60"/>
-      <c r="P4" s="60"/>
-      <c r="Q4" s="63" t="s">
+      <c r="O4" s="61"/>
+      <c r="P4" s="61"/>
+      <c r="Q4" s="64" t="s">
         <v>476</v>
       </c>
-      <c r="R4" s="63"/>
-    </row>
-    <row r="5" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+      <c r="R4" s="64"/>
+    </row>
+    <row r="5" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>167</v>
       </c>
@@ -3548,7 +3542,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>0</v>
       </c>
@@ -3604,7 +3598,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>24</v>
       </c>
@@ -3660,7 +3654,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>33</v>
       </c>
@@ -3716,7 +3710,7 @@
         <v>5.79E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>42</v>
       </c>
@@ -3772,7 +3766,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>51</v>
       </c>
@@ -3828,12 +3822,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="36" t="s">
         <v>303</v>
@@ -3853,17 +3847,17 @@
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
       <c r="M14" s="11"/>
-      <c r="N14" s="60" t="s">
+      <c r="N14" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="O14" s="60"/>
-      <c r="P14" s="60"/>
-      <c r="Q14" s="63" t="s">
+      <c r="O14" s="61"/>
+      <c r="P14" s="61"/>
+      <c r="Q14" s="64" t="s">
         <v>476</v>
       </c>
-      <c r="R14" s="63"/>
-    </row>
-    <row r="15" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+      <c r="R14" s="64"/>
+    </row>
+    <row r="15" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
         <v>167</v>
       </c>
@@ -3919,7 +3913,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>0</v>
       </c>
@@ -3975,7 +3969,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>24</v>
       </c>
@@ -4031,7 +4025,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>33</v>
       </c>
@@ -4087,7 +4081,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>42</v>
       </c>
@@ -4143,7 +4137,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>51</v>
       </c>
@@ -4199,32 +4193,32 @@
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="N21" s="14"/>
       <c r="O21" s="14"/>
       <c r="P21" s="14"/>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="B22" s="66" t="s">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="B22" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="C22" s="67"/>
-      <c r="D22" s="67"/>
-      <c r="F22" s="66" t="s">
+      <c r="C22" s="68"/>
+      <c r="D22" s="68"/>
+      <c r="F22" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="G22" s="67"/>
-      <c r="H22" s="67"/>
-      <c r="J22" s="66" t="s">
+      <c r="G22" s="68"/>
+      <c r="H22" s="68"/>
+      <c r="J22" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="K22" s="67"/>
-      <c r="L22" s="67"/>
+      <c r="K22" s="68"/>
+      <c r="L22" s="68"/>
       <c r="N22" s="14"/>
       <c r="O22" s="14"/>
       <c r="P22" s="14"/>
     </row>
-    <row r="23" spans="1:18" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:18" ht="45" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>13</v>
       </c>
@@ -4253,7 +4247,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>0</v>
       </c>
@@ -4291,7 +4285,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>24</v>
       </c>
@@ -4329,7 +4323,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>33</v>
       </c>
@@ -4367,7 +4361,7 @@
         <v>5.5E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>42</v>
       </c>
@@ -4405,7 +4399,7 @@
         <v>1.596E-3</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>51</v>
       </c>
@@ -4443,21 +4437,21 @@
         <v>2.1000000000000001E-2</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B30" s="64" t="s">
+    <row r="30" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="65" t="s">
         <v>481</v>
       </c>
-      <c r="C30" s="65"/>
-      <c r="F30" s="64" t="s">
+      <c r="C30" s="66"/>
+      <c r="F30" s="65" t="s">
         <v>478</v>
       </c>
-      <c r="G30" s="65"/>
-      <c r="J30" s="64" t="s">
+      <c r="G30" s="66"/>
+      <c r="J30" s="65" t="s">
         <v>478</v>
       </c>
-      <c r="K30" s="65"/>
-    </row>
-    <row r="31" spans="1:18" ht="58" x14ac:dyDescent="0.35">
+      <c r="K30" s="66"/>
+    </row>
+    <row r="31" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="B31" s="45" t="s">
         <v>482</v>
       </c>
@@ -4477,7 +4471,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>0</v>
       </c>
@@ -4506,7 +4500,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>24</v>
       </c>
@@ -4535,7 +4529,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>33</v>
       </c>
@@ -4564,7 +4558,7 @@
         <v>6.2399999999999997E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>42</v>
       </c>
@@ -4593,7 +4587,7 @@
         <v>2.1299999999999999E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>51</v>
       </c>
@@ -4640,29 +4634,29 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF33DC08-0ADF-4DCE-AE54-63FEA87CD800}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H29"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="21.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.54296875" customWidth="1"/>
-    <col min="7" max="7" width="24.08984375" customWidth="1"/>
-    <col min="8" max="8" width="23.7265625" customWidth="1"/>
+    <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" customWidth="1"/>
+    <col min="7" max="7" width="24.140625" customWidth="1"/>
+    <col min="8" max="8" width="23.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.5" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="G2" s="14"/>
       <c r="H2" s="14"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>368</v>
       </c>
@@ -4688,7 +4682,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="41">
         <v>0</v>
       </c>
@@ -4714,7 +4708,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="41" t="s">
         <v>24</v>
       </c>
@@ -4740,7 +4734,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
         <v>33</v>
       </c>
@@ -4766,7 +4760,7 @@
         <v>1.7299999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
         <v>42</v>
       </c>
@@ -4792,7 +4786,7 @@
         <v>6.5399999999999998E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
         <v>51</v>
       </c>
@@ -4818,7 +4812,7 @@
         <v>1.01E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>398</v>
       </c>
@@ -4844,7 +4838,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="41">
         <v>0</v>
       </c>
@@ -4870,7 +4864,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="41" t="s">
         <v>24</v>
       </c>
@@ -4896,7 +4890,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="41" t="s">
         <v>33</v>
       </c>
@@ -4922,7 +4916,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
         <v>42</v>
       </c>
@@ -4948,7 +4942,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
         <v>51</v>
       </c>
@@ -4974,7 +4968,7 @@
         <v>3.7600000000000001E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>424</v>
       </c>
@@ -5000,7 +4994,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="41">
         <v>0</v>
       </c>
@@ -5026,7 +5020,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="s">
         <v>24</v>
       </c>
@@ -5052,7 +5046,7 @@
         <v>3.1199999999999999E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
         <v>33</v>
       </c>
@@ -5078,7 +5072,7 @@
         <v>6.5399999999999998E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
         <v>42</v>
       </c>
@@ -5104,7 +5098,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
         <v>51</v>
       </c>
@@ -5130,7 +5124,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>444</v>
       </c>
@@ -5156,7 +5150,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" s="41">
         <v>0</v>
       </c>
@@ -5182,7 +5176,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
         <v>24</v>
       </c>
@@ -5208,7 +5202,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="41" t="s">
         <v>33</v>
       </c>
@@ -5234,7 +5228,7 @@
         <v>1.4200000000000001E-2</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="41" t="s">
         <v>42</v>
       </c>
@@ -5260,7 +5254,7 @@
         <v>1.0699999999999999E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="41" t="s">
         <v>51</v>
       </c>

--- a/Part2_analyses/All_stats_clean.xlsx
+++ b/Part2_analyses/All_stats_clean.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="2" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="485">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="483">
   <si>
     <t>Regarding age</t>
   </si>
@@ -285,9 +285,6 @@
     <t>458 (53.19%)</t>
   </si>
   <si>
-    <t>Females = 861</t>
-  </si>
-  <si>
     <t>54 (8.71%)</t>
   </si>
   <si>
@@ -348,33 +345,15 @@
     <t>272 (43.87%)</t>
   </si>
   <si>
-    <t>Males = 620</t>
-  </si>
-  <si>
     <t>With all data</t>
   </si>
   <si>
-    <t>Total dataset = 1,923</t>
-  </si>
-  <si>
     <t>BD patients = 436</t>
   </si>
   <si>
-    <t>Controls = 1,487</t>
-  </si>
-  <si>
     <t>P-value (Chi-squared / Wilcox)</t>
   </si>
   <si>
-    <t>1133 (58.9)</t>
-  </si>
-  <si>
-    <t>270 (61.9)</t>
-  </si>
-  <si>
-    <t>863 (58.0)</t>
-  </si>
-  <si>
     <t>Age (median [IQR])</t>
   </si>
   <si>
@@ -384,9 +363,6 @@
     <t>28.00 [23.00, 46.00]</t>
   </si>
   <si>
-    <t xml:space="preserve"> 55.00 [45.00, 64.00]</t>
-  </si>
-  <si>
     <t>&lt;1E-16</t>
   </si>
   <si>
@@ -432,27 +408,9 @@
     <t>Sex = Female(%)</t>
   </si>
   <si>
-    <t xml:space="preserve">   529 (61.1%) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   268 (61.9%) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">   261 (60.3%) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 54.00 [45.00, 61.00]</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 53.00 [45.00, 59.00]</t>
-  </si>
-  <si>
     <t>100.00 [82.00, 100.00]</t>
   </si>
   <si>
-    <t>100.00 [88.00, 100.00]</t>
-  </si>
-  <si>
     <t>Sex = Female (%)</t>
   </si>
   <si>
@@ -468,57 +426,12 @@
     <t>42 (2.82%)</t>
   </si>
   <si>
-    <t>1350 (90.79%)</t>
-  </si>
-  <si>
-    <t>1445 (97.18%)</t>
-  </si>
-  <si>
-    <t>112 (7.53%)</t>
-  </si>
-  <si>
-    <t>1368 (92.00%)</t>
-  </si>
-  <si>
-    <t>1480 (99.53%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">84 (5.65%) </t>
   </si>
   <si>
-    <t xml:space="preserve">94 (6.32%) </t>
-  </si>
-  <si>
-    <t>1309 (88.03%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 1393 (93.68%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">55 (3.70%) </t>
-  </si>
-  <si>
-    <t>395 (26.56%)</t>
-  </si>
-  <si>
-    <t>1037 (69.74%)</t>
-  </si>
-  <si>
-    <t>1092 (73.44%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">32 (2.15%)  </t>
   </si>
   <si>
-    <t>756 (50.84%)</t>
-  </si>
-  <si>
-    <t>699 (47.01%)</t>
-  </si>
-  <si>
-    <t>731 (49.16%)</t>
-  </si>
-  <si>
     <t>Controls age-matched = 433</t>
   </si>
   <si>
@@ -1483,6 +1396,87 @@
   </si>
   <si>
     <t>Controls NRH</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  1127 (58.8) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   270 (61.9) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">  857 (57.9) </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 55.00 [44.00, 64.00]</t>
+  </si>
+  <si>
+    <t>Controls = 1,480</t>
+  </si>
+  <si>
+    <t>Total dataset = 1,916</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 53.00 [44.00, 59.00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 54.00 [44.00, 61.00]</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   262 (60.1) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">   532 (61.0) </t>
+  </si>
+  <si>
+    <t>752 (50.84%)</t>
+  </si>
+  <si>
+    <t>Males = 623</t>
+  </si>
+  <si>
+    <t>Females = 857</t>
+  </si>
+  <si>
+    <t>696 (47.03%)</t>
+  </si>
+  <si>
+    <t>728 (49.19%)</t>
+  </si>
+  <si>
+    <t>1089 (73.58%)</t>
+  </si>
+  <si>
+    <t>1034 (69.86%)</t>
+  </si>
+  <si>
+    <t>391 (26.42%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">55 (3.72%)  </t>
+  </si>
+  <si>
+    <t>1386 (93.65%)</t>
+  </si>
+  <si>
+    <t>1302 (87.97%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">94 (6.35%)   </t>
+  </si>
+  <si>
+    <t>1343 (90.74%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1438 (97.16%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 112 (7.57%)  </t>
+  </si>
+  <si>
+    <t>1361 (91.96%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1473 (99.53%)</t>
   </si>
 </sst>
 </file>
@@ -1740,7 +1734,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1865,6 +1859,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2163,42 +2160,42 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
-        <v>364</v>
+        <v>335</v>
       </c>
       <c r="D1" s="14"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
       <c r="B3" s="1" t="s">
-        <v>108</v>
+        <v>461</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>110</v>
+        <v>460</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>112</v>
+        <v>456</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>113</v>
+        <v>457</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>114</v>
+        <v>458</v>
       </c>
       <c r="E4" s="17">
         <v>0.16300000000000001</v>
@@ -2206,33 +2203,33 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>116</v>
+        <v>109</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>117</v>
+        <v>459</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="E6" s="1">
         <v>8.2999999999999999E-9</v>
@@ -2240,16 +2237,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>125</v>
+        <v>116</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>124</v>
+        <v>117</v>
       </c>
       <c r="E7" s="1">
         <v>7.1999999999999996E-13</v>
@@ -2257,16 +2254,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>127</v>
+        <v>120</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>128</v>
+        <v>119</v>
       </c>
       <c r="E8" s="19">
         <v>5.5000000000000002E-5</v>
@@ -2274,36 +2271,36 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="4" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>131</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>163</v>
+        <v>123</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>134</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="B12" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>136</v>
+        <v>125</v>
+      </c>
+      <c r="B12" t="s">
+        <v>465</v>
+      </c>
+      <c r="C12" t="s">
+        <v>464</v>
+      </c>
+      <c r="D12" t="s">
+        <v>457</v>
       </c>
       <c r="E12" s="20">
         <v>0.67579999999999996</v>
@@ -2311,16 +2308,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" s="17" t="s">
-        <v>137</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>138</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>118</v>
+        <v>108</v>
+      </c>
+      <c r="B13" t="s">
+        <v>463</v>
+      </c>
+      <c r="C13" t="s">
+        <v>462</v>
+      </c>
+      <c r="D13" t="s">
+        <v>459</v>
       </c>
       <c r="E13" s="21">
         <v>2.8678831295294999E-3</v>
@@ -2328,33 +2325,33 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B14" s="17" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>121</v>
-      </c>
-      <c r="D14" s="17" t="s">
-        <v>140</v>
+        <v>112</v>
+      </c>
+      <c r="B14" t="s">
+        <v>126</v>
+      </c>
+      <c r="C14" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" t="s">
+        <v>115</v>
       </c>
       <c r="E14" s="21">
-        <v>3.2982903137362699E-2</v>
+        <v>2.3E-2</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>142</v>
-      </c>
-      <c r="B15" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>124</v>
-      </c>
-      <c r="D15" s="17" t="s">
-        <v>124</v>
+        <v>128</v>
+      </c>
+      <c r="B15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" t="s">
+        <v>116</v>
+      </c>
+      <c r="D15" t="s">
+        <v>116</v>
       </c>
       <c r="E15" s="19">
         <v>1.7271311771889999E-4</v>
@@ -2362,19 +2359,19 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="B16" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="C16" s="17" t="s">
-        <v>126</v>
-      </c>
-      <c r="D16" s="17" t="s">
-        <v>128</v>
+        <v>129</v>
+      </c>
+      <c r="B16" t="s">
+        <v>118</v>
+      </c>
+      <c r="C16" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" t="s">
+        <v>120</v>
       </c>
       <c r="E16" s="21">
-        <v>2.3891492307289899E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
     </row>
   </sheetData>
@@ -2384,36 +2381,39 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S19"/>
+  <dimension ref="A1:S22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
+    <col min="2" max="2" width="10.85546875" customWidth="1"/>
+    <col min="3" max="3" width="11.85546875" customWidth="1"/>
+    <col min="4" max="4" width="13.42578125" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="40" t="s">
-        <v>365</v>
+        <v>336</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="22" t="s">
-        <v>110</v>
+        <v>460</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
       <c r="G3" s="3" t="s">
-        <v>85</v>
+        <v>468</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="11" t="s">
-        <v>106</v>
+        <v>467</v>
       </c>
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
@@ -2438,7 +2438,7 @@
         <v>62</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>484</v>
+        <v>455</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>63</v>
@@ -2453,7 +2453,7 @@
         <v>62</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>484</v>
+        <v>455</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>63</v>
@@ -2468,7 +2468,7 @@
         <v>62</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>484</v>
+        <v>455</v>
       </c>
       <c r="P4" s="12" t="s">
         <v>63</v>
@@ -2477,7 +2477,7 @@
         <v>13</v>
       </c>
       <c r="R4" s="15" t="s">
-        <v>471</v>
+        <v>442</v>
       </c>
       <c r="S4" s="15" t="s">
         <v>14</v>
@@ -2488,19 +2488,19 @@
         <v>0</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>148</v>
+        <v>480</v>
       </c>
       <c r="C5" s="24" t="s">
         <v>64</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>149</v>
+        <v>481</v>
       </c>
       <c r="E5" s="24">
         <v>119</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>150</v>
+        <v>482</v>
       </c>
       <c r="G5" s="9" t="s">
         <v>65</v>
@@ -2516,17 +2516,17 @@
         <v>68</v>
       </c>
       <c r="L5" s="13" t="s">
+        <v>85</v>
+      </c>
+      <c r="M5" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="M5" s="13" t="s">
+      <c r="N5" s="13" t="s">
         <v>87</v>
-      </c>
-      <c r="N5" s="13" t="s">
-        <v>88</v>
       </c>
       <c r="O5" s="13"/>
       <c r="P5" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="Q5" t="s">
         <v>23</v>
@@ -2543,19 +2543,19 @@
         <v>24</v>
       </c>
       <c r="B6" s="24" t="s">
-        <v>144</v>
+        <v>130</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>146</v>
+        <v>478</v>
       </c>
       <c r="E6" s="24">
         <v>137</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>147</v>
+        <v>479</v>
       </c>
       <c r="G6" s="9" t="s">
         <v>69</v>
@@ -2571,17 +2571,17 @@
         <v>72</v>
       </c>
       <c r="L6" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="M6" s="13" t="s">
         <v>90</v>
       </c>
-      <c r="M6" s="13" t="s">
+      <c r="N6" s="13" t="s">
         <v>91</v>
-      </c>
-      <c r="N6" s="13" t="s">
-        <v>92</v>
       </c>
       <c r="O6" s="13"/>
       <c r="P6" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="Q6" t="s">
         <v>23</v>
@@ -2598,19 +2598,19 @@
         <v>33</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>151</v>
+        <v>132</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>152</v>
+        <v>477</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>153</v>
+        <v>476</v>
       </c>
       <c r="E7" s="24">
         <v>178</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>154</v>
+        <v>475</v>
       </c>
       <c r="G7" s="9" t="s">
         <v>73</v>
@@ -2626,17 +2626,17 @@
         <v>76</v>
       </c>
       <c r="L7" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="M7" s="13" t="s">
         <v>94</v>
       </c>
-      <c r="M7" s="13" t="s">
+      <c r="N7" s="13" t="s">
         <v>95</v>
-      </c>
-      <c r="N7" s="13" t="s">
-        <v>96</v>
       </c>
       <c r="O7" s="13"/>
       <c r="P7" s="13" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q7" t="s">
         <v>23</v>
@@ -2653,19 +2653,19 @@
         <v>42</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>155</v>
+        <v>474</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>156</v>
+        <v>473</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>157</v>
+        <v>472</v>
       </c>
       <c r="E8" s="24">
         <v>450</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>158</v>
+        <v>471</v>
       </c>
       <c r="G8" s="9" t="s">
         <v>77</v>
@@ -2681,17 +2681,17 @@
         <v>80</v>
       </c>
       <c r="L8" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="M8" s="13" t="s">
         <v>98</v>
       </c>
-      <c r="M8" s="13" t="s">
+      <c r="N8" s="13" t="s">
         <v>99</v>
-      </c>
-      <c r="N8" s="13" t="s">
-        <v>100</v>
       </c>
       <c r="O8" s="13"/>
       <c r="P8" s="13" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q8" t="s">
         <v>23</v>
@@ -2708,19 +2708,19 @@
         <v>51</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>159</v>
+        <v>133</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>160</v>
+        <v>466</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>161</v>
+        <v>469</v>
       </c>
       <c r="E9" s="24">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>162</v>
+        <v>470</v>
       </c>
       <c r="G9" s="9" t="s">
         <v>81</v>
@@ -2736,17 +2736,17 @@
         <v>84</v>
       </c>
       <c r="L9" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="M9" s="13" t="s">
         <v>102</v>
       </c>
-      <c r="M9" s="13" t="s">
+      <c r="N9" s="13" t="s">
         <v>103</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>104</v>
       </c>
       <c r="O9" s="13"/>
       <c r="P9" s="13" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="Q9" t="s">
         <v>23</v>
@@ -2800,7 +2800,9 @@
       <c r="D14" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="5"/>
+      <c r="E14" s="5" t="s">
+        <v>455</v>
+      </c>
       <c r="F14" s="5" t="s">
         <v>8</v>
       </c>
@@ -2813,7 +2815,9 @@
       <c r="I14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="6"/>
+      <c r="J14" s="6" t="s">
+        <v>455</v>
+      </c>
       <c r="K14" s="6" t="s">
         <v>12</v>
       </c>
@@ -2821,7 +2825,7 @@
         <v>13</v>
       </c>
       <c r="M14" s="7" t="s">
-        <v>471</v>
+        <v>442</v>
       </c>
       <c r="N14" s="7" t="s">
         <v>14</v>
@@ -3029,6 +3033,11 @@
         <v>1.7499999999999999E-7</v>
       </c>
       <c r="O19" s="10"/>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A22" s="69"/>
+      <c r="B22" s="69"/>
+      <c r="C22" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3036,6 +3045,7 @@
     <mergeCell ref="Q3:R3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3049,7 +3059,7 @@
   <sheetData>
     <row r="1" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
-        <v>366</v>
+        <v>337</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
@@ -3057,66 +3067,66 @@
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>164</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:19" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="25" t="s">
-        <v>165</v>
+        <v>136</v>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
       <c r="E4" s="25"/>
       <c r="F4" s="2" t="s">
-        <v>166</v>
+        <v>137</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2"/>
       <c r="J4" s="3" t="s">
-        <v>132</v>
+        <v>124</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
       <c r="M4" s="3"/>
       <c r="N4" s="62" t="s">
-        <v>475</v>
+        <v>446</v>
       </c>
       <c r="O4" s="63"/>
       <c r="P4" s="63"/>
       <c r="Q4" s="64" t="s">
-        <v>472</v>
+        <v>443</v>
       </c>
       <c r="R4" s="64"/>
     </row>
     <row r="5" spans="1:19" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>175</v>
+        <v>146</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>60</v>
@@ -3134,17 +3144,17 @@
         <v>13</v>
       </c>
       <c r="O5" s="44" t="s">
-        <v>477</v>
+        <v>448</v>
       </c>
       <c r="P5" s="44" t="s">
         <v>14</v>
       </c>
       <c r="Q5" s="45" t="s">
-        <v>473</v>
+        <v>444</v>
       </c>
       <c r="R5" s="45"/>
       <c r="S5" s="45" t="s">
-        <v>474</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -3152,40 +3162,40 @@
         <v>0</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>176</v>
+        <v>147</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>177</v>
+        <v>148</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>179</v>
+        <v>150</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>180</v>
+        <v>151</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>181</v>
+        <v>152</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>182</v>
+        <v>153</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>183</v>
+        <v>154</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>184</v>
+        <v>155</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>185</v>
+        <v>156</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>186</v>
+        <v>157</v>
       </c>
       <c r="M6" s="47" t="s">
-        <v>187</v>
+        <v>158</v>
       </c>
       <c r="N6" s="17" t="s">
         <v>23</v>
@@ -3209,40 +3219,40 @@
         <v>24</v>
       </c>
       <c r="B7" s="27" t="s">
-        <v>188</v>
+        <v>159</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>189</v>
+        <v>160</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>190</v>
+        <v>161</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>191</v>
+        <v>162</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>192</v>
+        <v>163</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>193</v>
+        <v>164</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>194</v>
+        <v>165</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>195</v>
+        <v>166</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>196</v>
+        <v>167</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>197</v>
+        <v>168</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>198</v>
+        <v>169</v>
       </c>
       <c r="M7" s="47" t="s">
-        <v>199</v>
+        <v>170</v>
       </c>
       <c r="N7" s="17" t="s">
         <v>23</v>
@@ -3266,40 +3276,40 @@
         <v>33</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>200</v>
+        <v>171</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>201</v>
+        <v>172</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>202</v>
+        <v>173</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>203</v>
+        <v>174</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>204</v>
+        <v>175</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>206</v>
+        <v>177</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>207</v>
+        <v>178</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>208</v>
+        <v>179</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>209</v>
+        <v>180</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>210</v>
+        <v>181</v>
       </c>
       <c r="M8" s="47" t="s">
-        <v>211</v>
+        <v>182</v>
       </c>
       <c r="N8" s="17" t="s">
         <v>23</v>
@@ -3323,40 +3333,40 @@
         <v>42</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>212</v>
+        <v>183</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>213</v>
+        <v>184</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>214</v>
+        <v>185</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>215</v>
+        <v>186</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>217</v>
+        <v>188</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>218</v>
+        <v>189</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>219</v>
+        <v>190</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>220</v>
+        <v>191</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>221</v>
+        <v>192</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="M9" s="47" t="s">
-        <v>223</v>
+        <v>194</v>
       </c>
       <c r="N9" s="17" t="s">
         <v>23</v>
@@ -3380,40 +3390,40 @@
         <v>51</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>224</v>
+        <v>195</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>225</v>
+        <v>196</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>226</v>
+        <v>197</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>227</v>
+        <v>198</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>228</v>
+        <v>199</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>229</v>
+        <v>200</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>230</v>
+        <v>201</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>231</v>
+        <v>202</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>232</v>
+        <v>203</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>233</v>
+        <v>204</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>234</v>
+        <v>205</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>235</v>
+        <v>206</v>
       </c>
       <c r="N10" s="17" t="s">
         <v>23</v>
@@ -3448,30 +3458,30 @@
   <sheetData>
     <row r="1" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
-        <v>367</v>
+        <v>338</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="28" t="s">
-        <v>237</v>
+        <v>208</v>
       </c>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="29" t="s">
-        <v>238</v>
+        <v>209</v>
       </c>
       <c r="G4" s="29"/>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="3" t="s">
-        <v>239</v>
+        <v>210</v>
       </c>
       <c r="K4" s="3"/>
       <c r="L4" s="3"/>
@@ -3482,37 +3492,37 @@
       <c r="O4" s="61"/>
       <c r="P4" s="61"/>
       <c r="Q4" s="64" t="s">
-        <v>476</v>
+        <v>447</v>
       </c>
       <c r="R4" s="64"/>
     </row>
     <row r="5" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="F5" s="31" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="I5" s="31" t="s">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="J5" s="6" t="s">
         <v>60</v>
@@ -3530,16 +3540,16 @@
         <v>13</v>
       </c>
       <c r="O5" s="15" t="s">
-        <v>477</v>
+        <v>448</v>
       </c>
       <c r="P5" s="15" t="s">
         <v>14</v>
       </c>
       <c r="Q5" s="45" t="s">
-        <v>473</v>
+        <v>444</v>
       </c>
       <c r="R5" s="45" t="s">
-        <v>474</v>
+        <v>445</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -3547,40 +3557,40 @@
         <v>0</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>242</v>
+        <v>213</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>244</v>
+        <v>215</v>
       </c>
       <c r="E6" s="32" t="s">
-        <v>245</v>
+        <v>216</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>246</v>
+        <v>217</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>247</v>
+        <v>218</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>248</v>
+        <v>219</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>249</v>
+        <v>220</v>
       </c>
       <c r="J6" s="9" t="s">
-        <v>250</v>
+        <v>221</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>251</v>
+        <v>222</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>252</v>
+        <v>223</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>253</v>
+        <v>224</v>
       </c>
       <c r="N6" t="s">
         <v>23</v>
@@ -3603,40 +3613,40 @@
         <v>24</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>254</v>
+        <v>225</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>255</v>
+        <v>226</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>256</v>
+        <v>227</v>
       </c>
       <c r="E7" s="32" t="s">
-        <v>257</v>
+        <v>228</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>258</v>
+        <v>229</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>259</v>
+        <v>230</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>260</v>
+        <v>231</v>
       </c>
       <c r="I7" s="33" t="s">
-        <v>261</v>
+        <v>232</v>
       </c>
       <c r="J7" s="9" t="s">
-        <v>262</v>
+        <v>233</v>
       </c>
       <c r="K7" s="9" t="s">
-        <v>263</v>
+        <v>234</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>264</v>
+        <v>235</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>265</v>
+        <v>236</v>
       </c>
       <c r="N7" t="s">
         <v>23</v>
@@ -3659,40 +3669,40 @@
         <v>33</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>266</v>
+        <v>237</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>267</v>
+        <v>238</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>268</v>
+        <v>239</v>
       </c>
       <c r="E8" s="32" t="s">
-        <v>269</v>
+        <v>240</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>271</v>
+        <v>242</v>
       </c>
       <c r="H8" s="33" t="s">
-        <v>272</v>
+        <v>243</v>
       </c>
       <c r="I8" s="33" t="s">
-        <v>273</v>
+        <v>244</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>276</v>
+        <v>247</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>277</v>
+        <v>248</v>
       </c>
       <c r="N8" t="s">
         <v>23</v>
@@ -3715,40 +3725,40 @@
         <v>42</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>278</v>
+        <v>249</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="E9" s="32" t="s">
-        <v>281</v>
+        <v>252</v>
       </c>
       <c r="F9" s="33" t="s">
-        <v>282</v>
+        <v>253</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>283</v>
+        <v>254</v>
       </c>
       <c r="H9" s="33" t="s">
-        <v>284</v>
+        <v>255</v>
       </c>
       <c r="I9" s="33" t="s">
-        <v>285</v>
+        <v>256</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>286</v>
+        <v>257</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>287</v>
+        <v>258</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>288</v>
+        <v>259</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>289</v>
+        <v>260</v>
       </c>
       <c r="N9" t="s">
         <v>23</v>
@@ -3771,40 +3781,40 @@
         <v>51</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>290</v>
+        <v>261</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>291</v>
+        <v>262</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>292</v>
+        <v>263</v>
       </c>
       <c r="E10" s="32" t="s">
-        <v>293</v>
+        <v>264</v>
       </c>
       <c r="F10" s="33" t="s">
-        <v>294</v>
+        <v>265</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>295</v>
+        <v>266</v>
       </c>
       <c r="H10" s="33" t="s">
-        <v>296</v>
+        <v>267</v>
       </c>
       <c r="I10" s="33" t="s">
-        <v>297</v>
+        <v>268</v>
       </c>
       <c r="J10" s="9" t="s">
-        <v>298</v>
+        <v>269</v>
       </c>
       <c r="K10" s="9" t="s">
-        <v>299</v>
+        <v>270</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>301</v>
+        <v>272</v>
       </c>
       <c r="N10" t="s">
         <v>23</v>
@@ -3824,25 +3834,25 @@
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>302</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="36" t="s">
-        <v>303</v>
+        <v>274</v>
       </c>
       <c r="C14" s="36"/>
       <c r="D14" s="36"/>
       <c r="E14" s="36"/>
       <c r="F14" s="2" t="s">
-        <v>304</v>
+        <v>275</v>
       </c>
       <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="11" t="s">
-        <v>305</v>
+        <v>276</v>
       </c>
       <c r="K14" s="11"/>
       <c r="L14" s="11"/>
@@ -3853,37 +3863,37 @@
       <c r="O14" s="61"/>
       <c r="P14" s="61"/>
       <c r="Q14" s="64" t="s">
-        <v>476</v>
+        <v>447</v>
       </c>
       <c r="R14" s="64"/>
     </row>
     <row r="15" spans="1:18" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>167</v>
+        <v>138</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>168</v>
+        <v>139</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>169</v>
+        <v>140</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>172</v>
+        <v>143</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>174</v>
+        <v>145</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>241</v>
+        <v>212</v>
       </c>
       <c r="J15" s="12" t="s">
         <v>60</v>
@@ -3901,16 +3911,16 @@
         <v>13</v>
       </c>
       <c r="O15" s="15" t="s">
-        <v>477</v>
+        <v>448</v>
       </c>
       <c r="P15" s="15" t="s">
         <v>14</v>
       </c>
       <c r="Q15" s="45" t="s">
-        <v>473</v>
+        <v>444</v>
       </c>
       <c r="R15" s="45" t="s">
-        <v>474</v>
+        <v>445</v>
       </c>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
@@ -3918,40 +3928,40 @@
         <v>0</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>306</v>
+        <v>277</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>307</v>
+        <v>278</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>308</v>
+        <v>279</v>
       </c>
       <c r="E16" s="38" t="s">
-        <v>309</v>
+        <v>280</v>
       </c>
       <c r="F16" s="8" t="s">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>311</v>
+        <v>282</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>312</v>
+        <v>283</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="J16" s="13" t="s">
-        <v>314</v>
+        <v>285</v>
       </c>
       <c r="K16" s="13" t="s">
-        <v>315</v>
+        <v>286</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>316</v>
+        <v>287</v>
       </c>
       <c r="M16" s="13" t="s">
-        <v>317</v>
+        <v>288</v>
       </c>
       <c r="N16" s="50" t="s">
         <v>23</v>
@@ -3974,40 +3984,40 @@
         <v>24</v>
       </c>
       <c r="B17" s="38" t="s">
-        <v>318</v>
+        <v>289</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>319</v>
+        <v>290</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>320</v>
+        <v>291</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>321</v>
+        <v>292</v>
       </c>
       <c r="F17" s="8" t="s">
-        <v>322</v>
+        <v>293</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>323</v>
+        <v>294</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>324</v>
+        <v>295</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>325</v>
+        <v>296</v>
       </c>
       <c r="J17" s="13" t="s">
-        <v>326</v>
+        <v>297</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>327</v>
+        <v>298</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>328</v>
+        <v>299</v>
       </c>
       <c r="M17" s="13" t="s">
-        <v>329</v>
+        <v>300</v>
       </c>
       <c r="N17" s="50" t="s">
         <v>23</v>
@@ -4030,40 +4040,40 @@
         <v>33</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>330</v>
+        <v>301</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>331</v>
+        <v>302</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>332</v>
+        <v>303</v>
       </c>
       <c r="E18" s="38" t="s">
+        <v>279</v>
+      </c>
+      <c r="F18" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="G18" s="8" t="s">
+        <v>305</v>
+      </c>
+      <c r="H18" s="8" t="s">
+        <v>306</v>
+      </c>
+      <c r="I18" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="J18" s="13" t="s">
         <v>308</v>
       </c>
-      <c r="F18" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="G18" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="H18" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="I18" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>337</v>
-      </c>
       <c r="K18" s="13" t="s">
-        <v>337</v>
+        <v>308</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>338</v>
+        <v>309</v>
       </c>
       <c r="M18" s="13" t="s">
-        <v>339</v>
+        <v>310</v>
       </c>
       <c r="N18" s="50" t="s">
         <v>23</v>
@@ -4086,40 +4096,40 @@
         <v>42</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>340</v>
+        <v>311</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>341</v>
+        <v>312</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>342</v>
+        <v>313</v>
       </c>
       <c r="E19" s="38" t="s">
-        <v>343</v>
+        <v>314</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>344</v>
+        <v>315</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>345</v>
+        <v>316</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>346</v>
+        <v>317</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>347</v>
+        <v>318</v>
       </c>
       <c r="J19" s="13" t="s">
-        <v>348</v>
+        <v>319</v>
       </c>
       <c r="K19" s="13" t="s">
-        <v>349</v>
+        <v>320</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>350</v>
+        <v>321</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>351</v>
+        <v>322</v>
       </c>
       <c r="N19" s="50" t="s">
         <v>23</v>
@@ -4142,40 +4152,40 @@
         <v>51</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>352</v>
+        <v>323</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>353</v>
+        <v>324</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>354</v>
+        <v>325</v>
       </c>
       <c r="E20" s="38" t="s">
-        <v>355</v>
+        <v>326</v>
       </c>
       <c r="F20" s="8" t="s">
-        <v>356</v>
+        <v>327</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>357</v>
+        <v>328</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>358</v>
+        <v>329</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>359</v>
+        <v>330</v>
       </c>
       <c r="J20" s="13" t="s">
-        <v>360</v>
+        <v>331</v>
       </c>
       <c r="K20" s="13" t="s">
-        <v>361</v>
+        <v>332</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>362</v>
+        <v>333</v>
       </c>
       <c r="M20" s="13" t="s">
-        <v>363</v>
+        <v>334</v>
       </c>
       <c r="N20" s="50" t="s">
         <v>23</v>
@@ -4223,7 +4233,7 @@
         <v>13</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>471</v>
+        <v>442</v>
       </c>
       <c r="D23" s="15" t="s">
         <v>14</v>
@@ -4232,7 +4242,7 @@
         <v>13</v>
       </c>
       <c r="G23" s="15" t="s">
-        <v>471</v>
+        <v>442</v>
       </c>
       <c r="H23" s="15" t="s">
         <v>14</v>
@@ -4241,7 +4251,7 @@
         <v>13</v>
       </c>
       <c r="K23" s="15" t="s">
-        <v>471</v>
+        <v>442</v>
       </c>
       <c r="L23" s="15" t="s">
         <v>14</v>
@@ -4439,36 +4449,36 @@
     </row>
     <row r="30" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="65" t="s">
-        <v>481</v>
+        <v>452</v>
       </c>
       <c r="C30" s="66"/>
       <c r="F30" s="65" t="s">
-        <v>478</v>
+        <v>449</v>
       </c>
       <c r="G30" s="66"/>
       <c r="J30" s="65" t="s">
-        <v>478</v>
+        <v>449</v>
       </c>
       <c r="K30" s="66"/>
     </row>
     <row r="31" spans="1:18" ht="75" x14ac:dyDescent="0.25">
       <c r="B31" s="45" t="s">
-        <v>482</v>
+        <v>453</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>483</v>
+        <v>454</v>
       </c>
       <c r="F31" s="45" t="s">
-        <v>482</v>
+        <v>453</v>
       </c>
       <c r="G31" s="45" t="s">
-        <v>483</v>
+        <v>454</v>
       </c>
       <c r="J31" s="45" t="s">
-        <v>482</v>
+        <v>453</v>
       </c>
       <c r="K31" s="45" t="s">
-        <v>483</v>
+        <v>454</v>
       </c>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
@@ -4649,7 +4659,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
-        <v>470</v>
+        <v>441</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -4658,28 +4668,28 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>368</v>
+        <v>339</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="G3" s="57" t="s">
-        <v>479</v>
+        <v>450</v>
       </c>
       <c r="H3" s="57" t="s">
-        <v>480</v>
+        <v>451</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -4687,19 +4697,19 @@
         <v>0</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>373</v>
+        <v>344</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>374</v>
+        <v>345</v>
       </c>
       <c r="D4" s="42" t="s">
-        <v>375</v>
+        <v>346</v>
       </c>
       <c r="E4" s="42" t="s">
-        <v>376</v>
+        <v>347</v>
       </c>
       <c r="F4" s="42" t="s">
-        <v>377</v>
+        <v>348</v>
       </c>
       <c r="G4" s="17" t="s">
         <v>23</v>
@@ -4713,19 +4723,19 @@
         <v>24</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>378</v>
+        <v>349</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>379</v>
+        <v>350</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>380</v>
+        <v>351</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>381</v>
+        <v>352</v>
       </c>
       <c r="F5" s="42" t="s">
-        <v>382</v>
+        <v>353</v>
       </c>
       <c r="G5" s="17" t="s">
         <v>23</v>
@@ -4739,19 +4749,19 @@
         <v>33</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>383</v>
+        <v>354</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>384</v>
+        <v>355</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>385</v>
+        <v>356</v>
       </c>
       <c r="E6" s="42" t="s">
-        <v>386</v>
+        <v>357</v>
       </c>
       <c r="F6" s="42" t="s">
-        <v>387</v>
+        <v>358</v>
       </c>
       <c r="G6" s="1">
         <v>3.5799999999999998E-2</v>
@@ -4765,19 +4775,19 @@
         <v>42</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>388</v>
+        <v>359</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>389</v>
+        <v>360</v>
       </c>
       <c r="D7" s="42" t="s">
-        <v>390</v>
+        <v>361</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>391</v>
+        <v>362</v>
       </c>
       <c r="F7" s="42" t="s">
-        <v>392</v>
+        <v>363</v>
       </c>
       <c r="G7" s="4">
         <v>2.4500000000000001E-2</v>
@@ -4791,19 +4801,19 @@
         <v>51</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>393</v>
+        <v>364</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>394</v>
+        <v>365</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>395</v>
+        <v>366</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>396</v>
+        <v>367</v>
       </c>
       <c r="F8" s="42" t="s">
-        <v>397</v>
+        <v>368</v>
       </c>
       <c r="G8" s="4">
         <v>4.1700000000000001E-3</v>
@@ -4814,28 +4824,28 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>398</v>
+        <v>369</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="G10" s="57" t="s">
-        <v>479</v>
+        <v>450</v>
       </c>
       <c r="H10" s="57" t="s">
-        <v>480</v>
+        <v>451</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -4843,19 +4853,19 @@
         <v>0</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>399</v>
+        <v>370</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>400</v>
+        <v>371</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>401</v>
+        <v>372</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>402</v>
+        <v>373</v>
       </c>
       <c r="F11" s="42" t="s">
-        <v>403</v>
+        <v>374</v>
       </c>
       <c r="G11" s="17" t="s">
         <v>23</v>
@@ -4869,19 +4879,19 @@
         <v>24</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>404</v>
+        <v>375</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>405</v>
+        <v>376</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>406</v>
+        <v>377</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>407</v>
+        <v>378</v>
       </c>
       <c r="F12" s="42" t="s">
-        <v>408</v>
+        <v>379</v>
       </c>
       <c r="G12" s="17" t="s">
         <v>23</v>
@@ -4895,19 +4905,19 @@
         <v>33</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>409</v>
+        <v>380</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>410</v>
+        <v>381</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>411</v>
+        <v>382</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>412</v>
+        <v>383</v>
       </c>
       <c r="F13" s="42" t="s">
-        <v>413</v>
+        <v>384</v>
       </c>
       <c r="G13" s="17" t="s">
         <v>23</v>
@@ -4921,19 +4931,19 @@
         <v>42</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>414</v>
+        <v>385</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>415</v>
+        <v>386</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>416</v>
+        <v>387</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>417</v>
+        <v>388</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>418</v>
+        <v>389</v>
       </c>
       <c r="G14" s="17" t="s">
         <v>23</v>
@@ -4947,19 +4957,19 @@
         <v>51</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>419</v>
+        <v>390</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>420</v>
+        <v>391</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>421</v>
+        <v>392</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>422</v>
+        <v>393</v>
       </c>
       <c r="F15" s="42" t="s">
-        <v>423</v>
+        <v>394</v>
       </c>
       <c r="G15" s="4">
         <v>4.8899999999999999E-2</v>
@@ -4970,28 +4980,28 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>424</v>
+        <v>395</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="G17" s="57" t="s">
-        <v>479</v>
+        <v>450</v>
       </c>
       <c r="H17" s="57" t="s">
-        <v>480</v>
+        <v>451</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -4999,19 +5009,19 @@
         <v>0</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>425</v>
+        <v>396</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>426</v>
+        <v>397</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>427</v>
+        <v>398</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>428</v>
+        <v>399</v>
       </c>
       <c r="F18" s="42" t="s">
-        <v>429</v>
+        <v>400</v>
       </c>
       <c r="G18" s="17" t="s">
         <v>23</v>
@@ -5025,19 +5035,19 @@
         <v>24</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>430</v>
+        <v>401</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>431</v>
+        <v>402</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>432</v>
+        <v>403</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>428</v>
+        <v>399</v>
       </c>
       <c r="F19" s="42" t="s">
-        <v>429</v>
+        <v>400</v>
       </c>
       <c r="G19" s="4">
         <v>1.46E-2</v>
@@ -5051,19 +5061,19 @@
         <v>33</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>433</v>
+        <v>404</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>434</v>
+        <v>405</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>435</v>
+        <v>406</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>436</v>
+        <v>407</v>
       </c>
       <c r="F20" s="42" t="s">
-        <v>428</v>
+        <v>399</v>
       </c>
       <c r="G20" s="4">
         <v>1.01E-2</v>
@@ -5077,19 +5087,19 @@
         <v>42</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>437</v>
+        <v>408</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>438</v>
+        <v>409</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>439</v>
+        <v>410</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>436</v>
+        <v>407</v>
       </c>
       <c r="F21" s="42" t="s">
-        <v>440</v>
+        <v>411</v>
       </c>
       <c r="G21" s="17" t="s">
         <v>23</v>
@@ -5103,19 +5113,19 @@
         <v>51</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>441</v>
+        <v>412</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>442</v>
+        <v>413</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>443</v>
+        <v>414</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>436</v>
+        <v>407</v>
       </c>
       <c r="F22" s="42" t="s">
-        <v>428</v>
+        <v>399</v>
       </c>
       <c r="G22" s="4">
         <v>3.0800000000000001E-2</v>
@@ -5126,28 +5136,28 @@
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>444</v>
+        <v>415</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>369</v>
+        <v>340</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>370</v>
+        <v>341</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>371</v>
+        <v>342</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>372</v>
+        <v>343</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>240</v>
+        <v>211</v>
       </c>
       <c r="G24" s="57" t="s">
-        <v>479</v>
+        <v>450</v>
       </c>
       <c r="H24" s="57" t="s">
-        <v>480</v>
+        <v>451</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -5155,19 +5165,19 @@
         <v>0</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>445</v>
+        <v>416</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>446</v>
+        <v>417</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>447</v>
+        <v>418</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>448</v>
+        <v>419</v>
       </c>
       <c r="F25" s="42" t="s">
-        <v>449</v>
+        <v>420</v>
       </c>
       <c r="G25" s="17" t="s">
         <v>23</v>
@@ -5181,19 +5191,19 @@
         <v>24</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>450</v>
+        <v>421</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>451</v>
+        <v>422</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>452</v>
+        <v>423</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>453</v>
+        <v>424</v>
       </c>
       <c r="F26" s="42" t="s">
-        <v>454</v>
+        <v>425</v>
       </c>
       <c r="G26" s="17" t="s">
         <v>23</v>
@@ -5207,19 +5217,19 @@
         <v>33</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>455</v>
+        <v>426</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>456</v>
+        <v>427</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>457</v>
+        <v>428</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>458</v>
+        <v>429</v>
       </c>
       <c r="F27" s="42" t="s">
-        <v>459</v>
+        <v>430</v>
       </c>
       <c r="G27" s="1">
         <v>4.6399999999999997E-2</v>
@@ -5233,19 +5243,19 @@
         <v>42</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>460</v>
+        <v>431</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>461</v>
+        <v>432</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>462</v>
+        <v>433</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>463</v>
+        <v>434</v>
       </c>
       <c r="F28" s="42" t="s">
-        <v>464</v>
+        <v>435</v>
       </c>
       <c r="G28" s="4">
         <v>3.7699999999999997E-2</v>
@@ -5259,19 +5269,19 @@
         <v>51</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>465</v>
+        <v>436</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>466</v>
+        <v>437</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>467</v>
+        <v>438</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>468</v>
+        <v>439</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>469</v>
+        <v>440</v>
       </c>
       <c r="G29" s="4">
         <v>2.4E-2</v>

--- a/Part2_analyses/All_stats_clean.xlsx
+++ b/Part2_analyses/All_stats_clean.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1"/>
+    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="2" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="Table2" sheetId="3" r:id="rId3"/>
     <sheet name="Table 3" sheetId="4" r:id="rId4"/>
     <sheet name="Table 4" sheetId="6" r:id="rId5"/>
+    <sheet name="Table 5" sheetId="7" r:id="rId6"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,14 +29,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="811" uniqueCount="483">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="517">
   <si>
     <t>Regarding age</t>
   </si>
   <si>
-    <t>Old (&gt;40y.o.) = 472</t>
-  </si>
-  <si>
     <t>Young (&lt;40.y.o) = 1008</t>
   </si>
   <si>
@@ -225,126 +223,15 @@
     <t>7 (0.47%)</t>
   </si>
   <si>
-    <t>57 (6.62%)</t>
-  </si>
-  <si>
-    <t>4 (0.46%)</t>
-  </si>
-  <si>
-    <t>800 (92.92%)</t>
-  </si>
-  <si>
-    <t>857 (99.54%)</t>
-  </si>
-  <si>
-    <t>52 (6.04%)</t>
-  </si>
-  <si>
-    <t>18 (2.09%)</t>
-  </si>
-  <si>
-    <t>791 (91.87%)</t>
-  </si>
-  <si>
-    <t>843 (97.91%)</t>
-  </si>
-  <si>
-    <t>47 (5.46%)</t>
-  </si>
-  <si>
-    <t>43 (4.99%)</t>
-  </si>
-  <si>
-    <t>771 (89.55%)</t>
-  </si>
-  <si>
-    <t>818 (95.01%)</t>
-  </si>
-  <si>
-    <t>34 (3.95%)</t>
-  </si>
-  <si>
-    <t>195 (22.65%)</t>
-  </si>
-  <si>
-    <t>632 (73.40%)</t>
-  </si>
-  <si>
-    <t>666 (77.35%)</t>
-  </si>
-  <si>
-    <t>20 (2.32%)</t>
-  </si>
-  <si>
-    <t>403 (46.81%)</t>
-  </si>
-  <si>
-    <t>438 (50.87%)</t>
-  </si>
-  <si>
-    <t>458 (53.19%)</t>
-  </si>
-  <si>
-    <t>54 (8.71%)</t>
-  </si>
-  <si>
     <t>3 (0.48%)</t>
   </si>
   <si>
-    <t>563 (90.81%)</t>
-  </si>
-  <si>
-    <t>617 (99.52%)</t>
-  </si>
-  <si>
-    <t>43 (6.94%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 (3.71%) </t>
-  </si>
-  <si>
-    <t>554 (89.35%)</t>
-  </si>
-  <si>
-    <t>597 (96.29%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37 (5.97%) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 (8.06%)  </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 533 (85.97%)</t>
-  </si>
-  <si>
-    <t>570 (91.94%)</t>
-  </si>
-  <si>
     <t>21 (3.39%)</t>
   </si>
   <si>
-    <t>197 (31.77%)</t>
-  </si>
-  <si>
-    <t>402 (64.84%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 423 (68.23%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">12 (1.94%) </t>
   </si>
   <si>
-    <t>348 (56.13%)</t>
-  </si>
-  <si>
-    <t>260 (41.94%)</t>
-  </si>
-  <si>
-    <t>272 (43.87%)</t>
-  </si>
-  <si>
     <t>With all data</t>
   </si>
   <si>
@@ -402,9 +289,6 @@
     <t>BD patients = 433</t>
   </si>
   <si>
-    <t>Controls = 433</t>
-  </si>
-  <si>
     <t>Sex = Female(%)</t>
   </si>
   <si>
@@ -438,12 +322,6 @@
     <t>Balanced</t>
   </si>
   <si>
-    <t>Total = 866</t>
-  </si>
-  <si>
-    <t>BD = 433</t>
-  </si>
-  <si>
     <t>Threshold</t>
   </si>
   <si>
@@ -477,192 +355,30 @@
     <t>3 (0.35%)</t>
   </si>
   <si>
-    <t>805 (92.96%)</t>
-  </si>
-  <si>
-    <t>863 (99.65%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 30 (6.93%)  </t>
-  </si>
-  <si>
     <t xml:space="preserve">2 (0.46%)  </t>
   </si>
   <si>
-    <t>401 (92.61%)</t>
-  </si>
-  <si>
-    <t>431 (99.54%)</t>
-  </si>
-  <si>
-    <t>28 (6.47%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">1 (0.23%)   </t>
   </si>
   <si>
-    <t>404 (93.30%)</t>
-  </si>
-  <si>
-    <t>432 (99.77%)</t>
-  </si>
-  <si>
     <t>47 (5.43%)</t>
   </si>
   <si>
     <t>24 (2.77%)</t>
   </si>
   <si>
-    <t>795 (91.80%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 842 (97.23%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 22 (5.08%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 (3.70%)  </t>
-  </si>
-  <si>
-    <t>395 (91.22%)</t>
-  </si>
-  <si>
-    <t>417 (96.30%)</t>
-  </si>
-  <si>
-    <t>25 (5.77%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8 (1.85%) </t>
-  </si>
-  <si>
-    <t>400 (92.38%)</t>
-  </si>
-  <si>
-    <t>425 (98.15%)</t>
-  </si>
-  <si>
     <t>40 (4.62%)</t>
   </si>
   <si>
-    <t>56 (6.47%)</t>
-  </si>
-  <si>
-    <t>770 (88.91%)</t>
-  </si>
-  <si>
-    <t>810 (93.53%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 17 (3.93%) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">36 (8.31%)  </t>
-  </si>
-  <si>
-    <t>380 (87.76%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 397 (91.69%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23 (5.31%) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">20 (4.62%)  </t>
-  </si>
-  <si>
-    <t>390 (90.07%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 413 (95.38%)</t>
-  </si>
-  <si>
     <t>30 (3.46%)</t>
   </si>
   <si>
-    <t>185 (21.36%)</t>
-  </si>
-  <si>
-    <t>651 (75.17%)</t>
-  </si>
-  <si>
-    <t>681 (78.64%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 (3.00%)  </t>
-  </si>
-  <si>
-    <t>92 (21.25%)</t>
-  </si>
-  <si>
-    <t>328 (75.75%)</t>
-  </si>
-  <si>
-    <t>341 (78.75%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 17 (3.93%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 93 (21.48%) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 323 (74.60%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 340 (78.52%)</t>
-  </si>
-  <si>
     <t>18 (2.08%)</t>
   </si>
   <si>
-    <t>320 (36.95%)</t>
-  </si>
-  <si>
-    <t>528 (60.97%)</t>
-  </si>
-  <si>
-    <t>546 (63.05%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9 (2.08%)   </t>
-  </si>
-  <si>
-    <t>141 (32.56%)</t>
-  </si>
-  <si>
-    <t>283 (65.36%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 292 (67.44%)</t>
-  </si>
-  <si>
-    <t>9 (2.08%)</t>
-  </si>
-  <si>
-    <t>179 (41.34%)</t>
-  </si>
-  <si>
-    <t>245 (56.58%)</t>
-  </si>
-  <si>
-    <t>254 (58.66%)</t>
-  </si>
-  <si>
     <t>Females</t>
   </si>
   <si>
-    <t>Total = 528</t>
-  </si>
-  <si>
-    <t>BD =267</t>
-  </si>
-  <si>
-    <t>Controls =261</t>
-  </si>
-  <si>
     <t>Lateralized</t>
   </si>
   <si>
@@ -675,138 +391,51 @@
     <t xml:space="preserve">2 (0.38%) </t>
   </si>
   <si>
-    <t xml:space="preserve"> 497 (94.13%)</t>
-  </si>
-  <si>
-    <t>526 (99.62%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">17 (6.37%) </t>
   </si>
   <si>
     <t xml:space="preserve">1 (0.37%) </t>
   </si>
   <si>
-    <t xml:space="preserve"> 249 (93.26%)</t>
-  </si>
-  <si>
-    <t>266 (99.63%)</t>
-  </si>
-  <si>
-    <t>12 (4.60%)</t>
-  </si>
-  <si>
     <t>1 (0.38%)</t>
   </si>
   <si>
-    <t>248 (95.02%)</t>
-  </si>
-  <si>
-    <t>260 (99.62%)</t>
-  </si>
-  <si>
     <t>25 (4.73%)</t>
   </si>
   <si>
     <t>12 (2.27%)</t>
   </si>
   <si>
-    <t>491 (92.99%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 516 (97.73%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13 (4.87%) </t>
-  </si>
-  <si>
-    <t>8 (3.00%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 246 (92.13%)</t>
-  </si>
-  <si>
-    <t>259 (97.00%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">12 (4.60%)  </t>
   </si>
   <si>
     <t xml:space="preserve">4 (1.53%)  </t>
   </si>
   <si>
-    <t xml:space="preserve"> 245 (93.87%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  257 (98.47%)</t>
-  </si>
-  <si>
     <t>21 (3.98%)</t>
   </si>
   <si>
     <t>26 (4.92%)</t>
   </si>
   <si>
-    <t>481 (91.10%)</t>
-  </si>
-  <si>
-    <t>502 (95.08%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">10 (3.75%) </t>
   </si>
   <si>
     <t>18 (6.74%)</t>
   </si>
   <si>
-    <t>239 (89.51%)</t>
-  </si>
-  <si>
-    <t>249 (93.26%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">11 (4.21%) </t>
   </si>
   <si>
     <t xml:space="preserve"> 8 (3.07%)</t>
   </si>
   <si>
-    <t>242 (92.72%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 253 (96.93%)</t>
-  </si>
-  <si>
-    <t>16 (3.03%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">96 (18.18%) </t>
-  </si>
-  <si>
-    <t>416 (78.79%)</t>
-  </si>
-  <si>
-    <t>432 (81.82%)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 7 (2.62%) </t>
   </si>
   <si>
-    <t xml:space="preserve">53 (19.85%) </t>
-  </si>
-  <si>
-    <t>207 (77.53%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 214 (80.15%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">9 (3.45%)   </t>
   </si>
   <si>
-    <t>43 (16.48%)</t>
-  </si>
-  <si>
     <t>209 (80.08%)</t>
   </si>
   <si>
@@ -816,33 +445,12 @@
     <t xml:space="preserve">10 (1.89%)  </t>
   </si>
   <si>
-    <t>176 (33.33%)</t>
-  </si>
-  <si>
-    <t>342 (64.77%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 352 (66.67%)</t>
-  </si>
-  <si>
     <t>5 (1.87%)</t>
   </si>
   <si>
-    <t>80 (29.96%)</t>
-  </si>
-  <si>
-    <t>182 (68.16%)</t>
-  </si>
-  <si>
-    <t>187 (70.04%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">5 (1.92%) </t>
   </si>
   <si>
-    <t xml:space="preserve">96 (36.78%) </t>
-  </si>
-  <si>
     <t>160 (61.30%)</t>
   </si>
   <si>
@@ -852,189 +460,66 @@
     <t>Males</t>
   </si>
   <si>
-    <t>Total = 336</t>
-  </si>
-  <si>
-    <t>BD = 165</t>
-  </si>
-  <si>
-    <t>Controls =171</t>
-  </si>
-  <si>
     <t xml:space="preserve">29 (8.63%) </t>
   </si>
   <si>
     <t xml:space="preserve"> 1 (0.30%) </t>
   </si>
   <si>
-    <t>306 (91.07%)</t>
-  </si>
-  <si>
-    <t>335 (99.70%)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 13 (7.88%)</t>
   </si>
   <si>
     <t xml:space="preserve"> 1 (0.61%)  </t>
   </si>
   <si>
-    <t>151 (91.52%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 164 (99.39%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16 (9.36%) </t>
-  </si>
-  <si>
     <t>0 (0%)</t>
   </si>
   <si>
-    <t xml:space="preserve"> 155 (90.64%)</t>
-  </si>
-  <si>
-    <t>171 (100.00%)</t>
-  </si>
-  <si>
     <t xml:space="preserve"> 22 (6.55%)  </t>
   </si>
   <si>
     <t xml:space="preserve"> 12 (3.57%)  </t>
   </si>
   <si>
-    <t>302 (89.88%)</t>
-  </si>
-  <si>
-    <t>324 (96.43%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">9 (5.45%) </t>
   </si>
   <si>
     <t>8 (4.85%)</t>
   </si>
   <si>
-    <t>148 (89.70%</t>
-  </si>
-  <si>
-    <t>157 (95.15%)</t>
-  </si>
-  <si>
     <t>13 (7.60%)</t>
   </si>
   <si>
     <t xml:space="preserve">4 (2.34%) </t>
   </si>
   <si>
-    <t>154 (90.06%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 167 (97.66%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">19 (5.65%)  </t>
   </si>
   <si>
-    <t xml:space="preserve">30 (8.93%) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 287 (85.42%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">7 (4.24%) </t>
   </si>
   <si>
     <t xml:space="preserve">18 (10.91%) </t>
   </si>
   <si>
-    <t>140 (84.85%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 147 (89.09%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12 (7.02%) </t>
-  </si>
-  <si>
-    <t>147 (85.96%)</t>
-  </si>
-  <si>
-    <t>159 (92.98%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  14 (4.17%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">88 (26.19%) </t>
-  </si>
-  <si>
-    <t>234 (69.64%)</t>
-  </si>
-  <si>
-    <t>248 (73.81%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">6 (3.64%)   </t>
   </si>
   <si>
     <t xml:space="preserve">38 (23.03%) </t>
   </si>
   <si>
-    <t>121 (73.33%)</t>
-  </si>
-  <si>
-    <t>127 (76.97%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">8 (4.68%)  </t>
   </si>
   <si>
-    <t xml:space="preserve">50 (29.24%) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 113 (66.08%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  121 (70.76%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">8 (2.38%) </t>
   </si>
   <si>
-    <t>142 (42.26%)</t>
-  </si>
-  <si>
-    <t>186 (55.36%)</t>
-  </si>
-  <si>
-    <t>194 (57.74%)</t>
-  </si>
-  <si>
     <t xml:space="preserve">4 (2.42%)   </t>
   </si>
   <si>
     <t xml:space="preserve">60 (36.36%) </t>
   </si>
   <si>
-    <t xml:space="preserve"> 101 (61.21%)</t>
-  </si>
-  <si>
-    <t>105 (63.64%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4 (2.34%)   </t>
-  </si>
-  <si>
-    <t>82 (47.95%)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">85 (49.71%) </t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 89 (52.05%) </t>
-  </si>
-  <si>
     <t>Table 1: Characteristics of the sample</t>
   </si>
   <si>
@@ -1359,9 +844,6 @@
     <t>Non-right-handedness</t>
   </si>
   <si>
-    <t>Regression model of BD_patient ~ predictor + covariates (Sex + Age)</t>
-  </si>
-  <si>
     <t>P-value of Non-right-handedness</t>
   </si>
   <si>
@@ -1477,6 +959,627 @@
   </si>
   <si>
     <t xml:space="preserve"> 1473 (99.53%)</t>
+  </si>
+  <si>
+    <t>455 (53.09%)</t>
+  </si>
+  <si>
+    <t>435 (50.76%)</t>
+  </si>
+  <si>
+    <t>402 (46.91%)</t>
+  </si>
+  <si>
+    <t>20 (2.33%)</t>
+  </si>
+  <si>
+    <t>350 (56.18%)</t>
+  </si>
+  <si>
+    <t>261 (41.89%)</t>
+  </si>
+  <si>
+    <t>273 (43.82%)</t>
+  </si>
+  <si>
+    <t>663 (77.36%)</t>
+  </si>
+  <si>
+    <t>629 (73.40%)</t>
+  </si>
+  <si>
+    <t>194 (22.64%)</t>
+  </si>
+  <si>
+    <t>34 (3.97%)</t>
+  </si>
+  <si>
+    <t>426 (68.38%)</t>
+  </si>
+  <si>
+    <t>405 (65.01%)</t>
+  </si>
+  <si>
+    <t>197 (31.62%)</t>
+  </si>
+  <si>
+    <t>814 (94.98%)</t>
+  </si>
+  <si>
+    <t>767 (89.50%)</t>
+  </si>
+  <si>
+    <t>43 (5.02%)</t>
+  </si>
+  <si>
+    <t>47 (5.48%)</t>
+  </si>
+  <si>
+    <t>572 (91.81%)</t>
+  </si>
+  <si>
+    <t>535 (85.87%)</t>
+  </si>
+  <si>
+    <t>51 (8.19%)</t>
+  </si>
+  <si>
+    <t>37 (5.94%)</t>
+  </si>
+  <si>
+    <t>839 (97.90%)</t>
+  </si>
+  <si>
+    <t>787 (91.83%)</t>
+  </si>
+  <si>
+    <t>18 (2.10%)</t>
+  </si>
+  <si>
+    <t>52 (6.07%)</t>
+  </si>
+  <si>
+    <t>599 (96.15%)</t>
+  </si>
+  <si>
+    <t>556 (89.25%)</t>
+  </si>
+  <si>
+    <t>24 (3.85%)</t>
+  </si>
+  <si>
+    <t>43 (6.90%)</t>
+  </si>
+  <si>
+    <t>55 (8.83%)</t>
+  </si>
+  <si>
+    <t>565 (90.69%)</t>
+  </si>
+  <si>
+    <t>620 (99.52%)</t>
+  </si>
+  <si>
+    <t>57 (6.65%)</t>
+  </si>
+  <si>
+    <t>4 (0.47%)</t>
+  </si>
+  <si>
+    <t>796 (92.88%)</t>
+  </si>
+  <si>
+    <t>853 (99.53%)</t>
+  </si>
+  <si>
+    <t>61 (7.1%)</t>
+  </si>
+  <si>
+    <t>70 (8.17%)</t>
+  </si>
+  <si>
+    <t>90 (10.5%)</t>
+  </si>
+  <si>
+    <t>228 (26.6%)</t>
+  </si>
+  <si>
+    <t>422 (49.2%)</t>
+  </si>
+  <si>
+    <t>119 (8.04%)</t>
+  </si>
+  <si>
+    <t>137 (9.26%)</t>
+  </si>
+  <si>
+    <t>178 (12.03%)</t>
+  </si>
+  <si>
+    <t>450 (30.41%)</t>
+  </si>
+  <si>
+    <t>784 (52.97%)</t>
+  </si>
+  <si>
+    <t>58 (9.31%)</t>
+  </si>
+  <si>
+    <t>67 (10.75%)</t>
+  </si>
+  <si>
+    <t>88 (14.12%)</t>
+  </si>
+  <si>
+    <t>218 (34.99%)</t>
+  </si>
+  <si>
+    <t>362 (58.11%)</t>
+  </si>
+  <si>
+    <t>Old (=&gt;40y.o.) = 472</t>
+  </si>
+  <si>
+    <t>PRSs</t>
+  </si>
+  <si>
+    <t>Regression model of NRH_cutoff  ~ Sex + Age</t>
+  </si>
+  <si>
+    <t>NRH</t>
+  </si>
+  <si>
+    <t>NRH (SEX P-value)</t>
+  </si>
+  <si>
+    <t>NRH (Age P-value)</t>
+  </si>
+  <si>
+    <t>Total = 872</t>
+  </si>
+  <si>
+    <t>BD = 436</t>
+  </si>
+  <si>
+    <t>Controls = 436</t>
+  </si>
+  <si>
+    <t>811 (93.00%)</t>
+  </si>
+  <si>
+    <t>869 (99.66%)</t>
+  </si>
+  <si>
+    <t>801 (91.86%)</t>
+  </si>
+  <si>
+    <t>848 (97.25%)</t>
+  </si>
+  <si>
+    <t>57 (6.54%)</t>
+  </si>
+  <si>
+    <t>775 (88.88%)</t>
+  </si>
+  <si>
+    <t>815 (93.46%)</t>
+  </si>
+  <si>
+    <t>187 (21.44%)</t>
+  </si>
+  <si>
+    <t>655 (75.11%)</t>
+  </si>
+  <si>
+    <t>685 (78.56%)</t>
+  </si>
+  <si>
+    <t>324 (37.16%)</t>
+  </si>
+  <si>
+    <t>530 (60.78%)</t>
+  </si>
+  <si>
+    <t>548 (62.84%)</t>
+  </si>
+  <si>
+    <t>61 (7%)</t>
+  </si>
+  <si>
+    <t>71 (8.14%)</t>
+  </si>
+  <si>
+    <t>97 (11.12%)</t>
+  </si>
+  <si>
+    <t>217 (24.89%)</t>
+  </si>
+  <si>
+    <t>342 (39.22%)</t>
+  </si>
+  <si>
+    <t>28 (6.42%)</t>
+  </si>
+  <si>
+    <t>407 (93.35%)</t>
+  </si>
+  <si>
+    <t>435 (99.77%)</t>
+  </si>
+  <si>
+    <t>30 (6.88%)</t>
+  </si>
+  <si>
+    <t>404 (92.66%)</t>
+  </si>
+  <si>
+    <t>434 (99.54%)</t>
+  </si>
+  <si>
+    <t>25 (5.73%)</t>
+  </si>
+  <si>
+    <t>8 (1.83%)</t>
+  </si>
+  <si>
+    <t>403 (92.43%)</t>
+  </si>
+  <si>
+    <t>428 (98.17%)</t>
+  </si>
+  <si>
+    <t>23 (5.28%)</t>
+  </si>
+  <si>
+    <t>21 (4.82%)</t>
+  </si>
+  <si>
+    <t>392 (89.91%)</t>
+  </si>
+  <si>
+    <t>415 (95.18%)</t>
+  </si>
+  <si>
+    <t>13 (2.98%)</t>
+  </si>
+  <si>
+    <t>17 (3.90%)</t>
+  </si>
+  <si>
+    <t>95 (21.79%)</t>
+  </si>
+  <si>
+    <t>324 (74.31%)</t>
+  </si>
+  <si>
+    <t>341 (78.21%)</t>
+  </si>
+  <si>
+    <t>92 (21.10%)</t>
+  </si>
+  <si>
+    <t>331 (75.92%)</t>
+  </si>
+  <si>
+    <t>344 (78.90%)</t>
+  </si>
+  <si>
+    <t>400 (91.74%)</t>
+  </si>
+  <si>
+    <t>383 (87.84%)</t>
+  </si>
+  <si>
+    <t>36 (8.26%)</t>
+  </si>
+  <si>
+    <t>22 (5.05%)</t>
+  </si>
+  <si>
+    <t>16 (3.67%)</t>
+  </si>
+  <si>
+    <t>398 (91.28%)</t>
+  </si>
+  <si>
+    <t>420 (96.33%)</t>
+  </si>
+  <si>
+    <t>182 (41.74%)</t>
+  </si>
+  <si>
+    <t>254 (58.26%)</t>
+  </si>
+  <si>
+    <t>245 (56.19%)</t>
+  </si>
+  <si>
+    <t>9 (2.06%)</t>
+  </si>
+  <si>
+    <t>142 (32.57%)</t>
+  </si>
+  <si>
+    <t>285 (65.37%)</t>
+  </si>
+  <si>
+    <t>294 (67.43%)</t>
+  </si>
+  <si>
+    <t>32 (7.34%)</t>
+  </si>
+  <si>
+    <t>38 (8.71%)</t>
+  </si>
+  <si>
+    <t>53 (12.16%)</t>
+  </si>
+  <si>
+    <t>105 (24.08%)</t>
+  </si>
+  <si>
+    <t>151 (34.63%)</t>
+  </si>
+  <si>
+    <t>181 (41.51%)</t>
+  </si>
+  <si>
+    <t>112 (25.69%)</t>
+  </si>
+  <si>
+    <t>29 (6.65%)</t>
+  </si>
+  <si>
+    <t>33 (7.57%)</t>
+  </si>
+  <si>
+    <t>44 (10.09%)</t>
+  </si>
+  <si>
+    <t>Regression model of HANDUSE ~ BD_patient + covariates (Sex + Age)</t>
+  </si>
+  <si>
+    <t>P-value of NRH</t>
+  </si>
+  <si>
+    <t>Total = 532</t>
+  </si>
+  <si>
+    <t>BD = 270</t>
+  </si>
+  <si>
+    <t>Controls =262</t>
+  </si>
+  <si>
+    <t>Total = 340</t>
+  </si>
+  <si>
+    <t>BD = 166</t>
+  </si>
+  <si>
+    <t>Controls =174</t>
+  </si>
+  <si>
+    <t>501 (94.17%)</t>
+  </si>
+  <si>
+    <t>530 (99.62%)</t>
+  </si>
+  <si>
+    <t>495 (93.05%)</t>
+  </si>
+  <si>
+    <t>520 (97.74%)</t>
+  </si>
+  <si>
+    <t>485 (91.17%)</t>
+  </si>
+  <si>
+    <t>506 (95.11%)</t>
+  </si>
+  <si>
+    <t>98 (18.42%)</t>
+  </si>
+  <si>
+    <t>16 (3.01%)</t>
+  </si>
+  <si>
+    <t>418 (78.57%)</t>
+  </si>
+  <si>
+    <t>434 (81.58%)</t>
+  </si>
+  <si>
+    <t>179 (33.65%)</t>
+  </si>
+  <si>
+    <t>343 (64.47%)</t>
+  </si>
+  <si>
+    <t>353 (66.35%)</t>
+  </si>
+  <si>
+    <t>310 (91.18%)</t>
+  </si>
+  <si>
+    <t>339 (99.71%)</t>
+  </si>
+  <si>
+    <t>306 (90.00%)</t>
+  </si>
+  <si>
+    <t>328 (96.47%)</t>
+  </si>
+  <si>
+    <t>31 (9.12%)</t>
+  </si>
+  <si>
+    <t>290 (85.29%)</t>
+  </si>
+  <si>
+    <t>309 (90.88%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 (4.12%) </t>
+  </si>
+  <si>
+    <t>89 (26.18%)</t>
+  </si>
+  <si>
+    <t>237 (69.71%)</t>
+  </si>
+  <si>
+    <t>251 (73.82%)</t>
+  </si>
+  <si>
+    <t>195 (57.35%)</t>
+  </si>
+  <si>
+    <t>187 (55.00%)</t>
+  </si>
+  <si>
+    <t>145 (42.65%)</t>
+  </si>
+  <si>
+    <t>12 (4.58%)</t>
+  </si>
+  <si>
+    <t>249 (95.04%)</t>
+  </si>
+  <si>
+    <t>261 (99.62%)</t>
+  </si>
+  <si>
+    <t>252 (93.33%)</t>
+  </si>
+  <si>
+    <t>269 (99.63%)</t>
+  </si>
+  <si>
+    <t>246 (93.89%)</t>
+  </si>
+  <si>
+    <t>258 (98.47%)</t>
+  </si>
+  <si>
+    <t>13 (4.81%)</t>
+  </si>
+  <si>
+    <t>8 (2.96%)</t>
+  </si>
+  <si>
+    <t>249 (92.22%)</t>
+  </si>
+  <si>
+    <t>262 (97.04%)</t>
+  </si>
+  <si>
+    <t>243 (92.75%)</t>
+  </si>
+  <si>
+    <t>254 (96.95%)</t>
+  </si>
+  <si>
+    <t>242 (89.63%)</t>
+  </si>
+  <si>
+    <t>44 (16.79%)</t>
+  </si>
+  <si>
+    <t>54 (20.00%)</t>
+  </si>
+  <si>
+    <t>209 (77.41%)</t>
+  </si>
+  <si>
+    <t>216 (80.00%)</t>
+  </si>
+  <si>
+    <t>97 (37.02%)</t>
+  </si>
+  <si>
+    <t>82 (30.37%)</t>
+  </si>
+  <si>
+    <t>183 (67.78%)</t>
+  </si>
+  <si>
+    <t>188 (69.63%)</t>
+  </si>
+  <si>
+    <t>106 (63.86%)</t>
+  </si>
+  <si>
+    <t>102 (61.45%)</t>
+  </si>
+  <si>
+    <t>89 (51.15%)</t>
+  </si>
+  <si>
+    <t>85 (48.85%)</t>
+  </si>
+  <si>
+    <t>4 (2.30%)</t>
+  </si>
+  <si>
+    <t>128 (77.11%)</t>
+  </si>
+  <si>
+    <t>122 (73.49%)</t>
+  </si>
+  <si>
+    <t>123 (70.69%)</t>
+  </si>
+  <si>
+    <t>115 (66.09%)</t>
+  </si>
+  <si>
+    <t>51 (29.31%)</t>
+  </si>
+  <si>
+    <t>148 (89.16%)</t>
+  </si>
+  <si>
+    <t>141 (84.94%)</t>
+  </si>
+  <si>
+    <t>161 (92.53%)</t>
+  </si>
+  <si>
+    <t>149 (85.63%)</t>
+  </si>
+  <si>
+    <t>13 (7.47%)</t>
+  </si>
+  <si>
+    <t>12 (6.90%)</t>
+  </si>
+  <si>
+    <t>158 (95.18%)</t>
+  </si>
+  <si>
+    <t>149 (89.76%)</t>
+  </si>
+  <si>
+    <t>170 (97.70%)</t>
+  </si>
+  <si>
+    <t>157 (90.23%)</t>
+  </si>
+  <si>
+    <t>165 (99.40%)</t>
+  </si>
+  <si>
+    <t>152 (91.57%)</t>
+  </si>
+  <si>
+    <t>174 (100.00%)</t>
+  </si>
+  <si>
+    <t>158 (90.80%)</t>
+  </si>
+  <si>
+    <t>16 (9.20%)</t>
   </si>
 </sst>
 </file>
@@ -1583,7 +1686,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1662,8 +1765,14 @@
         <bgColor rgb="FFFFE7E7"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCFF"/>
+        <bgColor rgb="FFFBE5D6"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1730,11 +1839,24 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="85">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1815,9 +1937,6 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -1830,11 +1949,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1854,14 +1970,55 @@
     <xf numFmtId="0" fontId="2" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1871,8 +2028,8 @@
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FFFFCCFF"/>
       <color rgb="FFFFEFFF"/>
-      <color rgb="FFFFCCFF"/>
       <color rgb="FFDBEDE9"/>
     </mruColors>
   </colors>
@@ -2160,42 +2317,42 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
-        <v>335</v>
+        <v>163</v>
       </c>
       <c r="D1" s="14"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
       <c r="B3" s="1" t="s">
-        <v>461</v>
+        <v>288</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>106</v>
+        <v>68</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>460</v>
+        <v>287</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>127</v>
+        <v>88</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>456</v>
+        <v>283</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>457</v>
+        <v>284</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>458</v>
+        <v>285</v>
       </c>
       <c r="E4" s="17">
         <v>0.16300000000000001</v>
@@ -2203,33 +2360,33 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>109</v>
+        <v>71</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>459</v>
+        <v>286</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="E5" s="18" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="C6" s="17" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>114</v>
+        <v>76</v>
       </c>
       <c r="E6" s="1">
         <v>8.2999999999999999E-9</v>
@@ -2237,16 +2394,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="C7" s="17" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>117</v>
+        <v>79</v>
       </c>
       <c r="E7" s="1">
         <v>7.1999999999999996E-13</v>
@@ -2254,16 +2411,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="C8" s="17" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="D8" s="17" t="s">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="E8" s="19">
         <v>5.5000000000000002E-5</v>
@@ -2271,36 +2428,36 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>121</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A11" s="10"/>
       <c r="B11" s="4" t="s">
-        <v>122</v>
+        <v>84</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>134</v>
+        <v>95</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>107</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>125</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>465</v>
+        <v>292</v>
       </c>
       <c r="C12" t="s">
-        <v>464</v>
+        <v>291</v>
       </c>
       <c r="D12" t="s">
-        <v>457</v>
+        <v>284</v>
       </c>
       <c r="E12" s="20">
         <v>0.67579999999999996</v>
@@ -2308,16 +2465,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>108</v>
+        <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>463</v>
+        <v>290</v>
       </c>
       <c r="C13" t="s">
-        <v>462</v>
+        <v>289</v>
       </c>
       <c r="D13" t="s">
-        <v>459</v>
+        <v>286</v>
       </c>
       <c r="E13" s="21">
         <v>2.8678831295294999E-3</v>
@@ -2325,16 +2482,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>112</v>
+        <v>74</v>
       </c>
       <c r="B14" t="s">
-        <v>126</v>
+        <v>87</v>
       </c>
       <c r="C14" t="s">
-        <v>113</v>
+        <v>75</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>77</v>
       </c>
       <c r="E14" s="21">
         <v>2.3E-2</v>
@@ -2342,16 +2499,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>128</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>78</v>
       </c>
       <c r="E15" s="19">
         <v>1.7271311771889999E-4</v>
@@ -2359,16 +2516,16 @@
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>129</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="C16" t="s">
-        <v>118</v>
+        <v>80</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>82</v>
       </c>
       <c r="E16" s="21">
         <v>1.4999999999999999E-2</v>
@@ -2381,265 +2538,295 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S22"/>
+  <dimension ref="A1:T22"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.28515625" customWidth="1"/>
     <col min="2" max="2" width="10.85546875" customWidth="1"/>
     <col min="3" max="3" width="11.85546875" customWidth="1"/>
     <col min="4" max="4" width="13.42578125" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
+    <col min="9" max="9" width="12.28515625" customWidth="1"/>
+    <col min="14" max="14" width="13.140625" customWidth="1"/>
+    <col min="15" max="15" width="16" customWidth="1"/>
+    <col min="20" max="20" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:20" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="40" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="22" t="s">
-        <v>460</v>
+        <v>287</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
       <c r="G3" s="3" t="s">
-        <v>468</v>
+        <v>295</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="11" t="s">
-        <v>467</v>
+        <v>294</v>
       </c>
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
       <c r="O3" s="11"/>
       <c r="P3" s="11"/>
-      <c r="Q3" s="61" t="s">
+      <c r="Q3" s="66" t="s">
+        <v>2</v>
+      </c>
+      <c r="R3" s="67"/>
+      <c r="S3" s="67"/>
+      <c r="T3" s="65" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="R3" s="61"/>
-    </row>
-    <row r="4" spans="1:19" ht="60" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
-        <v>4</v>
-      </c>
       <c r="B4" s="23" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" s="23" t="s">
         <v>60</v>
       </c>
-      <c r="C4" s="23" t="s">
+      <c r="D4" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="D4" s="23" t="s">
+      <c r="E4" s="23" t="s">
+        <v>282</v>
+      </c>
+      <c r="F4" s="23" t="s">
         <v>62</v>
       </c>
-      <c r="E4" s="23" t="s">
-        <v>455</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>63</v>
-      </c>
       <c r="G4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="I4" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="J4" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="K4" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="J4" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>63</v>
-      </c>
       <c r="L4" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="M4" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="M4" s="12" t="s">
+      <c r="N4" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="N4" s="12" t="s">
+      <c r="O4" s="12" t="s">
+        <v>282</v>
+      </c>
+      <c r="P4" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="O4" s="12" t="s">
-        <v>455</v>
-      </c>
-      <c r="P4" s="12" t="s">
-        <v>63</v>
-      </c>
       <c r="Q4" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="R4" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="S4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="R4" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="S4" s="15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T4" s="65" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>0</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>480</v>
+        <v>307</v>
       </c>
       <c r="C5" s="24" t="s">
+        <v>63</v>
+      </c>
+      <c r="D5" s="24" t="s">
+        <v>308</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>352</v>
+      </c>
+      <c r="F5" s="24" t="s">
+        <v>309</v>
+      </c>
+      <c r="G5" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>344</v>
+      </c>
+      <c r="I5" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="J5" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="K5" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="L5" s="13" t="s">
+        <v>340</v>
+      </c>
+      <c r="M5" s="13" t="s">
         <v>64</v>
       </c>
-      <c r="D5" s="24" t="s">
-        <v>481</v>
-      </c>
-      <c r="E5" s="24">
-        <v>119</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>482</v>
-      </c>
-      <c r="G5" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="I5" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="L5" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="M5" s="13" t="s">
-        <v>86</v>
-      </c>
       <c r="N5" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="O5" s="13"/>
+        <v>341</v>
+      </c>
+      <c r="O5" s="13" t="s">
+        <v>357</v>
+      </c>
       <c r="P5" s="13" t="s">
-        <v>88</v>
+        <v>342</v>
       </c>
       <c r="Q5" t="s">
+        <v>22</v>
+      </c>
+      <c r="R5" t="s">
+        <v>22</v>
+      </c>
+      <c r="S5" t="s">
+        <v>22</v>
+      </c>
+      <c r="T5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="R5" t="s">
-        <v>23</v>
-      </c>
-      <c r="S5" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="B6" s="24" t="s">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="C6" s="24" t="s">
-        <v>131</v>
+        <v>92</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>478</v>
-      </c>
-      <c r="E6" s="24">
-        <v>137</v>
+        <v>305</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>353</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>479</v>
+        <v>306</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>69</v>
+        <v>335</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>70</v>
+        <v>334</v>
       </c>
       <c r="I6" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="J6" s="9"/>
+        <v>333</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>348</v>
+      </c>
       <c r="K6" s="9" t="s">
-        <v>72</v>
+        <v>332</v>
       </c>
       <c r="L6" s="13" t="s">
-        <v>89</v>
+        <v>339</v>
       </c>
       <c r="M6" s="13" t="s">
-        <v>90</v>
+        <v>338</v>
       </c>
       <c r="N6" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="O6" s="13"/>
+        <v>337</v>
+      </c>
+      <c r="O6" s="13" t="s">
+        <v>358</v>
+      </c>
       <c r="P6" s="13" t="s">
-        <v>92</v>
+        <v>336</v>
       </c>
       <c r="Q6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R6" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="S6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="T6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B7" s="24" t="s">
-        <v>132</v>
+        <v>93</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>477</v>
+        <v>304</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>476</v>
-      </c>
-      <c r="E7" s="24">
-        <v>178</v>
+        <v>303</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>354</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>475</v>
+        <v>302</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>73</v>
+        <v>327</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>74</v>
+        <v>326</v>
       </c>
       <c r="I7" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="J7" s="9"/>
+        <v>325</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>349</v>
+      </c>
       <c r="K7" s="9" t="s">
-        <v>76</v>
+        <v>324</v>
       </c>
       <c r="L7" s="13" t="s">
-        <v>93</v>
+        <v>331</v>
       </c>
       <c r="M7" s="13" t="s">
-        <v>94</v>
+        <v>330</v>
       </c>
       <c r="N7" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="O7" s="13"/>
+        <v>329</v>
+      </c>
+      <c r="O7" s="13" t="s">
+        <v>359</v>
+      </c>
       <c r="P7" s="13" t="s">
-        <v>96</v>
+        <v>328</v>
       </c>
       <c r="Q7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R7" s="10">
         <v>3.61E-2</v>
@@ -2647,54 +2834,61 @@
       <c r="S7" s="10">
         <v>1.627E-2</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T7" s="43">
+        <v>3.9300000000000002E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>474</v>
+        <v>301</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>473</v>
+        <v>300</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>472</v>
-      </c>
-      <c r="E8" s="24">
-        <v>450</v>
+        <v>299</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>355</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>471</v>
+        <v>298</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>77</v>
+        <v>320</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>78</v>
+        <v>319</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="J8" s="9"/>
+        <v>318</v>
+      </c>
+      <c r="J8" s="9" t="s">
+        <v>350</v>
+      </c>
       <c r="K8" s="9" t="s">
-        <v>80</v>
+        <v>317</v>
       </c>
       <c r="L8" s="13" t="s">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>98</v>
+        <v>323</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="O8" s="13"/>
+        <v>322</v>
+      </c>
+      <c r="O8" s="13" t="s">
+        <v>360</v>
+      </c>
       <c r="P8" s="13" t="s">
-        <v>100</v>
+        <v>321</v>
       </c>
       <c r="Q8" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R8" s="10">
         <v>3.97E-4</v>
@@ -2702,54 +2896,61 @@
       <c r="S8" s="16">
         <v>8.5870000000000003E-5</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T8" s="43">
+        <v>7.2300000000000001E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B9" s="24" t="s">
-        <v>133</v>
+        <v>94</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>466</v>
+        <v>293</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>469</v>
-      </c>
-      <c r="E9" s="24">
-        <v>784</v>
+        <v>296</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>356</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>470</v>
+        <v>297</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>81</v>
+        <v>313</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="J9" s="9"/>
+        <v>311</v>
+      </c>
+      <c r="J9" s="9" t="s">
+        <v>351</v>
+      </c>
       <c r="K9" s="9" t="s">
-        <v>84</v>
+        <v>310</v>
       </c>
       <c r="L9" s="13" t="s">
-        <v>101</v>
+        <v>66</v>
       </c>
       <c r="M9" s="13" t="s">
-        <v>102</v>
+        <v>314</v>
       </c>
       <c r="N9" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="O9" s="13"/>
+        <v>315</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>361</v>
+      </c>
       <c r="P9" s="13" t="s">
-        <v>104</v>
+        <v>316</v>
       </c>
       <c r="Q9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R9" s="10">
         <v>6.7000000000000002E-4</v>
@@ -2757,233 +2958,251 @@
       <c r="S9" s="16">
         <v>3.8999999999999999E-4</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T9" s="43">
+        <v>1.2800000000000001E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.25">
       <c r="R10" s="10"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
-        <v>1</v>
+        <v>362</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="3" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
-      <c r="L13" s="60" t="s">
+      <c r="L13" s="68" t="s">
+        <v>2</v>
+      </c>
+      <c r="M13" s="69"/>
+      <c r="N13" s="70"/>
+      <c r="O13" s="65" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" ht="60" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="M13" s="60"/>
-    </row>
-    <row r="14" spans="1:19" ht="60" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="B14" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B14" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
+        <v>282</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>455</v>
-      </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="H14" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H14" s="6" t="s">
+      <c r="I14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="J14" s="6" t="s">
+        <v>282</v>
+      </c>
+      <c r="K14" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="J14" s="6" t="s">
-        <v>455</v>
-      </c>
-      <c r="K14" s="6" t="s">
+      <c r="L14" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="M14" s="7" t="s">
+        <v>270</v>
+      </c>
+      <c r="N14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="M14" s="7" t="s">
-        <v>442</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="O14" s="59"/>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="O14" s="65" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
         <v>0</v>
       </c>
       <c r="B15" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="8" t="s">
         <v>16</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>17</v>
       </c>
       <c r="E15" s="8"/>
       <c r="F15" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="G15" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="9" t="s">
+      <c r="H15" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="H15" s="9" t="s">
+      <c r="I15" s="9" t="s">
         <v>20</v>
-      </c>
-      <c r="I15" s="9" t="s">
-        <v>21</v>
       </c>
       <c r="J15" s="9"/>
       <c r="K15" s="9" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L15" t="s">
+        <v>22</v>
+      </c>
+      <c r="M15" t="s">
+        <v>22</v>
+      </c>
+      <c r="N15" t="s">
+        <v>22</v>
+      </c>
+      <c r="O15" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M15" t="s">
-        <v>23</v>
-      </c>
-      <c r="N15" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B16" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="8" t="s">
+      <c r="C16" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="C16" s="8" t="s">
+      <c r="D16" s="8" t="s">
         <v>26</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>27</v>
       </c>
       <c r="E16" s="8"/>
       <c r="F16" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="9" t="s">
         <v>28</v>
       </c>
-      <c r="G16" s="9" t="s">
+      <c r="H16" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="H16" s="9" t="s">
+      <c r="I16" s="9" t="s">
         <v>30</v>
-      </c>
-      <c r="I16" s="9" t="s">
-        <v>31</v>
       </c>
       <c r="J16" s="9"/>
       <c r="K16" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="L16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M16" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N16" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="O16" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B17" s="8" t="s">
+      <c r="C17" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="C17" s="8" t="s">
+      <c r="D17" s="8" t="s">
         <v>35</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>36</v>
       </c>
       <c r="E17" s="8"/>
       <c r="F17" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="G17" s="9" t="s">
+      <c r="H17" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="H17" s="9" t="s">
+      <c r="I17" s="9" t="s">
         <v>39</v>
-      </c>
-      <c r="I17" s="9" t="s">
-        <v>40</v>
       </c>
       <c r="J17" s="9"/>
       <c r="K17" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="N17" t="s">
-        <v>23</v>
+        <v>22</v>
+      </c>
+      <c r="O17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="8" t="s">
+      <c r="C18" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="C18" s="8" t="s">
+      <c r="D18" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>45</v>
       </c>
       <c r="E18" s="8"/>
       <c r="F18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G18" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="H18" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="H18" s="9" t="s">
+      <c r="I18" s="9" t="s">
         <v>48</v>
-      </c>
-      <c r="I18" s="9" t="s">
-        <v>49</v>
       </c>
       <c r="J18" s="9"/>
       <c r="K18" s="9" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L18" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M18" s="10">
         <v>9.7999999999999997E-3</v>
@@ -2991,40 +3210,42 @@
       <c r="N18" s="10">
         <v>1.2710000000000001E-2</v>
       </c>
-      <c r="O18" s="10"/>
+      <c r="O18" s="10">
+        <v>6.0109999999999999E-3</v>
+      </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="C19" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="8" t="s">
+      <c r="D19" s="8" t="s">
         <v>53</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>54</v>
       </c>
       <c r="E19" s="8"/>
       <c r="F19" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="G19" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="H19" s="9" t="s">
         <v>56</v>
       </c>
-      <c r="H19" s="9" t="s">
+      <c r="I19" s="9" t="s">
         <v>57</v>
-      </c>
-      <c r="I19" s="9" t="s">
-        <v>58</v>
       </c>
       <c r="J19" s="9"/>
       <c r="K19" s="9" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L19" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M19" s="10">
         <v>4.2739999999999998E-8</v>
@@ -3032,17 +3253,19 @@
       <c r="N19" s="10">
         <v>1.7499999999999999E-7</v>
       </c>
-      <c r="O19" s="10"/>
+      <c r="O19" s="16">
+        <v>1.0099999999999999E-8</v>
+      </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="69"/>
-      <c r="B22" s="69"/>
-      <c r="C22" s="69"/>
+      <c r="A22" s="58"/>
+      <c r="B22" s="58"/>
+      <c r="C22" s="58"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="Q3:R3"/>
+    <mergeCell ref="Q3:S3"/>
+    <mergeCell ref="L13:N13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3051,401 +3274,454 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S10"/>
+  <dimension ref="A1:U10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="17" max="17" width="15.85546875" customWidth="1"/>
+    <col min="20" max="20" width="8.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" ht="18.75" x14ac:dyDescent="0.3">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A2" s="39"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="4" spans="1:19" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="25" t="s">
-        <v>136</v>
+        <v>368</v>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
       <c r="E4" s="25"/>
-      <c r="F4" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="N4" s="62" t="s">
-        <v>446</v>
-      </c>
-      <c r="O4" s="63"/>
-      <c r="P4" s="63"/>
-      <c r="Q4" s="64" t="s">
-        <v>443</v>
-      </c>
-      <c r="R4" s="64"/>
-    </row>
-    <row r="5" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+      <c r="F4" s="25"/>
+      <c r="G4" s="71" t="s">
+        <v>369</v>
+      </c>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
+      <c r="J4" s="72"/>
+      <c r="K4" s="73"/>
+      <c r="L4" s="74" t="s">
+        <v>370</v>
+      </c>
+      <c r="M4" s="75"/>
+      <c r="N4" s="75"/>
+      <c r="O4" s="75"/>
+      <c r="P4" s="76"/>
+      <c r="Q4" s="60" t="s">
+        <v>273</v>
+      </c>
+      <c r="R4" s="61"/>
+      <c r="S4" s="61"/>
+      <c r="T4" s="62" t="s">
+        <v>435</v>
+      </c>
+      <c r="U4" s="62"/>
+    </row>
+    <row r="5" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="B5" s="26" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="C5" s="26" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="D5" s="26" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>142</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>143</v>
+        <v>365</v>
+      </c>
+      <c r="F5" s="26" t="s">
+        <v>101</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="H5" s="5" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="I5" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="J5" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="J5" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="K5" s="5" t="s">
+        <v>105</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="O5" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="P5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="M5" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="N5" s="7" t="s">
+      <c r="Q5" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="R5" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="S5" s="44" t="s">
         <v>13</v>
       </c>
-      <c r="O5" s="44" t="s">
-        <v>448</v>
-      </c>
-      <c r="P5" s="44" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q5" s="45" t="s">
-        <v>444</v>
-      </c>
-      <c r="R5" s="45"/>
-      <c r="S5" s="45" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T5" s="45" t="s">
+        <v>436</v>
+      </c>
+      <c r="U5" s="45" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>0</v>
       </c>
       <c r="B6" s="27" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="C6" s="27" t="s">
-        <v>148</v>
+        <v>107</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>149</v>
+        <v>371</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>150</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>151</v>
+        <v>384</v>
+      </c>
+      <c r="F6" s="27" t="s">
+        <v>372</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>152</v>
+        <v>392</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>153</v>
+        <v>108</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>156</v>
+        <v>393</v>
+      </c>
+      <c r="J6" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="K6" s="8" t="s">
+        <v>394</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>157</v>
-      </c>
-      <c r="M6" s="47" t="s">
-        <v>158</v>
-      </c>
-      <c r="N6" s="17" t="s">
+        <v>389</v>
+      </c>
+      <c r="M6" s="9" t="s">
+        <v>109</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="O6" s="47" t="s">
+        <v>432</v>
+      </c>
+      <c r="P6" s="47" t="s">
+        <v>391</v>
+      </c>
+      <c r="Q6" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="R6" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="S6" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="T6" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="U6" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O6" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="P6" s="17">
-        <v>0.56299999999999994</v>
-      </c>
-      <c r="Q6" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="R6" s="17"/>
-      <c r="S6" s="17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="B7" s="27" t="s">
-        <v>159</v>
+        <v>110</v>
       </c>
       <c r="C7" s="27" t="s">
-        <v>160</v>
+        <v>111</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>161</v>
+        <v>373</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>162</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>163</v>
+        <v>385</v>
+      </c>
+      <c r="F7" s="27" t="s">
+        <v>374</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>164</v>
+        <v>414</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>165</v>
+        <v>415</v>
       </c>
       <c r="I7" s="8" t="s">
-        <v>166</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>168</v>
+        <v>416</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>417</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="M7" s="47" t="s">
-        <v>170</v>
-      </c>
-      <c r="N7" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="O7" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="P7" s="48">
-        <v>9.7699999999999995E-2</v>
+        <v>395</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="O7" s="47" t="s">
+        <v>433</v>
+      </c>
+      <c r="P7" s="47" t="s">
+        <v>398</v>
       </c>
       <c r="Q7" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="R7" s="17"/>
+        <v>22</v>
+      </c>
+      <c r="R7" s="17" t="s">
+        <v>22</v>
+      </c>
       <c r="S7" s="17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="T7" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="U7" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" s="27" t="s">
-        <v>171</v>
+        <v>112</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>172</v>
+        <v>375</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>173</v>
+        <v>376</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>174</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>175</v>
+        <v>386</v>
+      </c>
+      <c r="F8" s="27" t="s">
+        <v>377</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>176</v>
+        <v>404</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>177</v>
+        <v>413</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>178</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>179</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>180</v>
+        <v>412</v>
+      </c>
+      <c r="J8" s="8" t="s">
+        <v>427</v>
+      </c>
+      <c r="K8" s="8" t="s">
+        <v>411</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>181</v>
-      </c>
-      <c r="M8" s="47" t="s">
-        <v>182</v>
-      </c>
-      <c r="N8" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="O8" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="P8" s="1">
+        <v>399</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="O8" s="47" t="s">
+        <v>434</v>
+      </c>
+      <c r="P8" s="47" t="s">
+        <v>402</v>
+      </c>
+      <c r="Q8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="R8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="S8" s="1">
         <v>2.7050000000000001E-2</v>
       </c>
-      <c r="Q8" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="R8" s="17"/>
-      <c r="S8" s="46">
-        <v>2.2700000000000001E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="T8" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="U8" s="46">
+        <v>3.2199999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="27" t="s">
-        <v>183</v>
+        <v>113</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>184</v>
+        <v>378</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>185</v>
+        <v>379</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>186</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>187</v>
+        <v>387</v>
+      </c>
+      <c r="F9" s="27" t="s">
+        <v>380</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>188</v>
+        <v>403</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>189</v>
+        <v>408</v>
       </c>
       <c r="I9" s="8" t="s">
-        <v>190</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>191</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>192</v>
+        <v>409</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>428</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>410</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>193</v>
-      </c>
-      <c r="M9" s="47" t="s">
-        <v>194</v>
-      </c>
-      <c r="N9" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="O9" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="P9" s="17">
-        <v>0.93389999999999995</v>
+        <v>404</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>405</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>406</v>
+      </c>
+      <c r="O9" s="47" t="s">
+        <v>431</v>
+      </c>
+      <c r="P9" s="47" t="s">
+        <v>407</v>
       </c>
       <c r="Q9" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="R9" s="17"/>
+        <v>22</v>
+      </c>
+      <c r="R9" s="17" t="s">
+        <v>22</v>
+      </c>
       <c r="S9" s="17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="T9" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="U9" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="27" t="s">
-        <v>195</v>
+        <v>114</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>196</v>
+        <v>381</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>197</v>
+        <v>382</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>198</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>199</v>
+        <v>388</v>
+      </c>
+      <c r="F10" s="27" t="s">
+        <v>383</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>200</v>
+        <v>421</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>201</v>
+        <v>422</v>
       </c>
       <c r="I10" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>203</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>204</v>
+        <v>423</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>429</v>
+      </c>
+      <c r="K10" s="8" t="s">
+        <v>424</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>205</v>
+        <v>421</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>206</v>
-      </c>
-      <c r="N10" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="O10" s="49">
+        <v>418</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>420</v>
+      </c>
+      <c r="O10" s="9" t="s">
+        <v>430</v>
+      </c>
+      <c r="P10" s="9" t="s">
+        <v>419</v>
+      </c>
+      <c r="Q10" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="R10" s="48">
         <v>8.0000000000000002E-3</v>
       </c>
-      <c r="P10" s="19">
+      <c r="S10" s="19">
         <v>7.4660000000000004E-3</v>
       </c>
-      <c r="Q10" s="46">
-        <v>1.9300000000000001E-2</v>
-      </c>
-      <c r="R10" s="46"/>
-      <c r="S10" s="1">
-        <v>1.7299999999999999E-2</v>
+      <c r="T10" s="46">
+        <v>1.37E-2</v>
+      </c>
+      <c r="U10" s="1">
+        <v>1.2200000000000001E-2</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="Q4:R4"/>
+  <mergeCells count="4">
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="G4:K4"/>
+    <mergeCell ref="L4:P4"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3453,811 +3729,874 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:U36"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="6" max="6" width="14" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:21" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="28" t="s">
-        <v>208</v>
+        <v>437</v>
       </c>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
-      <c r="F4" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="G4" s="29"/>
+      <c r="F4" s="28"/>
+      <c r="G4" s="29" t="s">
+        <v>438</v>
+      </c>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
-      <c r="J4" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
+      <c r="J4" s="29"/>
+      <c r="K4" s="29"/>
+      <c r="L4" s="3" t="s">
+        <v>439</v>
+      </c>
       <c r="M4" s="3"/>
-      <c r="N4" s="61" t="s">
-        <v>3</v>
-      </c>
-      <c r="O4" s="61"/>
-      <c r="P4" s="61"/>
-      <c r="Q4" s="64" t="s">
-        <v>447</v>
-      </c>
-      <c r="R4" s="64"/>
-    </row>
-    <row r="5" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="N4" s="3"/>
+      <c r="O4" s="3"/>
+      <c r="P4" s="3"/>
+      <c r="Q4" s="59" t="s">
+        <v>2</v>
+      </c>
+      <c r="R4" s="59"/>
+      <c r="S4" s="59"/>
+      <c r="T4" s="62" t="s">
+        <v>274</v>
+      </c>
+      <c r="U4" s="62"/>
+    </row>
+    <row r="5" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="C5" s="30" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="D5" s="30" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>211</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>143</v>
+        <v>365</v>
+      </c>
+      <c r="F5" s="30" t="s">
+        <v>116</v>
       </c>
       <c r="G5" s="31" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="H5" s="31" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="I5" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="J5" s="6" t="s">
+        <v>104</v>
+      </c>
+      <c r="J5" s="31" t="s">
+        <v>365</v>
+      </c>
+      <c r="K5" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M5" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="O5" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="P5" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="M5" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="N5" s="15" t="s">
+      <c r="Q5" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="R5" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="S5" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="O5" s="15" t="s">
-        <v>448</v>
-      </c>
-      <c r="P5" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q5" s="45" t="s">
-        <v>444</v>
-      </c>
-      <c r="R5" s="45" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="T5" s="45" t="s">
+        <v>271</v>
+      </c>
+      <c r="U5" s="45" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>0</v>
       </c>
       <c r="B6" s="32" t="s">
-        <v>213</v>
+        <v>118</v>
       </c>
       <c r="C6" s="32" t="s">
-        <v>214</v>
+        <v>119</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>215</v>
-      </c>
-      <c r="E6" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="F6" s="33" t="s">
-        <v>217</v>
+        <v>443</v>
+      </c>
+      <c r="E6" s="32"/>
+      <c r="F6" s="32" t="s">
+        <v>444</v>
       </c>
       <c r="G6" s="33" t="s">
-        <v>218</v>
+        <v>120</v>
       </c>
       <c r="H6" s="33" t="s">
-        <v>219</v>
+        <v>121</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>220</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>221</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>222</v>
+        <v>473</v>
+      </c>
+      <c r="J6" s="33"/>
+      <c r="K6" s="33" t="s">
+        <v>474</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>223</v>
+        <v>470</v>
       </c>
       <c r="M6" s="9" t="s">
-        <v>224</v>
-      </c>
-      <c r="N6" t="s">
+        <v>122</v>
+      </c>
+      <c r="N6" s="9" t="s">
+        <v>471</v>
+      </c>
+      <c r="O6" s="9"/>
+      <c r="P6" s="9" t="s">
+        <v>472</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>22</v>
+      </c>
+      <c r="R6" t="s">
+        <v>22</v>
+      </c>
+      <c r="S6" t="s">
+        <v>22</v>
+      </c>
+      <c r="T6" t="s">
+        <v>22</v>
+      </c>
+      <c r="U6" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O6" t="s">
-        <v>23</v>
-      </c>
-      <c r="P6" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>23</v>
-      </c>
-      <c r="R6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="B7" s="32" t="s">
-        <v>225</v>
+        <v>123</v>
       </c>
       <c r="C7" s="32" t="s">
-        <v>226</v>
+        <v>124</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="E7" s="32" t="s">
-        <v>228</v>
-      </c>
-      <c r="F7" s="33" t="s">
-        <v>229</v>
+        <v>445</v>
+      </c>
+      <c r="E7" s="32"/>
+      <c r="F7" s="32" t="s">
+        <v>446</v>
       </c>
       <c r="G7" s="33" t="s">
-        <v>230</v>
+        <v>477</v>
       </c>
       <c r="H7" s="33" t="s">
-        <v>231</v>
+        <v>478</v>
       </c>
       <c r="I7" s="33" t="s">
-        <v>232</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>233</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>234</v>
+        <v>479</v>
+      </c>
+      <c r="J7" s="33"/>
+      <c r="K7" s="33" t="s">
+        <v>480</v>
       </c>
       <c r="L7" s="9" t="s">
-        <v>235</v>
+        <v>125</v>
       </c>
       <c r="M7" s="9" t="s">
-        <v>236</v>
-      </c>
-      <c r="N7" t="s">
-        <v>23</v>
-      </c>
-      <c r="O7" t="s">
-        <v>23</v>
-      </c>
-      <c r="P7" t="s">
-        <v>23</v>
+        <v>126</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>475</v>
+      </c>
+      <c r="O7" s="9"/>
+      <c r="P7" s="9" t="s">
+        <v>476</v>
       </c>
       <c r="Q7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R7" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S7" t="s">
+        <v>22</v>
+      </c>
+      <c r="T7" t="s">
+        <v>22</v>
+      </c>
+      <c r="U7" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B8" s="32" t="s">
-        <v>237</v>
+        <v>127</v>
       </c>
       <c r="C8" s="32" t="s">
-        <v>238</v>
+        <v>128</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>239</v>
-      </c>
-      <c r="E8" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="F8" s="33" t="s">
-        <v>241</v>
+        <v>447</v>
+      </c>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32" t="s">
+        <v>448</v>
       </c>
       <c r="G8" s="33" t="s">
-        <v>242</v>
+        <v>129</v>
       </c>
       <c r="H8" s="33" t="s">
-        <v>243</v>
+        <v>130</v>
       </c>
       <c r="I8" s="33" t="s">
-        <v>244</v>
-      </c>
-      <c r="J8" s="9" t="s">
-        <v>245</v>
-      </c>
-      <c r="K8" s="9" t="s">
-        <v>246</v>
+        <v>483</v>
+      </c>
+      <c r="J8" s="33"/>
+      <c r="K8" s="33" t="s">
+        <v>473</v>
       </c>
       <c r="L8" s="9" t="s">
-        <v>247</v>
+        <v>131</v>
       </c>
       <c r="M8" s="9" t="s">
-        <v>248</v>
-      </c>
-      <c r="N8" t="s">
-        <v>23</v>
-      </c>
-      <c r="O8" t="s">
-        <v>23</v>
-      </c>
-      <c r="P8" s="34">
+        <v>132</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>481</v>
+      </c>
+      <c r="O8" s="9"/>
+      <c r="P8" s="9" t="s">
+        <v>482</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>22</v>
+      </c>
+      <c r="R8" t="s">
+        <v>22</v>
+      </c>
+      <c r="S8" s="34">
         <v>5.0900000000000001E-2</v>
       </c>
-      <c r="Q8" t="s">
-        <v>23</v>
-      </c>
-      <c r="R8" s="34">
+      <c r="T8" t="s">
+        <v>22</v>
+      </c>
+      <c r="U8" s="34">
         <v>5.79E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>249</v>
+        <v>450</v>
       </c>
       <c r="C9" s="32" t="s">
-        <v>250</v>
+        <v>449</v>
       </c>
       <c r="D9" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="E9" s="32" t="s">
-        <v>252</v>
-      </c>
-      <c r="F9" s="33" t="s">
-        <v>253</v>
+        <v>451</v>
+      </c>
+      <c r="E9" s="32"/>
+      <c r="F9" s="32" t="s">
+        <v>452</v>
       </c>
       <c r="G9" s="33" t="s">
-        <v>254</v>
+        <v>133</v>
       </c>
       <c r="H9" s="33" t="s">
-        <v>255</v>
+        <v>485</v>
       </c>
       <c r="I9" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="J9" s="9" t="s">
-        <v>257</v>
-      </c>
-      <c r="K9" s="9" t="s">
-        <v>258</v>
+        <v>486</v>
+      </c>
+      <c r="J9" s="33"/>
+      <c r="K9" s="33" t="s">
+        <v>487</v>
       </c>
       <c r="L9" s="9" t="s">
-        <v>259</v>
+        <v>134</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>260</v>
-      </c>
-      <c r="N9" t="s">
-        <v>23</v>
-      </c>
-      <c r="O9" t="s">
-        <v>23</v>
-      </c>
-      <c r="P9" t="s">
-        <v>23</v>
+        <v>484</v>
+      </c>
+      <c r="N9" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="O9" s="9"/>
+      <c r="P9" s="9" t="s">
+        <v>136</v>
       </c>
       <c r="Q9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="R9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="S9" t="s">
+        <v>22</v>
+      </c>
+      <c r="T9" t="s">
+        <v>22</v>
+      </c>
+      <c r="U9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="32" t="s">
-        <v>261</v>
+        <v>137</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>262</v>
+        <v>453</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="E10" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="F10" s="33" t="s">
-        <v>265</v>
+        <v>454</v>
+      </c>
+      <c r="E10" s="32"/>
+      <c r="F10" s="32" t="s">
+        <v>455</v>
       </c>
       <c r="G10" s="33" t="s">
-        <v>266</v>
+        <v>138</v>
       </c>
       <c r="H10" s="33" t="s">
-        <v>267</v>
+        <v>489</v>
       </c>
       <c r="I10" s="33" t="s">
-        <v>268</v>
-      </c>
-      <c r="J10" s="9" t="s">
-        <v>269</v>
-      </c>
-      <c r="K10" s="9" t="s">
-        <v>270</v>
+        <v>490</v>
+      </c>
+      <c r="J10" s="33"/>
+      <c r="K10" s="33" t="s">
+        <v>491</v>
       </c>
       <c r="L10" s="9" t="s">
-        <v>271</v>
+        <v>139</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>272</v>
-      </c>
-      <c r="N10" t="s">
-        <v>23</v>
-      </c>
-      <c r="O10" s="52">
+        <v>488</v>
+      </c>
+      <c r="N10" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="O10" s="9"/>
+      <c r="P10" s="9" t="s">
+        <v>141</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>22</v>
+      </c>
+      <c r="R10" s="51">
         <v>9.8000000000000004E-2</v>
       </c>
-      <c r="P10" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>23</v>
-      </c>
-      <c r="R10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="S10" s="35" t="s">
+        <v>22</v>
+      </c>
+      <c r="T10" t="s">
+        <v>22</v>
+      </c>
+      <c r="U10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A13" s="10" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="36" t="s">
-        <v>274</v>
+        <v>440</v>
       </c>
       <c r="C14" s="36"/>
       <c r="D14" s="36"/>
       <c r="E14" s="36"/>
-      <c r="F14" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="G14" s="2"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="2" t="s">
+        <v>441</v>
+      </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
-      <c r="J14" s="11" t="s">
-        <v>276</v>
-      </c>
-      <c r="K14" s="11"/>
-      <c r="L14" s="11"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="11" t="s">
+        <v>442</v>
+      </c>
       <c r="M14" s="11"/>
-      <c r="N14" s="61" t="s">
-        <v>3</v>
-      </c>
-      <c r="O14" s="61"/>
-      <c r="P14" s="61"/>
-      <c r="Q14" s="64" t="s">
-        <v>447</v>
-      </c>
-      <c r="R14" s="64"/>
-    </row>
-    <row r="15" spans="1:18" ht="60" x14ac:dyDescent="0.25">
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="59" t="s">
+        <v>2</v>
+      </c>
+      <c r="R14" s="59"/>
+      <c r="S14" s="59"/>
+      <c r="T14" s="62" t="s">
+        <v>274</v>
+      </c>
+      <c r="U14" s="62"/>
+    </row>
+    <row r="15" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>138</v>
+        <v>97</v>
       </c>
       <c r="B15" s="37" t="s">
-        <v>139</v>
+        <v>98</v>
       </c>
       <c r="C15" s="37" t="s">
-        <v>140</v>
+        <v>99</v>
       </c>
       <c r="D15" s="37" t="s">
-        <v>141</v>
+        <v>100</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>211</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>143</v>
+        <v>365</v>
+      </c>
+      <c r="F15" s="37" t="s">
+        <v>116</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>144</v>
+        <v>102</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>145</v>
+        <v>103</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>212</v>
-      </c>
-      <c r="J15" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="J15" s="5" t="s">
+        <v>365</v>
+      </c>
+      <c r="K15" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="L15" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15" s="12" t="s">
         <v>60</v>
       </c>
-      <c r="K15" s="12" t="s">
+      <c r="N15" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="L15" s="12" t="s">
+      <c r="O15" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="P15" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="M15" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="N15" s="15" t="s">
+      <c r="Q15" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="R15" s="15" t="s">
+        <v>275</v>
+      </c>
+      <c r="S15" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="O15" s="15" t="s">
-        <v>448</v>
-      </c>
-      <c r="P15" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="Q15" s="45" t="s">
-        <v>444</v>
-      </c>
-      <c r="R15" s="45" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="T15" s="45" t="s">
+        <v>271</v>
+      </c>
+      <c r="U15" s="45" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A16" s="1">
         <v>0</v>
       </c>
       <c r="B16" s="38" t="s">
-        <v>277</v>
+        <v>143</v>
       </c>
       <c r="C16" s="38" t="s">
-        <v>278</v>
+        <v>144</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>279</v>
-      </c>
-      <c r="E16" s="38" t="s">
-        <v>280</v>
-      </c>
-      <c r="F16" s="8" t="s">
-        <v>281</v>
+        <v>456</v>
+      </c>
+      <c r="E16" s="38"/>
+      <c r="F16" s="38" t="s">
+        <v>457</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>282</v>
+        <v>145</v>
       </c>
       <c r="H16" s="8" t="s">
-        <v>283</v>
+        <v>146</v>
       </c>
       <c r="I16" s="8" t="s">
-        <v>284</v>
-      </c>
-      <c r="J16" s="13" t="s">
-        <v>285</v>
-      </c>
-      <c r="K16" s="13" t="s">
-        <v>286</v>
+        <v>513</v>
+      </c>
+      <c r="J16" s="8"/>
+      <c r="K16" s="8" t="s">
+        <v>512</v>
       </c>
       <c r="L16" s="13" t="s">
-        <v>287</v>
+        <v>516</v>
       </c>
       <c r="M16" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="N16" s="50" t="s">
+        <v>147</v>
+      </c>
+      <c r="N16" s="13" t="s">
+        <v>515</v>
+      </c>
+      <c r="O16" s="13"/>
+      <c r="P16" s="13" t="s">
+        <v>514</v>
+      </c>
+      <c r="Q16" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="R16" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="S16" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="T16" t="s">
+        <v>22</v>
+      </c>
+      <c r="U16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="O16" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="P16" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>23</v>
-      </c>
-      <c r="R16" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>24</v>
-      </c>
       <c r="B17" s="38" t="s">
-        <v>289</v>
+        <v>148</v>
       </c>
       <c r="C17" s="38" t="s">
-        <v>290</v>
+        <v>149</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>291</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>292</v>
-      </c>
-      <c r="F17" s="8" t="s">
-        <v>293</v>
+        <v>458</v>
+      </c>
+      <c r="E17" s="38"/>
+      <c r="F17" s="38" t="s">
+        <v>459</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>294</v>
+        <v>150</v>
       </c>
       <c r="H17" s="8" t="s">
-        <v>295</v>
+        <v>151</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>296</v>
-      </c>
-      <c r="J17" s="13" t="s">
-        <v>297</v>
-      </c>
-      <c r="K17" s="13" t="s">
-        <v>298</v>
+        <v>509</v>
+      </c>
+      <c r="J17" s="8"/>
+      <c r="K17" s="8" t="s">
+        <v>508</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>299</v>
+        <v>152</v>
       </c>
       <c r="M17" s="13" t="s">
-        <v>300</v>
-      </c>
-      <c r="N17" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="O17" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="P17" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q17" t="s">
-        <v>23</v>
-      </c>
-      <c r="R17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+      <c r="N17" s="13" t="s">
+        <v>511</v>
+      </c>
+      <c r="O17" s="13"/>
+      <c r="P17" s="13" t="s">
+        <v>510</v>
+      </c>
+      <c r="Q17" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="R17" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="S17" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="T17" t="s">
+        <v>22</v>
+      </c>
+      <c r="U17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B18" s="38" t="s">
-        <v>301</v>
+        <v>154</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>302</v>
+        <v>460</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>303</v>
-      </c>
-      <c r="E18" s="38" t="s">
-        <v>279</v>
-      </c>
-      <c r="F18" s="8" t="s">
-        <v>304</v>
+        <v>461</v>
+      </c>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38" t="s">
+        <v>462</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>305</v>
+        <v>155</v>
       </c>
       <c r="H18" s="8" t="s">
-        <v>306</v>
+        <v>156</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>307</v>
-      </c>
-      <c r="J18" s="13" t="s">
-        <v>308</v>
-      </c>
-      <c r="K18" s="13" t="s">
-        <v>308</v>
+        <v>503</v>
+      </c>
+      <c r="J18" s="8"/>
+      <c r="K18" s="8" t="s">
+        <v>502</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>309</v>
+        <v>507</v>
       </c>
       <c r="M18" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="N18" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="O18" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="P18" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q18" t="s">
-        <v>23</v>
-      </c>
-      <c r="R18" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="19" spans="1:18" x14ac:dyDescent="0.25">
+        <v>506</v>
+      </c>
+      <c r="N18" s="13" t="s">
+        <v>505</v>
+      </c>
+      <c r="O18" s="13"/>
+      <c r="P18" s="13" t="s">
+        <v>504</v>
+      </c>
+      <c r="Q18" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="R18" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="S18" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="T18" t="s">
+        <v>22</v>
+      </c>
+      <c r="U18" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B19" s="38" t="s">
-        <v>311</v>
+        <v>463</v>
       </c>
       <c r="C19" s="38" t="s">
-        <v>312</v>
+        <v>464</v>
       </c>
       <c r="D19" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="E19" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>315</v>
+        <v>465</v>
+      </c>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38" t="s">
+        <v>466</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>316</v>
+        <v>157</v>
       </c>
       <c r="H19" s="8" t="s">
-        <v>317</v>
+        <v>158</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>318</v>
-      </c>
-      <c r="J19" s="13" t="s">
-        <v>319</v>
-      </c>
-      <c r="K19" s="13" t="s">
-        <v>320</v>
+        <v>498</v>
+      </c>
+      <c r="J19" s="8"/>
+      <c r="K19" s="8" t="s">
+        <v>497</v>
       </c>
       <c r="L19" s="13" t="s">
-        <v>321</v>
+        <v>159</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>322</v>
-      </c>
-      <c r="N19" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="O19" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="P19" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q19" t="s">
-        <v>23</v>
-      </c>
-      <c r="R19" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.25">
+        <v>501</v>
+      </c>
+      <c r="N19" s="13" t="s">
+        <v>500</v>
+      </c>
+      <c r="O19" s="13"/>
+      <c r="P19" s="13" t="s">
+        <v>499</v>
+      </c>
+      <c r="Q19" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="R19" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="S19" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="T19" t="s">
+        <v>22</v>
+      </c>
+      <c r="U19" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B20" s="38" t="s">
-        <v>323</v>
+        <v>160</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>324</v>
+        <v>469</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>325</v>
-      </c>
-      <c r="E20" s="38" t="s">
-        <v>326</v>
-      </c>
-      <c r="F20" s="8" t="s">
-        <v>327</v>
+        <v>468</v>
+      </c>
+      <c r="E20" s="38"/>
+      <c r="F20" s="38" t="s">
+        <v>467</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>328</v>
+        <v>161</v>
       </c>
       <c r="H20" s="8" t="s">
-        <v>329</v>
+        <v>162</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>330</v>
-      </c>
-      <c r="J20" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="K20" s="13" t="s">
-        <v>332</v>
+        <v>493</v>
+      </c>
+      <c r="J20" s="8"/>
+      <c r="K20" s="8" t="s">
+        <v>492</v>
       </c>
       <c r="L20" s="13" t="s">
-        <v>333</v>
+        <v>496</v>
       </c>
       <c r="M20" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="N20" s="50" t="s">
-        <v>23</v>
-      </c>
-      <c r="O20" s="51">
+        <v>495</v>
+      </c>
+      <c r="N20" s="13" t="s">
+        <v>495</v>
+      </c>
+      <c r="O20" s="13"/>
+      <c r="P20" s="13" t="s">
+        <v>494</v>
+      </c>
+      <c r="Q20" s="49" t="s">
+        <v>22</v>
+      </c>
+      <c r="R20" s="50">
         <v>3.39E-2</v>
       </c>
-      <c r="P20" s="51">
+      <c r="S20" s="50">
         <v>3.1E-2</v>
       </c>
-      <c r="Q20" s="43">
+      <c r="T20" s="43">
         <v>4.0099999999999997E-2</v>
       </c>
-      <c r="R20" s="43">
+      <c r="U20" s="43">
         <v>3.5000000000000003E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="N21" s="14"/>
-      <c r="O21" s="14"/>
-      <c r="P21" s="14"/>
-    </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="B22" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="F22" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="J22" s="67" t="s">
-        <v>3</v>
-      </c>
-      <c r="K22" s="68"/>
-      <c r="L22" s="68"/>
-      <c r="N22" s="14"/>
-      <c r="O22" s="14"/>
-      <c r="P22" s="14"/>
-    </row>
-    <row r="23" spans="1:18" ht="45" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="Q21" s="14"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="B22" s="84" t="s">
+        <v>2</v>
+      </c>
+      <c r="C22" s="84"/>
+      <c r="D22" s="84"/>
+      <c r="E22" s="77"/>
+      <c r="G22" s="84" t="s">
+        <v>2</v>
+      </c>
+      <c r="H22" s="84"/>
+      <c r="I22" s="84"/>
+      <c r="J22" s="77"/>
+      <c r="L22" s="84" t="s">
+        <v>2</v>
+      </c>
+      <c r="M22" s="84"/>
+      <c r="N22" s="84"/>
+      <c r="O22" s="77"/>
+      <c r="Q22" s="14"/>
+      <c r="R22" s="14"/>
+      <c r="S22" s="14"/>
+    </row>
+    <row r="23" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="D23" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="C23" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="D23" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="F23" s="15" t="s">
+      <c r="E23" s="78"/>
+      <c r="G23" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="H23" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="I23" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="H23" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="J23" s="15" t="s">
+      <c r="J23" s="78"/>
+      <c r="L23" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="M23" s="15" t="s">
+        <v>270</v>
+      </c>
+      <c r="N23" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="K23" s="15" t="s">
-        <v>442</v>
-      </c>
-      <c r="L23" s="15" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O23" s="78"/>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
         <v>0</v>
       </c>
@@ -4265,379 +4604,398 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="C24" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" s="79"/>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
+      <c r="G24" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H24" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J24" s="79"/>
+      <c r="K24" s="1">
+        <v>0</v>
+      </c>
+      <c r="L24" s="52">
+        <v>4.9439999999999998E-2</v>
+      </c>
+      <c r="M24" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N24" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="O24" s="79"/>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D24" s="17" t="s">
+      <c r="B25" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="E25" s="79"/>
+      <c r="F25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E24" s="1">
-        <v>0</v>
-      </c>
-      <c r="F24" s="17" t="s">
+      <c r="G25" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H25" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="79"/>
+      <c r="K25" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G24" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I24" s="1">
-        <v>0</v>
-      </c>
-      <c r="J24" s="53">
-        <v>4.9439999999999998E-2</v>
-      </c>
-      <c r="K24" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="L24" s="17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B25" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F25" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G25" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J25" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="K25" s="17" t="s">
-        <v>23</v>
-      </c>
       <c r="L25" s="17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.25">
+        <v>22</v>
+      </c>
+      <c r="M25" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="N25" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="O25" s="79"/>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="54">
+        <v>22</v>
+      </c>
+      <c r="C26" s="53">
         <v>9.5790000000000007E-3</v>
       </c>
-      <c r="D26" s="55">
+      <c r="D26" s="54">
         <v>1.9769999999999999E-2</v>
       </c>
-      <c r="E26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F26" s="17" t="s">
-        <v>23</v>
+      <c r="E26" s="82"/>
+      <c r="F26" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H26" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J26" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="K26" s="21">
+        <v>22</v>
+      </c>
+      <c r="I26" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="79"/>
+      <c r="K26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M26" s="21">
         <v>2.1819999999999999E-2</v>
       </c>
-      <c r="L26" s="56">
+      <c r="N26" s="55">
         <v>5.5E-2</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O26" s="80"/>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C27" s="54">
+        <v>22</v>
+      </c>
+      <c r="C27" s="53">
         <v>2.3990000000000001E-3</v>
       </c>
       <c r="D27" s="19">
         <v>5.0610000000000004E-3</v>
       </c>
-      <c r="E27" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F27" s="17" t="s">
-        <v>23</v>
+      <c r="E27" s="83"/>
+      <c r="F27" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G27" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H27" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J27" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="K27" s="21">
+        <v>22</v>
+      </c>
+      <c r="I27" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J27" s="79"/>
+      <c r="K27" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L27" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M27" s="21">
         <v>1.0939999999999999E-3</v>
       </c>
-      <c r="L27" s="21">
+      <c r="N27" s="21">
         <v>1.596E-3</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O27" s="81"/>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C28" s="54">
+        <v>22</v>
+      </c>
+      <c r="C28" s="53">
         <v>5.6470000000000001E-3</v>
       </c>
       <c r="D28" s="19">
         <v>7.9810000000000002E-3</v>
       </c>
-      <c r="E28" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F28" s="17" t="s">
-        <v>23</v>
+      <c r="E28" s="83"/>
+      <c r="F28" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="G28" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H28" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J28" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="K28" s="21">
+        <v>22</v>
+      </c>
+      <c r="I28" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J28" s="79"/>
+      <c r="K28" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L28" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M28" s="21">
         <v>1.7299999999999999E-2</v>
       </c>
-      <c r="L28" s="21">
+      <c r="N28" s="21">
         <v>2.1000000000000001E-2</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="65" t="s">
-        <v>452</v>
-      </c>
-      <c r="C30" s="66"/>
-      <c r="F30" s="65" t="s">
-        <v>449</v>
-      </c>
-      <c r="G30" s="66"/>
-      <c r="J30" s="65" t="s">
-        <v>449</v>
-      </c>
-      <c r="K30" s="66"/>
-    </row>
-    <row r="31" spans="1:18" ht="75" x14ac:dyDescent="0.25">
+      <c r="O28" s="81"/>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="E29" s="79"/>
+    </row>
+    <row r="30" spans="1:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="63" t="s">
+        <v>279</v>
+      </c>
+      <c r="C30" s="64"/>
+      <c r="E30" s="79"/>
+      <c r="G30" s="63" t="s">
+        <v>276</v>
+      </c>
+      <c r="H30" s="64"/>
+      <c r="L30" s="63" t="s">
+        <v>276</v>
+      </c>
+      <c r="M30" s="64"/>
+    </row>
+    <row r="31" spans="1:21" ht="75" x14ac:dyDescent="0.25">
       <c r="B31" s="45" t="s">
-        <v>453</v>
+        <v>280</v>
       </c>
       <c r="C31" s="45" t="s">
-        <v>454</v>
-      </c>
-      <c r="F31" s="45" t="s">
-        <v>453</v>
+        <v>281</v>
       </c>
       <c r="G31" s="45" t="s">
-        <v>454</v>
-      </c>
-      <c r="J31" s="45" t="s">
-        <v>453</v>
-      </c>
-      <c r="K31" s="45" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.25">
+        <v>280</v>
+      </c>
+      <c r="H31" s="45" t="s">
+        <v>281</v>
+      </c>
+      <c r="L31" s="45" t="s">
+        <v>280</v>
+      </c>
+      <c r="M31" s="45" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="1">
         <v>0</v>
       </c>
       <c r="B32" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C32" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H32" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K32" s="1">
+        <v>0</v>
+      </c>
+      <c r="L32" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M32" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C32" s="17" t="s">
+      <c r="B33" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="C33" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="F33" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E32" s="1">
-        <v>0</v>
-      </c>
-      <c r="F32" s="17" t="s">
+      <c r="G33" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="H33" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="G32" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I32" s="1">
-        <v>0</v>
-      </c>
-      <c r="J32" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="K32" s="17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B33" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="C33" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="F33" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="G33" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="J33" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="K33" s="17" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="L33" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="M33" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="B34" s="54">
+        <v>32</v>
+      </c>
+      <c r="B34" s="53">
         <v>9.75E-3</v>
       </c>
-      <c r="C34" s="54">
+      <c r="C34" s="53">
         <v>1.9400000000000001E-2</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F34" s="17" t="s">
-        <v>23</v>
+      <c r="F34" s="1" t="s">
+        <v>32</v>
       </c>
       <c r="G34" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="J34" s="46">
+        <v>22</v>
+      </c>
+      <c r="H34" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L34" s="46">
         <v>2.4E-2</v>
       </c>
-      <c r="K34" s="58">
+      <c r="M34" s="57">
         <v>6.2399999999999997E-2</v>
       </c>
     </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B35" s="54">
+        <v>41</v>
+      </c>
+      <c r="B35" s="53">
         <v>3.2100000000000002E-3</v>
       </c>
-      <c r="C35" s="54">
+      <c r="C35" s="53">
         <v>6.6E-3</v>
       </c>
-      <c r="E35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F35" s="17" t="s">
-        <v>23</v>
+      <c r="F35" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="G35" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J35" s="46">
+        <v>22</v>
+      </c>
+      <c r="H35" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K35" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="L35" s="46">
         <v>1.42E-3</v>
       </c>
-      <c r="K35" s="46">
+      <c r="M35" s="46">
         <v>2.1299999999999999E-3</v>
       </c>
     </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B36" s="54">
+        <v>50</v>
+      </c>
+      <c r="B36" s="53">
         <v>5.64E-3</v>
       </c>
-      <c r="C36" s="54">
+      <c r="C36" s="53">
         <v>8.0099999999999998E-3</v>
       </c>
-      <c r="E36" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="F36" s="17" t="s">
-        <v>23</v>
+      <c r="F36" s="1" t="s">
+        <v>50</v>
       </c>
       <c r="G36" s="17" t="s">
-        <v>23</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J36" s="46">
+        <v>22</v>
+      </c>
+      <c r="H36" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="L36" s="46">
         <v>1.2999999999999999E-2</v>
       </c>
-      <c r="K36" s="46">
+      <c r="M36" s="46">
         <v>1.5900000000000001E-2</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="L30:M30"/>
+    <mergeCell ref="G30:H30"/>
     <mergeCell ref="B30:C30"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="T4:U4"/>
+    <mergeCell ref="T14:U14"/>
     <mergeCell ref="B22:D22"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="J22:L22"/>
-    <mergeCell ref="N4:P4"/>
-    <mergeCell ref="N14:P14"/>
+    <mergeCell ref="G22:I22"/>
+    <mergeCell ref="L22:N22"/>
+    <mergeCell ref="Q4:S4"/>
+    <mergeCell ref="Q14:S14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4659,7 +5017,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
-        <v>441</v>
+        <v>269</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
@@ -4668,28 +5026,28 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>339</v>
+        <v>167</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>340</v>
+        <v>168</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>341</v>
+        <v>169</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>342</v>
+        <v>170</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>343</v>
+        <v>171</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G3" s="57" t="s">
-        <v>450</v>
-      </c>
-      <c r="H3" s="57" t="s">
-        <v>451</v>
+        <v>116</v>
+      </c>
+      <c r="G3" s="56" t="s">
+        <v>277</v>
+      </c>
+      <c r="H3" s="56" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -4697,71 +5055,71 @@
         <v>0</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>344</v>
+        <v>172</v>
       </c>
       <c r="C4" s="42" t="s">
-        <v>345</v>
+        <v>173</v>
       </c>
       <c r="D4" s="42" t="s">
-        <v>346</v>
+        <v>174</v>
       </c>
       <c r="E4" s="42" t="s">
-        <v>347</v>
+        <v>175</v>
       </c>
       <c r="F4" s="42" t="s">
-        <v>348</v>
+        <v>176</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B5" s="17" t="s">
-        <v>349</v>
+        <v>177</v>
       </c>
       <c r="C5" s="42" t="s">
-        <v>350</v>
+        <v>178</v>
       </c>
       <c r="D5" s="42" t="s">
-        <v>351</v>
+        <v>179</v>
       </c>
       <c r="E5" s="42" t="s">
-        <v>352</v>
+        <v>180</v>
       </c>
       <c r="F5" s="42" t="s">
-        <v>353</v>
+        <v>181</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H5" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B6" s="17" t="s">
-        <v>354</v>
+        <v>182</v>
       </c>
       <c r="C6" s="42" t="s">
-        <v>355</v>
+        <v>183</v>
       </c>
       <c r="D6" s="42" t="s">
-        <v>356</v>
+        <v>184</v>
       </c>
       <c r="E6" s="42" t="s">
-        <v>357</v>
+        <v>185</v>
       </c>
       <c r="F6" s="42" t="s">
-        <v>358</v>
+        <v>186</v>
       </c>
       <c r="G6" s="1">
         <v>3.5799999999999998E-2</v>
@@ -4772,22 +5130,22 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B7" s="17" t="s">
-        <v>359</v>
+        <v>187</v>
       </c>
       <c r="C7" s="42" t="s">
-        <v>360</v>
+        <v>188</v>
       </c>
       <c r="D7" s="42" t="s">
-        <v>361</v>
+        <v>189</v>
       </c>
       <c r="E7" s="42" t="s">
-        <v>362</v>
+        <v>190</v>
       </c>
       <c r="F7" s="42" t="s">
-        <v>363</v>
+        <v>191</v>
       </c>
       <c r="G7" s="4">
         <v>2.4500000000000001E-2</v>
@@ -4798,22 +5156,22 @@
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="17" t="s">
-        <v>364</v>
+        <v>192</v>
       </c>
       <c r="C8" s="42" t="s">
-        <v>365</v>
+        <v>193</v>
       </c>
       <c r="D8" s="42" t="s">
-        <v>366</v>
+        <v>194</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>367</v>
+        <v>195</v>
       </c>
       <c r="F8" s="42" t="s">
-        <v>368</v>
+        <v>196</v>
       </c>
       <c r="G8" s="4">
         <v>4.1700000000000001E-3</v>
@@ -4824,28 +5182,28 @@
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>369</v>
+        <v>197</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>340</v>
+        <v>168</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>341</v>
+        <v>169</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>342</v>
+        <v>170</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>343</v>
+        <v>171</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G10" s="57" t="s">
-        <v>450</v>
-      </c>
-      <c r="H10" s="57" t="s">
-        <v>451</v>
+        <v>116</v>
+      </c>
+      <c r="G10" s="56" t="s">
+        <v>277</v>
+      </c>
+      <c r="H10" s="56" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -4853,123 +5211,123 @@
         <v>0</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>370</v>
+        <v>198</v>
       </c>
       <c r="C11" s="17" t="s">
-        <v>371</v>
+        <v>199</v>
       </c>
       <c r="D11" s="17" t="s">
-        <v>372</v>
+        <v>200</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>373</v>
+        <v>201</v>
       </c>
       <c r="F11" s="42" t="s">
-        <v>374</v>
+        <v>202</v>
       </c>
       <c r="G11" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H11" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B12" s="17" t="s">
-        <v>375</v>
+        <v>203</v>
       </c>
       <c r="C12" s="42" t="s">
-        <v>376</v>
+        <v>204</v>
       </c>
       <c r="D12" s="17" t="s">
-        <v>377</v>
+        <v>205</v>
       </c>
       <c r="E12" s="17" t="s">
-        <v>378</v>
+        <v>206</v>
       </c>
       <c r="F12" s="42" t="s">
-        <v>379</v>
+        <v>207</v>
       </c>
       <c r="G12" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H12" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B13" s="17" t="s">
-        <v>380</v>
+        <v>208</v>
       </c>
       <c r="C13" s="42" t="s">
-        <v>381</v>
+        <v>209</v>
       </c>
       <c r="D13" s="17" t="s">
-        <v>382</v>
+        <v>210</v>
       </c>
       <c r="E13" s="17" t="s">
-        <v>383</v>
+        <v>211</v>
       </c>
       <c r="F13" s="42" t="s">
-        <v>384</v>
+        <v>212</v>
       </c>
       <c r="G13" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H13" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B14" s="17" t="s">
-        <v>385</v>
+        <v>213</v>
       </c>
       <c r="C14" s="42" t="s">
-        <v>386</v>
+        <v>214</v>
       </c>
       <c r="D14" s="17" t="s">
-        <v>387</v>
+        <v>215</v>
       </c>
       <c r="E14" s="17" t="s">
-        <v>388</v>
+        <v>216</v>
       </c>
       <c r="F14" s="42" t="s">
-        <v>389</v>
+        <v>217</v>
       </c>
       <c r="G14" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" s="17" t="s">
-        <v>390</v>
+        <v>218</v>
       </c>
       <c r="C15" s="42" t="s">
-        <v>391</v>
+        <v>219</v>
       </c>
       <c r="D15" s="17" t="s">
-        <v>392</v>
+        <v>220</v>
       </c>
       <c r="E15" s="17" t="s">
-        <v>393</v>
+        <v>221</v>
       </c>
       <c r="F15" s="42" t="s">
-        <v>394</v>
+        <v>222</v>
       </c>
       <c r="G15" s="4">
         <v>4.8899999999999999E-2</v>
@@ -4980,28 +5338,28 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>395</v>
+        <v>223</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>340</v>
+        <v>168</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>341</v>
+        <v>169</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>342</v>
+        <v>170</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>343</v>
+        <v>171</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G17" s="57" t="s">
-        <v>450</v>
-      </c>
-      <c r="H17" s="57" t="s">
-        <v>451</v>
+        <v>116</v>
+      </c>
+      <c r="G17" s="56" t="s">
+        <v>277</v>
+      </c>
+      <c r="H17" s="56" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -5009,45 +5367,45 @@
         <v>0</v>
       </c>
       <c r="B18" s="17" t="s">
-        <v>396</v>
+        <v>224</v>
       </c>
       <c r="C18" s="17" t="s">
-        <v>397</v>
+        <v>225</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>398</v>
+        <v>226</v>
       </c>
       <c r="E18" s="17" t="s">
-        <v>399</v>
+        <v>227</v>
       </c>
       <c r="F18" s="42" t="s">
-        <v>400</v>
+        <v>228</v>
       </c>
       <c r="G18" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H18" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B19" s="17" t="s">
-        <v>401</v>
+        <v>229</v>
       </c>
       <c r="C19" s="42" t="s">
-        <v>402</v>
+        <v>230</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>403</v>
+        <v>231</v>
       </c>
       <c r="E19" s="17" t="s">
-        <v>399</v>
+        <v>227</v>
       </c>
       <c r="F19" s="42" t="s">
-        <v>400</v>
+        <v>228</v>
       </c>
       <c r="G19" s="4">
         <v>1.46E-2</v>
@@ -5058,22 +5416,22 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B20" s="17" t="s">
-        <v>404</v>
+        <v>232</v>
       </c>
       <c r="C20" s="42" t="s">
-        <v>405</v>
+        <v>233</v>
       </c>
       <c r="D20" s="17" t="s">
-        <v>406</v>
+        <v>234</v>
       </c>
       <c r="E20" s="17" t="s">
-        <v>407</v>
+        <v>235</v>
       </c>
       <c r="F20" s="42" t="s">
-        <v>399</v>
+        <v>227</v>
       </c>
       <c r="G20" s="4">
         <v>1.01E-2</v>
@@ -5084,80 +5442,80 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B21" s="17" t="s">
-        <v>408</v>
+        <v>236</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>409</v>
+        <v>237</v>
       </c>
       <c r="D21" s="17" t="s">
-        <v>410</v>
+        <v>238</v>
       </c>
       <c r="E21" s="17" t="s">
-        <v>407</v>
+        <v>235</v>
       </c>
       <c r="F21" s="42" t="s">
-        <v>411</v>
+        <v>239</v>
       </c>
       <c r="G21" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H21" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="17" t="s">
-        <v>412</v>
+        <v>240</v>
       </c>
       <c r="C22" s="42" t="s">
-        <v>413</v>
+        <v>241</v>
       </c>
       <c r="D22" s="17" t="s">
-        <v>414</v>
+        <v>242</v>
       </c>
       <c r="E22" s="17" t="s">
-        <v>407</v>
+        <v>235</v>
       </c>
       <c r="F22" s="42" t="s">
-        <v>399</v>
+        <v>227</v>
       </c>
       <c r="G22" s="4">
         <v>3.0800000000000001E-2</v>
       </c>
       <c r="H22" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>415</v>
+        <v>243</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>340</v>
+        <v>168</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>341</v>
+        <v>169</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>342</v>
+        <v>170</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>343</v>
+        <v>171</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>211</v>
-      </c>
-      <c r="G24" s="57" t="s">
-        <v>450</v>
-      </c>
-      <c r="H24" s="57" t="s">
-        <v>451</v>
+        <v>116</v>
+      </c>
+      <c r="G24" s="56" t="s">
+        <v>277</v>
+      </c>
+      <c r="H24" s="56" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -5165,71 +5523,71 @@
         <v>0</v>
       </c>
       <c r="B25" s="17" t="s">
-        <v>416</v>
+        <v>244</v>
       </c>
       <c r="C25" s="17" t="s">
-        <v>417</v>
+        <v>245</v>
       </c>
       <c r="D25" s="17" t="s">
-        <v>418</v>
+        <v>246</v>
       </c>
       <c r="E25" s="17" t="s">
-        <v>419</v>
+        <v>247</v>
       </c>
       <c r="F25" s="42" t="s">
-        <v>420</v>
+        <v>248</v>
       </c>
       <c r="G25" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H25" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B26" s="17" t="s">
-        <v>421</v>
+        <v>249</v>
       </c>
       <c r="C26" s="42" t="s">
-        <v>422</v>
+        <v>250</v>
       </c>
       <c r="D26" s="17" t="s">
-        <v>423</v>
+        <v>251</v>
       </c>
       <c r="E26" s="17" t="s">
-        <v>424</v>
+        <v>252</v>
       </c>
       <c r="F26" s="42" t="s">
-        <v>425</v>
+        <v>253</v>
       </c>
       <c r="G26" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H26" s="42" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" s="41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="17" t="s">
-        <v>426</v>
+        <v>254</v>
       </c>
       <c r="C27" s="42" t="s">
-        <v>427</v>
+        <v>255</v>
       </c>
       <c r="D27" s="17" t="s">
-        <v>428</v>
+        <v>256</v>
       </c>
       <c r="E27" s="17" t="s">
-        <v>429</v>
+        <v>257</v>
       </c>
       <c r="F27" s="42" t="s">
-        <v>430</v>
+        <v>258</v>
       </c>
       <c r="G27" s="1">
         <v>4.6399999999999997E-2</v>
@@ -5240,22 +5598,22 @@
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" s="41" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B28" s="17" t="s">
-        <v>431</v>
+        <v>259</v>
       </c>
       <c r="C28" s="42" t="s">
-        <v>432</v>
+        <v>260</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>433</v>
+        <v>261</v>
       </c>
       <c r="E28" s="17" t="s">
-        <v>434</v>
+        <v>262</v>
       </c>
       <c r="F28" s="42" t="s">
-        <v>435</v>
+        <v>263</v>
       </c>
       <c r="G28" s="4">
         <v>3.7699999999999997E-2</v>
@@ -5266,28 +5624,43 @@
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" s="41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B29" s="17" t="s">
-        <v>436</v>
+        <v>264</v>
       </c>
       <c r="C29" s="42" t="s">
-        <v>437</v>
+        <v>265</v>
       </c>
       <c r="D29" s="17" t="s">
-        <v>438</v>
+        <v>266</v>
       </c>
       <c r="E29" s="17" t="s">
-        <v>439</v>
+        <v>267</v>
       </c>
       <c r="F29" s="42" t="s">
-        <v>440</v>
+        <v>268</v>
       </c>
       <c r="G29" s="4">
         <v>2.4E-2</v>
       </c>
       <c r="H29" s="4">
         <v>7.5599999999999999E-3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>363</v>
       </c>
     </row>
   </sheetData>

--- a/Part2_analyses/All_stats_clean.xlsx
+++ b/Part2_analyses/All_stats_clean.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3"/>
+    <workbookView xWindow="-60" yWindow="-16320" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="5"/>
   </bookViews>
   <sheets>
     <sheet name="Table 1" sheetId="2" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="863" uniqueCount="517">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="568">
   <si>
     <t>Regarding age</t>
   </si>
@@ -844,9 +844,6 @@
     <t>Non-right-handedness</t>
   </si>
   <si>
-    <t>P-value of Non-right-handedness</t>
-  </si>
-  <si>
     <t>P-value of Lateralized</t>
   </si>
   <si>
@@ -871,9 +868,6 @@
     <t>Regression model of Hand use ~ Sex + Covariates(Age + BD patient)</t>
   </si>
   <si>
-    <t>P-value of Sex in Non-right-handedness</t>
-  </si>
-  <si>
     <t>P-value of Sex in Lateralized</t>
   </si>
   <si>
@@ -1120,9 +1114,6 @@
     <t>Old (=&gt;40y.o.) = 472</t>
   </si>
   <si>
-    <t>PRSs</t>
-  </si>
-  <si>
     <t>Regression model of NRH_cutoff  ~ Sex + Age</t>
   </si>
   <si>
@@ -1580,6 +1571,168 @@
   </si>
   <si>
     <t>16 (9.20%)</t>
+  </si>
+  <si>
+    <t>31 (5.8%)</t>
+  </si>
+  <si>
+    <t>37 (6.96%)</t>
+  </si>
+  <si>
+    <t>47 (8.83%)</t>
+  </si>
+  <si>
+    <t>114 (21.42%)</t>
+  </si>
+  <si>
+    <t>189 (35.53%)</t>
+  </si>
+  <si>
+    <t>Mixed hand use</t>
+  </si>
+  <si>
+    <t>Left handers</t>
+  </si>
+  <si>
+    <t>153 (45%)</t>
+  </si>
+  <si>
+    <t>30 (8.82%)</t>
+  </si>
+  <si>
+    <t>34 (10%)</t>
+  </si>
+  <si>
+    <t>50 (14.7%)</t>
+  </si>
+  <si>
+    <t>103 (30.29%)</t>
+  </si>
+  <si>
+    <t>18 (6.67%)</t>
+  </si>
+  <si>
+    <t>21 (7.78%)</t>
+  </si>
+  <si>
+    <t>28 (10.37%)</t>
+  </si>
+  <si>
+    <t>61 (22.59%)</t>
+  </si>
+  <si>
+    <t>87 (32.22%)</t>
+  </si>
+  <si>
+    <t>17 (10.24%)</t>
+  </si>
+  <si>
+    <t>25 (15.06%)</t>
+  </si>
+  <si>
+    <t>44 (26.5%)</t>
+  </si>
+  <si>
+    <t>64 (38.55%)</t>
+  </si>
+  <si>
+    <t>14 (8.43%)</t>
+  </si>
+  <si>
+    <t>13 (4.9%)</t>
+  </si>
+  <si>
+    <t>16 (6.11%)</t>
+  </si>
+  <si>
+    <t>19 (7.25%)</t>
+  </si>
+  <si>
+    <t>53 (20.23%)</t>
+  </si>
+  <si>
+    <t>102 (38.93%)</t>
+  </si>
+  <si>
+    <t>17 (9.77%)</t>
+  </si>
+  <si>
+    <t>25 (14.37%)</t>
+  </si>
+  <si>
+    <t>59 (33.91%)</t>
+  </si>
+  <si>
+    <t>P-value of Sex in NRH</t>
+  </si>
+  <si>
+    <t>Regression model of Hand use ~ BD_patient + covariates (Age)</t>
+  </si>
+  <si>
+    <t>P-value of BD_patient for NRH</t>
+  </si>
+  <si>
+    <t>P-value of BD_patient for Lateralized</t>
+  </si>
+  <si>
+    <t>P-value of scale in regression NRH ~ scale + covariates (sex + age)</t>
+  </si>
+  <si>
+    <t>P-value of scale in regression LAT ~ scale + covariates (sex + age)</t>
+  </si>
+  <si>
+    <t>Target</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Sample</t>
+  </si>
+  <si>
+    <t>ß</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>PRS r²</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Full r² </t>
+  </si>
+  <si>
+    <t>P-value</t>
+  </si>
+  <si>
+    <t>NRH_0</t>
+  </si>
+  <si>
+    <t>PRS_handedness</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>LQ</t>
+  </si>
+  <si>
+    <t>BD_patient</t>
+  </si>
+  <si>
+    <t>Only BD (265)</t>
+  </si>
+  <si>
+    <t>Only BD</t>
+  </si>
+  <si>
+    <t>PRS_BD</t>
+  </si>
+  <si>
+    <t>Base model accounts for Age, Sex, PC1 and PC2</t>
+  </si>
+  <si>
+    <t>Repeat computing the PCs according to the individuals included</t>
   </si>
 </sst>
 </file>
@@ -1686,7 +1839,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1769,6 +1922,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCCFF"/>
         <bgColor rgb="FFFBE5D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCCFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1856,7 +2021,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="85">
+  <cellXfs count="90">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1948,31 +2113,23 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -1986,6 +2143,15 @@
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2006,20 +2172,26 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="11" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2329,13 +2501,13 @@
     <row r="3" spans="1:5" ht="45" x14ac:dyDescent="0.25">
       <c r="A3" s="10"/>
       <c r="B3" s="1" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>69</v>
@@ -2346,13 +2518,13 @@
         <v>88</v>
       </c>
       <c r="B4" s="17" t="s">
+        <v>281</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>282</v>
+      </c>
+      <c r="D4" s="17" t="s">
         <v>283</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>284</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>285</v>
       </c>
       <c r="E4" s="17">
         <v>0.16300000000000001</v>
@@ -2366,7 +2538,7 @@
         <v>71</v>
       </c>
       <c r="C5" s="17" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D5" s="17" t="s">
         <v>72</v>
@@ -2451,13 +2623,13 @@
         <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C12" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="D12" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E12" s="20">
         <v>0.67579999999999996</v>
@@ -2468,13 +2640,13 @@
         <v>70</v>
       </c>
       <c r="B13" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C13" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="D13" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E13" s="21">
         <v>2.8678831295294999E-3</v>
@@ -2561,21 +2733,21 @@
     <row r="3" spans="1:20" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="22" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C3" s="22"/>
       <c r="D3" s="22"/>
       <c r="E3" s="22"/>
       <c r="F3" s="22"/>
       <c r="G3" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="11" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="M3" s="11"/>
       <c r="N3" s="11"/>
@@ -2586,8 +2758,8 @@
       </c>
       <c r="R3" s="67"/>
       <c r="S3" s="67"/>
-      <c r="T3" s="65" t="s">
-        <v>364</v>
+      <c r="T3" s="58" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="4" spans="1:20" ht="60" x14ac:dyDescent="0.25">
@@ -2604,7 +2776,7 @@
         <v>61</v>
       </c>
       <c r="E4" s="23" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F4" s="23" t="s">
         <v>62</v>
@@ -2619,7 +2791,7 @@
         <v>61</v>
       </c>
       <c r="J4" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K4" s="6" t="s">
         <v>62</v>
@@ -2634,7 +2806,7 @@
         <v>61</v>
       </c>
       <c r="O4" s="12" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="P4" s="12" t="s">
         <v>62</v>
@@ -2648,8 +2820,8 @@
       <c r="S4" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="T4" s="65" t="s">
-        <v>366</v>
+      <c r="T4" s="58" t="s">
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
@@ -2657,49 +2829,49 @@
         <v>0</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="C5" s="24" t="s">
         <v>63</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="G5" s="9" t="s">
+        <v>341</v>
+      </c>
+      <c r="H5" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="I5" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="H5" s="9" t="s">
+      <c r="J5" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="K5" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="I5" s="9" t="s">
-        <v>345</v>
-      </c>
-      <c r="J5" s="9" t="s">
-        <v>347</v>
-      </c>
-      <c r="K5" s="9" t="s">
-        <v>346</v>
-      </c>
       <c r="L5" s="13" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="M5" s="13" t="s">
         <v>64</v>
       </c>
       <c r="N5" s="13" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="O5" s="13" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="P5" s="13" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="Q5" t="s">
         <v>22</v>
@@ -2725,43 +2897,43 @@
         <v>92</v>
       </c>
       <c r="D6" s="24" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F6" s="24" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="G6" s="9" t="s">
+        <v>333</v>
+      </c>
+      <c r="H6" s="9" t="s">
+        <v>332</v>
+      </c>
+      <c r="I6" s="9" t="s">
+        <v>331</v>
+      </c>
+      <c r="J6" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="K6" s="9" t="s">
+        <v>330</v>
+      </c>
+      <c r="L6" s="13" t="s">
+        <v>337</v>
+      </c>
+      <c r="M6" s="13" t="s">
+        <v>336</v>
+      </c>
+      <c r="N6" s="13" t="s">
         <v>335</v>
       </c>
-      <c r="H6" s="9" t="s">
+      <c r="O6" s="13" t="s">
+        <v>356</v>
+      </c>
+      <c r="P6" s="13" t="s">
         <v>334</v>
-      </c>
-      <c r="I6" s="9" t="s">
-        <v>333</v>
-      </c>
-      <c r="J6" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="K6" s="9" t="s">
-        <v>332</v>
-      </c>
-      <c r="L6" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="M6" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="N6" s="13" t="s">
-        <v>337</v>
-      </c>
-      <c r="O6" s="13" t="s">
-        <v>358</v>
-      </c>
-      <c r="P6" s="13" t="s">
-        <v>336</v>
       </c>
       <c r="Q6" t="s">
         <v>22</v>
@@ -2784,46 +2956,46 @@
         <v>93</v>
       </c>
       <c r="C7" s="24" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D7" s="24" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="F7" s="24" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="G7" s="9" t="s">
+        <v>325</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>324</v>
+      </c>
+      <c r="I7" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="J7" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="K7" s="9" t="s">
+        <v>322</v>
+      </c>
+      <c r="L7" s="13" t="s">
+        <v>329</v>
+      </c>
+      <c r="M7" s="13" t="s">
+        <v>328</v>
+      </c>
+      <c r="N7" s="13" t="s">
         <v>327</v>
       </c>
-      <c r="H7" s="9" t="s">
+      <c r="O7" s="13" t="s">
+        <v>357</v>
+      </c>
+      <c r="P7" s="13" t="s">
         <v>326</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>325</v>
-      </c>
-      <c r="J7" s="9" t="s">
-        <v>349</v>
-      </c>
-      <c r="K7" s="9" t="s">
-        <v>324</v>
-      </c>
-      <c r="L7" s="13" t="s">
-        <v>331</v>
-      </c>
-      <c r="M7" s="13" t="s">
-        <v>330</v>
-      </c>
-      <c r="N7" s="13" t="s">
-        <v>329</v>
-      </c>
-      <c r="O7" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="P7" s="13" t="s">
-        <v>328</v>
       </c>
       <c r="Q7" t="s">
         <v>22</v>
@@ -2843,49 +3015,49 @@
         <v>41</v>
       </c>
       <c r="B8" s="24" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="C8" s="24" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D8" s="24" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F8" s="24" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="K8" s="9" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="L8" s="13" t="s">
         <v>65</v>
       </c>
       <c r="M8" s="13" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="N8" s="13" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="O8" s="13" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="P8" s="13" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="Q8" t="s">
         <v>22</v>
@@ -2908,46 +3080,46 @@
         <v>94</v>
       </c>
       <c r="C9" s="24" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D9" s="24" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="F9" s="24" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="I9" s="9" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="J9" s="9" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="K9" s="9" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="L9" s="13" t="s">
         <v>66</v>
       </c>
       <c r="M9" s="13" t="s">
+        <v>312</v>
+      </c>
+      <c r="N9" s="13" t="s">
+        <v>313</v>
+      </c>
+      <c r="O9" s="13" t="s">
+        <v>359</v>
+      </c>
+      <c r="P9" s="13" t="s">
         <v>314</v>
-      </c>
-      <c r="N9" s="13" t="s">
-        <v>315</v>
-      </c>
-      <c r="O9" s="13" t="s">
-        <v>361</v>
-      </c>
-      <c r="P9" s="13" t="s">
-        <v>316</v>
       </c>
       <c r="Q9" t="s">
         <v>22</v>
@@ -2973,7 +3145,7 @@
     <row r="13" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -2991,8 +3163,8 @@
       </c>
       <c r="M13" s="69"/>
       <c r="N13" s="70"/>
-      <c r="O13" s="65" t="s">
-        <v>364</v>
+      <c r="O13" s="58" t="s">
+        <v>361</v>
       </c>
     </row>
     <row r="14" spans="1:20" ht="60" x14ac:dyDescent="0.25">
@@ -3009,7 +3181,7 @@
         <v>6</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>7</v>
@@ -3024,7 +3196,7 @@
         <v>10</v>
       </c>
       <c r="J14" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="K14" s="6" t="s">
         <v>11</v>
@@ -3038,8 +3210,8 @@
       <c r="N14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="O14" s="65" t="s">
-        <v>367</v>
+      <c r="O14" s="58" t="s">
+        <v>364</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
@@ -3258,9 +3430,9 @@
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A22" s="58"/>
-      <c r="B22" s="58"/>
-      <c r="C22" s="58"/>
+      <c r="A22" s="57"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -3296,35 +3468,35 @@
     <row r="4" spans="1:21" ht="45.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="25" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="C4" s="25"/>
       <c r="D4" s="25"/>
       <c r="E4" s="25"/>
       <c r="F4" s="25"/>
-      <c r="G4" s="71" t="s">
-        <v>369</v>
-      </c>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-      <c r="J4" s="72"/>
-      <c r="K4" s="73"/>
-      <c r="L4" s="74" t="s">
-        <v>370</v>
-      </c>
-      <c r="M4" s="75"/>
-      <c r="N4" s="75"/>
-      <c r="O4" s="75"/>
-      <c r="P4" s="76"/>
-      <c r="Q4" s="60" t="s">
-        <v>273</v>
-      </c>
-      <c r="R4" s="61"/>
-      <c r="S4" s="61"/>
-      <c r="T4" s="62" t="s">
-        <v>435</v>
-      </c>
-      <c r="U4" s="62"/>
+      <c r="G4" s="74" t="s">
+        <v>366</v>
+      </c>
+      <c r="H4" s="75"/>
+      <c r="I4" s="75"/>
+      <c r="J4" s="75"/>
+      <c r="K4" s="76"/>
+      <c r="L4" s="77" t="s">
+        <v>367</v>
+      </c>
+      <c r="M4" s="78"/>
+      <c r="N4" s="78"/>
+      <c r="O4" s="78"/>
+      <c r="P4" s="79"/>
+      <c r="Q4" s="71" t="s">
+        <v>272</v>
+      </c>
+      <c r="R4" s="72"/>
+      <c r="S4" s="72"/>
+      <c r="T4" s="73" t="s">
+        <v>432</v>
+      </c>
+      <c r="U4" s="73"/>
     </row>
     <row r="5" spans="1:21" ht="45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -3340,7 +3512,7 @@
         <v>100</v>
       </c>
       <c r="E5" s="26" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F5" s="26" t="s">
         <v>101</v>
@@ -3355,7 +3527,7 @@
         <v>104</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>105</v>
@@ -3370,7 +3542,7 @@
         <v>61</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="P5" s="6" t="s">
         <v>62</v>
@@ -3379,16 +3551,16 @@
         <v>12</v>
       </c>
       <c r="R5" s="44" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="S5" s="44" t="s">
         <v>13</v>
       </c>
       <c r="T5" s="45" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="U5" s="45" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -3402,43 +3574,43 @@
         <v>107</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="E6" s="27" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="H6" s="8" t="s">
         <v>108</v>
       </c>
       <c r="I6" s="8" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="J6" s="8" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="K6" s="8" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="M6" s="9" t="s">
         <v>109</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="O6" s="47" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="P6" s="47" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="Q6" s="17" t="s">
         <v>22</v>
@@ -3467,43 +3639,43 @@
         <v>111</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="E7" s="27" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="G7" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="J7" s="8" t="s">
+        <v>423</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="I7" s="8" t="s">
-        <v>416</v>
-      </c>
-      <c r="J7" s="8" t="s">
-        <v>426</v>
-      </c>
-      <c r="K7" s="8" t="s">
-        <v>417</v>
-      </c>
       <c r="L7" s="9" t="s">
+        <v>392</v>
+      </c>
+      <c r="M7" s="9" t="s">
+        <v>393</v>
+      </c>
+      <c r="N7" s="9" t="s">
+        <v>394</v>
+      </c>
+      <c r="O7" s="47" t="s">
+        <v>430</v>
+      </c>
+      <c r="P7" s="47" t="s">
         <v>395</v>
-      </c>
-      <c r="M7" s="9" t="s">
-        <v>396</v>
-      </c>
-      <c r="N7" s="9" t="s">
-        <v>397</v>
-      </c>
-      <c r="O7" s="47" t="s">
-        <v>433</v>
-      </c>
-      <c r="P7" s="47" t="s">
-        <v>398</v>
       </c>
       <c r="Q7" s="17" t="s">
         <v>22</v>
@@ -3529,46 +3701,46 @@
         <v>112</v>
       </c>
       <c r="C8" s="27" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="E8" s="27" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="I8" s="8" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="J8" s="8" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="K8" s="8" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="L8" s="9" t="s">
+        <v>396</v>
+      </c>
+      <c r="M8" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="N8" s="9" t="s">
+        <v>398</v>
+      </c>
+      <c r="O8" s="47" t="s">
+        <v>431</v>
+      </c>
+      <c r="P8" s="47" t="s">
         <v>399</v>
-      </c>
-      <c r="M8" s="9" t="s">
-        <v>400</v>
-      </c>
-      <c r="N8" s="9" t="s">
-        <v>401</v>
-      </c>
-      <c r="O8" s="47" t="s">
-        <v>434</v>
-      </c>
-      <c r="P8" s="47" t="s">
-        <v>402</v>
       </c>
       <c r="Q8" s="17" t="s">
         <v>22</v>
@@ -3594,46 +3766,46 @@
         <v>113</v>
       </c>
       <c r="C9" s="27" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="E9" s="27" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="G9" s="8" t="s">
+        <v>400</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>405</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>406</v>
+      </c>
+      <c r="J9" s="8" t="s">
+        <v>425</v>
+      </c>
+      <c r="K9" s="8" t="s">
+        <v>407</v>
+      </c>
+      <c r="L9" s="9" t="s">
+        <v>401</v>
+      </c>
+      <c r="M9" s="9" t="s">
+        <v>402</v>
+      </c>
+      <c r="N9" s="9" t="s">
         <v>403</v>
       </c>
-      <c r="H9" s="8" t="s">
-        <v>408</v>
-      </c>
-      <c r="I9" s="8" t="s">
-        <v>409</v>
-      </c>
-      <c r="J9" s="8" t="s">
+      <c r="O9" s="47" t="s">
         <v>428</v>
       </c>
-      <c r="K9" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="L9" s="9" t="s">
+      <c r="P9" s="47" t="s">
         <v>404</v>
-      </c>
-      <c r="M9" s="9" t="s">
-        <v>405</v>
-      </c>
-      <c r="N9" s="9" t="s">
-        <v>406</v>
-      </c>
-      <c r="O9" s="47" t="s">
-        <v>431</v>
-      </c>
-      <c r="P9" s="47" t="s">
-        <v>407</v>
       </c>
       <c r="Q9" s="17" t="s">
         <v>22</v>
@@ -3659,46 +3831,46 @@
         <v>114</v>
       </c>
       <c r="C10" s="27" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="E10" s="27" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="G10" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>419</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="J10" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="K10" s="8" t="s">
         <v>421</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>422</v>
-      </c>
-      <c r="I10" s="8" t="s">
-        <v>423</v>
-      </c>
-      <c r="J10" s="8" t="s">
-        <v>429</v>
-      </c>
-      <c r="K10" s="8" t="s">
-        <v>424</v>
-      </c>
       <c r="L10" s="9" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="N10" s="9" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="O10" s="9" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="P10" s="9" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="Q10" s="17" t="s">
         <v>22</v>
@@ -3748,35 +3920,35 @@
     <row r="4" spans="1:21" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="28" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="C4" s="28"/>
       <c r="D4" s="28"/>
       <c r="E4" s="28"/>
       <c r="F4" s="28"/>
       <c r="G4" s="29" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
       <c r="J4" s="29"/>
       <c r="K4" s="29"/>
       <c r="L4" s="3" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
       <c r="P4" s="3"/>
-      <c r="Q4" s="59" t="s">
+      <c r="Q4" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="R4" s="59"/>
-      <c r="S4" s="59"/>
-      <c r="T4" s="62" t="s">
-        <v>274</v>
-      </c>
-      <c r="U4" s="62"/>
+      <c r="R4" s="83"/>
+      <c r="S4" s="83"/>
+      <c r="T4" s="73" t="s">
+        <v>545</v>
+      </c>
+      <c r="U4" s="73"/>
     </row>
     <row r="5" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
@@ -3792,7 +3964,7 @@
         <v>100</v>
       </c>
       <c r="E5" s="30" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F5" s="30" t="s">
         <v>116</v>
@@ -3807,7 +3979,7 @@
         <v>104</v>
       </c>
       <c r="J5" s="31" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="K5" s="31" t="s">
         <v>117</v>
@@ -3822,7 +3994,7 @@
         <v>61</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="P5" s="6" t="s">
         <v>62</v>
@@ -3831,16 +4003,16 @@
         <v>12</v>
       </c>
       <c r="R5" s="15" t="s">
-        <v>275</v>
+        <v>362</v>
       </c>
       <c r="S5" s="15" t="s">
         <v>13</v>
       </c>
       <c r="T5" s="45" t="s">
-        <v>271</v>
+        <v>546</v>
       </c>
       <c r="U5" s="45" t="s">
-        <v>272</v>
+        <v>547</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.25">
@@ -3854,11 +4026,13 @@
         <v>119</v>
       </c>
       <c r="D6" s="32" t="s">
-        <v>443</v>
-      </c>
-      <c r="E6" s="32"/>
+        <v>440</v>
+      </c>
+      <c r="E6" s="32" t="s">
+        <v>514</v>
+      </c>
       <c r="F6" s="32" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="G6" s="33" t="s">
         <v>120</v>
@@ -3867,24 +4041,28 @@
         <v>121</v>
       </c>
       <c r="I6" s="33" t="s">
-        <v>473</v>
-      </c>
-      <c r="J6" s="33"/>
+        <v>470</v>
+      </c>
+      <c r="J6" s="33" t="s">
+        <v>526</v>
+      </c>
       <c r="K6" s="33" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="L6" s="9" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="M6" s="9" t="s">
         <v>122</v>
       </c>
       <c r="N6" s="9" t="s">
-        <v>471</v>
-      </c>
-      <c r="O6" s="9"/>
+        <v>468</v>
+      </c>
+      <c r="O6" s="9" t="s">
+        <v>536</v>
+      </c>
       <c r="P6" s="9" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="Q6" t="s">
         <v>22</v>
@@ -3913,24 +4091,28 @@
         <v>124</v>
       </c>
       <c r="D7" s="32" t="s">
-        <v>445</v>
-      </c>
-      <c r="E7" s="32"/>
+        <v>442</v>
+      </c>
+      <c r="E7" s="32" t="s">
+        <v>515</v>
+      </c>
       <c r="F7" s="32" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="G7" s="33" t="s">
+        <v>474</v>
+      </c>
+      <c r="H7" s="33" t="s">
+        <v>475</v>
+      </c>
+      <c r="I7" s="33" t="s">
+        <v>476</v>
+      </c>
+      <c r="J7" s="33" t="s">
+        <v>527</v>
+      </c>
+      <c r="K7" s="33" t="s">
         <v>477</v>
-      </c>
-      <c r="H7" s="33" t="s">
-        <v>478</v>
-      </c>
-      <c r="I7" s="33" t="s">
-        <v>479</v>
-      </c>
-      <c r="J7" s="33"/>
-      <c r="K7" s="33" t="s">
-        <v>480</v>
       </c>
       <c r="L7" s="9" t="s">
         <v>125</v>
@@ -3939,11 +4121,13 @@
         <v>126</v>
       </c>
       <c r="N7" s="9" t="s">
-        <v>475</v>
-      </c>
-      <c r="O7" s="9"/>
+        <v>472</v>
+      </c>
+      <c r="O7" s="9" t="s">
+        <v>537</v>
+      </c>
       <c r="P7" s="9" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="Q7" t="s">
         <v>22</v>
@@ -3972,11 +4156,13 @@
         <v>128</v>
       </c>
       <c r="D8" s="32" t="s">
-        <v>447</v>
-      </c>
-      <c r="E8" s="32"/>
+        <v>444</v>
+      </c>
+      <c r="E8" s="32" t="s">
+        <v>516</v>
+      </c>
       <c r="F8" s="32" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="G8" s="33" t="s">
         <v>129</v>
@@ -3985,11 +4171,13 @@
         <v>130</v>
       </c>
       <c r="I8" s="33" t="s">
-        <v>483</v>
-      </c>
-      <c r="J8" s="33"/>
+        <v>480</v>
+      </c>
+      <c r="J8" s="33" t="s">
+        <v>528</v>
+      </c>
       <c r="K8" s="33" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="L8" s="9" t="s">
         <v>131</v>
@@ -3998,11 +4186,13 @@
         <v>132</v>
       </c>
       <c r="N8" s="9" t="s">
-        <v>481</v>
-      </c>
-      <c r="O8" s="9"/>
+        <v>478</v>
+      </c>
+      <c r="O8" s="9" t="s">
+        <v>538</v>
+      </c>
       <c r="P8" s="9" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="Q8" t="s">
         <v>22</v>
@@ -4025,41 +4215,47 @@
         <v>41</v>
       </c>
       <c r="B9" s="32" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C9" s="32" t="s">
+        <v>446</v>
+      </c>
+      <c r="D9" s="32" t="s">
+        <v>448</v>
+      </c>
+      <c r="E9" s="32" t="s">
+        <v>517</v>
+      </c>
+      <c r="F9" s="32" t="s">
         <v>449</v>
-      </c>
-      <c r="D9" s="32" t="s">
-        <v>451</v>
-      </c>
-      <c r="E9" s="32"/>
-      <c r="F9" s="32" t="s">
-        <v>452</v>
       </c>
       <c r="G9" s="33" t="s">
         <v>133</v>
       </c>
       <c r="H9" s="33" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="I9" s="33" t="s">
-        <v>486</v>
-      </c>
-      <c r="J9" s="33"/>
+        <v>483</v>
+      </c>
+      <c r="J9" s="33" t="s">
+        <v>529</v>
+      </c>
       <c r="K9" s="33" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="L9" s="9" t="s">
         <v>134</v>
       </c>
       <c r="M9" s="9" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="N9" s="9" t="s">
         <v>135</v>
       </c>
-      <c r="O9" s="9"/>
+      <c r="O9" s="9" t="s">
+        <v>539</v>
+      </c>
       <c r="P9" s="9" t="s">
         <v>136</v>
       </c>
@@ -4087,46 +4283,52 @@
         <v>137</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="D10" s="32" t="s">
-        <v>454</v>
-      </c>
-      <c r="E10" s="32"/>
+        <v>451</v>
+      </c>
+      <c r="E10" s="32" t="s">
+        <v>518</v>
+      </c>
       <c r="F10" s="32" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="G10" s="33" t="s">
         <v>138</v>
       </c>
       <c r="H10" s="33" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="I10" s="33" t="s">
-        <v>490</v>
-      </c>
-      <c r="J10" s="33"/>
+        <v>487</v>
+      </c>
+      <c r="J10" s="33" t="s">
+        <v>530</v>
+      </c>
       <c r="K10" s="33" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="L10" s="9" t="s">
         <v>139</v>
       </c>
       <c r="M10" s="9" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="N10" s="9" t="s">
         <v>140</v>
       </c>
-      <c r="O10" s="9"/>
+      <c r="O10" s="9" t="s">
+        <v>540</v>
+      </c>
       <c r="P10" s="9" t="s">
         <v>141</v>
       </c>
       <c r="Q10" t="s">
         <v>22</v>
       </c>
-      <c r="R10" s="51">
-        <v>9.8000000000000004E-2</v>
+      <c r="R10" t="s">
+        <v>22</v>
       </c>
       <c r="S10" s="35" t="s">
         <v>22</v>
@@ -4146,35 +4348,35 @@
     <row r="14" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="36" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="C14" s="36"/>
       <c r="D14" s="36"/>
       <c r="E14" s="36"/>
       <c r="F14" s="36"/>
       <c r="G14" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="11" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="M14" s="11"/>
       <c r="N14" s="11"/>
       <c r="O14" s="11"/>
       <c r="P14" s="11"/>
-      <c r="Q14" s="59" t="s">
+      <c r="Q14" s="83" t="s">
         <v>2</v>
       </c>
-      <c r="R14" s="59"/>
-      <c r="S14" s="59"/>
-      <c r="T14" s="62" t="s">
-        <v>274</v>
-      </c>
-      <c r="U14" s="62"/>
+      <c r="R14" s="83"/>
+      <c r="S14" s="83"/>
+      <c r="T14" s="73" t="s">
+        <v>273</v>
+      </c>
+      <c r="U14" s="73"/>
     </row>
     <row r="15" spans="1:21" ht="60" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
@@ -4190,7 +4392,7 @@
         <v>100</v>
       </c>
       <c r="E15" s="37" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="F15" s="37" t="s">
         <v>116</v>
@@ -4205,7 +4407,7 @@
         <v>104</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>117</v>
@@ -4220,7 +4422,7 @@
         <v>61</v>
       </c>
       <c r="O15" s="12" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="P15" s="12" t="s">
         <v>62</v>
@@ -4229,16 +4431,16 @@
         <v>12</v>
       </c>
       <c r="R15" s="15" t="s">
-        <v>275</v>
+        <v>362</v>
       </c>
       <c r="S15" s="15" t="s">
         <v>13</v>
       </c>
       <c r="T15" s="45" t="s">
-        <v>271</v>
+        <v>546</v>
       </c>
       <c r="U15" s="45" t="s">
-        <v>272</v>
+        <v>547</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.25">
@@ -4252,11 +4454,13 @@
         <v>144</v>
       </c>
       <c r="D16" s="38" t="s">
-        <v>456</v>
-      </c>
-      <c r="E16" s="38"/>
+        <v>453</v>
+      </c>
+      <c r="E16" s="38" t="s">
+        <v>522</v>
+      </c>
       <c r="F16" s="38" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="G16" s="8" t="s">
         <v>145</v>
@@ -4265,24 +4469,28 @@
         <v>146</v>
       </c>
       <c r="I16" s="8" t="s">
+        <v>510</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>509</v>
+      </c>
+      <c r="L16" s="13" t="s">
         <v>513</v>
-      </c>
-      <c r="J16" s="8"/>
-      <c r="K16" s="8" t="s">
-        <v>512</v>
-      </c>
-      <c r="L16" s="13" t="s">
-        <v>516</v>
       </c>
       <c r="M16" s="13" t="s">
         <v>147</v>
       </c>
       <c r="N16" s="13" t="s">
-        <v>515</v>
-      </c>
-      <c r="O16" s="13"/>
+        <v>512</v>
+      </c>
+      <c r="O16" s="13" t="s">
+        <v>513</v>
+      </c>
       <c r="P16" s="13" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="Q16" s="49" t="s">
         <v>22</v>
@@ -4311,11 +4519,13 @@
         <v>149</v>
       </c>
       <c r="D17" s="38" t="s">
-        <v>458</v>
-      </c>
-      <c r="E17" s="38"/>
+        <v>455</v>
+      </c>
+      <c r="E17" s="38" t="s">
+        <v>523</v>
+      </c>
       <c r="F17" s="38" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="G17" s="8" t="s">
         <v>150</v>
@@ -4324,11 +4534,13 @@
         <v>151</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>509</v>
-      </c>
-      <c r="J17" s="8"/>
+        <v>506</v>
+      </c>
+      <c r="J17" s="8" t="s">
+        <v>531</v>
+      </c>
       <c r="K17" s="8" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="L17" s="13" t="s">
         <v>152</v>
@@ -4337,11 +4549,13 @@
         <v>153</v>
       </c>
       <c r="N17" s="13" t="s">
-        <v>511</v>
-      </c>
-      <c r="O17" s="13"/>
+        <v>508</v>
+      </c>
+      <c r="O17" s="13" t="s">
+        <v>541</v>
+      </c>
       <c r="P17" s="13" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="Q17" s="49" t="s">
         <v>22</v>
@@ -4367,14 +4581,16 @@
         <v>154</v>
       </c>
       <c r="C18" s="38" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D18" s="38" t="s">
-        <v>461</v>
-      </c>
-      <c r="E18" s="38"/>
+        <v>458</v>
+      </c>
+      <c r="E18" s="38" t="s">
+        <v>524</v>
+      </c>
       <c r="F18" s="38" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="G18" s="8" t="s">
         <v>155</v>
@@ -4383,24 +4599,28 @@
         <v>156</v>
       </c>
       <c r="I18" s="8" t="s">
+        <v>500</v>
+      </c>
+      <c r="J18" s="8" t="s">
+        <v>532</v>
+      </c>
+      <c r="K18" s="8" t="s">
+        <v>499</v>
+      </c>
+      <c r="L18" s="13" t="s">
+        <v>504</v>
+      </c>
+      <c r="M18" s="13" t="s">
         <v>503</v>
       </c>
-      <c r="J18" s="8"/>
-      <c r="K18" s="8" t="s">
+      <c r="N18" s="13" t="s">
         <v>502</v>
       </c>
-      <c r="L18" s="13" t="s">
-        <v>507</v>
-      </c>
-      <c r="M18" s="13" t="s">
-        <v>506</v>
-      </c>
-      <c r="N18" s="13" t="s">
-        <v>505</v>
-      </c>
-      <c r="O18" s="13"/>
+      <c r="O18" s="13" t="s">
+        <v>542</v>
+      </c>
       <c r="P18" s="13" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="Q18" s="49" t="s">
         <v>22</v>
@@ -4423,17 +4643,19 @@
         <v>41</v>
       </c>
       <c r="B19" s="38" t="s">
+        <v>460</v>
+      </c>
+      <c r="C19" s="38" t="s">
+        <v>461</v>
+      </c>
+      <c r="D19" s="38" t="s">
+        <v>462</v>
+      </c>
+      <c r="E19" s="38" t="s">
+        <v>525</v>
+      </c>
+      <c r="F19" s="38" t="s">
         <v>463</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>464</v>
-      </c>
-      <c r="D19" s="38" t="s">
-        <v>465</v>
-      </c>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38" t="s">
-        <v>466</v>
       </c>
       <c r="G19" s="8" t="s">
         <v>157</v>
@@ -4442,24 +4664,28 @@
         <v>158</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>498</v>
-      </c>
-      <c r="J19" s="8"/>
+        <v>495</v>
+      </c>
+      <c r="J19" s="8" t="s">
+        <v>533</v>
+      </c>
       <c r="K19" s="8" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="L19" s="13" t="s">
         <v>159</v>
       </c>
       <c r="M19" s="13" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="N19" s="13" t="s">
-        <v>500</v>
-      </c>
-      <c r="O19" s="13"/>
+        <v>497</v>
+      </c>
+      <c r="O19" s="13" t="s">
+        <v>543</v>
+      </c>
       <c r="P19" s="13" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="Q19" s="49" t="s">
         <v>22</v>
@@ -4485,14 +4711,16 @@
         <v>160</v>
       </c>
       <c r="C20" s="38" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D20" s="38" t="s">
-        <v>468</v>
-      </c>
-      <c r="E20" s="38"/>
+        <v>465</v>
+      </c>
+      <c r="E20" s="38" t="s">
+        <v>521</v>
+      </c>
       <c r="F20" s="38" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="G20" s="8" t="s">
         <v>161</v>
@@ -4501,24 +4729,28 @@
         <v>162</v>
       </c>
       <c r="I20" s="8" t="s">
+        <v>490</v>
+      </c>
+      <c r="J20" s="8" t="s">
+        <v>534</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>489</v>
+      </c>
+      <c r="L20" s="13" t="s">
         <v>493</v>
       </c>
-      <c r="J20" s="8"/>
-      <c r="K20" s="8" t="s">
+      <c r="M20" s="13" t="s">
         <v>492</v>
       </c>
-      <c r="L20" s="13" t="s">
-        <v>496</v>
-      </c>
-      <c r="M20" s="13" t="s">
-        <v>495</v>
-      </c>
       <c r="N20" s="13" t="s">
-        <v>495</v>
-      </c>
-      <c r="O20" s="13"/>
+        <v>492</v>
+      </c>
+      <c r="O20" s="13" t="s">
+        <v>491</v>
+      </c>
       <c r="P20" s="13" t="s">
-        <v>494</v>
+        <v>491</v>
       </c>
       <c r="Q20" s="49" t="s">
         <v>22</v>
@@ -4530,10 +4762,10 @@
         <v>3.1E-2</v>
       </c>
       <c r="T20" s="43">
-        <v>4.0099999999999997E-2</v>
+        <v>2.69E-2</v>
       </c>
       <c r="U20" s="43">
-        <v>3.5000000000000003E-2</v>
+        <v>2.3199999999999998E-2</v>
       </c>
     </row>
     <row r="21" spans="1:21" x14ac:dyDescent="0.25">
@@ -4542,59 +4774,55 @@
       <c r="S21" s="14"/>
     </row>
     <row r="22" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="84" t="s">
+      <c r="B22" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="C22" s="84"/>
-      <c r="D22" s="84"/>
-      <c r="E22" s="77"/>
-      <c r="G22" s="84" t="s">
+      <c r="C22" s="82"/>
+      <c r="D22" s="82"/>
+      <c r="E22" s="59"/>
+      <c r="G22" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="H22" s="84"/>
-      <c r="I22" s="84"/>
-      <c r="J22" s="77"/>
-      <c r="L22" s="84" t="s">
+      <c r="H22" s="82"/>
+      <c r="I22" s="82"/>
+      <c r="L22" s="82" t="s">
         <v>2</v>
       </c>
-      <c r="M22" s="84"/>
-      <c r="N22" s="84"/>
-      <c r="O22" s="77"/>
+      <c r="M22" s="82"/>
+      <c r="N22" s="82"/>
       <c r="Q22" s="14"/>
       <c r="R22" s="14"/>
       <c r="S22" s="14"/>
     </row>
-    <row r="23" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" ht="30" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
-        <v>12</v>
+        <v>520</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>270</v>
+        <v>362</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="E23" s="78"/>
+        <v>519</v>
+      </c>
+      <c r="E23" s="60"/>
       <c r="G23" s="15" t="s">
-        <v>12</v>
+        <v>520</v>
       </c>
       <c r="H23" s="15" t="s">
-        <v>270</v>
+        <v>362</v>
       </c>
       <c r="I23" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="J23" s="78"/>
+        <v>519</v>
+      </c>
       <c r="L23" s="15" t="s">
-        <v>12</v>
+        <v>520</v>
       </c>
       <c r="M23" s="15" t="s">
-        <v>270</v>
+        <v>362</v>
       </c>
       <c r="N23" s="15" t="s">
-        <v>13</v>
-      </c>
-      <c r="O23" s="78"/>
+        <v>519</v>
+      </c>
     </row>
     <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="1">
@@ -4609,7 +4837,7 @@
       <c r="D24" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E24" s="79"/>
+      <c r="E24" s="61"/>
       <c r="F24" s="1">
         <v>0</v>
       </c>
@@ -4622,7 +4850,7 @@
       <c r="I24" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J24" s="79"/>
+      <c r="J24" s="61"/>
       <c r="K24" s="1">
         <v>0</v>
       </c>
@@ -4635,7 +4863,7 @@
       <c r="N24" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="O24" s="79"/>
+      <c r="O24" s="61"/>
     </row>
     <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
@@ -4650,7 +4878,7 @@
       <c r="D25" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="E25" s="79"/>
+      <c r="E25" s="61"/>
       <c r="F25" s="1" t="s">
         <v>23</v>
       </c>
@@ -4663,7 +4891,7 @@
       <c r="I25" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J25" s="79"/>
+      <c r="J25" s="61"/>
       <c r="K25" s="1" t="s">
         <v>23</v>
       </c>
@@ -4676,7 +4904,7 @@
       <c r="N25" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="O25" s="79"/>
+      <c r="O25" s="61"/>
     </row>
     <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
@@ -4691,7 +4919,7 @@
       <c r="D26" s="54">
         <v>1.9769999999999999E-2</v>
       </c>
-      <c r="E26" s="82"/>
+      <c r="E26" s="64"/>
       <c r="F26" s="1" t="s">
         <v>32</v>
       </c>
@@ -4704,7 +4932,7 @@
       <c r="I26" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J26" s="79"/>
+      <c r="J26" s="61"/>
       <c r="K26" s="1" t="s">
         <v>32</v>
       </c>
@@ -4717,7 +4945,7 @@
       <c r="N26" s="55">
         <v>5.5E-2</v>
       </c>
-      <c r="O26" s="80"/>
+      <c r="O26" s="62"/>
     </row>
     <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
@@ -4732,7 +4960,7 @@
       <c r="D27" s="19">
         <v>5.0610000000000004E-3</v>
       </c>
-      <c r="E27" s="83"/>
+      <c r="E27" s="65"/>
       <c r="F27" s="1" t="s">
         <v>41</v>
       </c>
@@ -4745,7 +4973,7 @@
       <c r="I27" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J27" s="79"/>
+      <c r="J27" s="61"/>
       <c r="K27" s="1" t="s">
         <v>41</v>
       </c>
@@ -4758,7 +4986,7 @@
       <c r="N27" s="21">
         <v>1.596E-3</v>
       </c>
-      <c r="O27" s="81"/>
+      <c r="O27" s="63"/>
     </row>
     <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
@@ -4773,7 +5001,7 @@
       <c r="D28" s="19">
         <v>7.9810000000000002E-3</v>
       </c>
-      <c r="E28" s="83"/>
+      <c r="E28" s="65"/>
       <c r="F28" s="1" t="s">
         <v>50</v>
       </c>
@@ -4786,7 +5014,7 @@
       <c r="I28" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="J28" s="79"/>
+      <c r="J28" s="61"/>
       <c r="K28" s="1" t="s">
         <v>50</v>
       </c>
@@ -4799,44 +5027,44 @@
       <c r="N28" s="21">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="O28" s="81"/>
+      <c r="O28" s="63"/>
     </row>
     <row r="29" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="E29" s="79"/>
+      <c r="E29" s="61"/>
     </row>
     <row r="30" spans="1:21" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="63" t="s">
+      <c r="B30" s="80" t="s">
+        <v>278</v>
+      </c>
+      <c r="C30" s="81"/>
+      <c r="E30" s="61"/>
+      <c r="G30" s="80" t="s">
+        <v>275</v>
+      </c>
+      <c r="H30" s="81"/>
+      <c r="L30" s="80" t="s">
+        <v>275</v>
+      </c>
+      <c r="M30" s="81"/>
+    </row>
+    <row r="31" spans="1:21" ht="45" x14ac:dyDescent="0.25">
+      <c r="B31" s="45" t="s">
+        <v>544</v>
+      </c>
+      <c r="C31" s="45" t="s">
         <v>279</v>
       </c>
-      <c r="C30" s="64"/>
-      <c r="E30" s="79"/>
-      <c r="G30" s="63" t="s">
-        <v>276</v>
-      </c>
-      <c r="H30" s="64"/>
-      <c r="L30" s="63" t="s">
-        <v>276</v>
-      </c>
-      <c r="M30" s="64"/>
-    </row>
-    <row r="31" spans="1:21" ht="75" x14ac:dyDescent="0.25">
-      <c r="B31" s="45" t="s">
-        <v>280</v>
-      </c>
-      <c r="C31" s="45" t="s">
-        <v>281</v>
-      </c>
       <c r="G31" s="45" t="s">
-        <v>280</v>
+        <v>544</v>
       </c>
       <c r="H31" s="45" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="L31" s="45" t="s">
-        <v>280</v>
+        <v>544</v>
       </c>
       <c r="M31" s="45" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
     </row>
     <row r="32" spans="1:21" x14ac:dyDescent="0.25">
@@ -4902,10 +5130,10 @@
         <v>32</v>
       </c>
       <c r="B34" s="53">
-        <v>9.75E-3</v>
+        <v>7.0000000000000001E-3</v>
       </c>
       <c r="C34" s="53">
-        <v>1.9400000000000001E-2</v>
+        <v>1.34E-2</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>32</v>
@@ -4920,10 +5148,10 @@
         <v>32</v>
       </c>
       <c r="L34" s="46">
-        <v>2.4E-2</v>
-      </c>
-      <c r="M34" s="57">
-        <v>6.2399999999999997E-2</v>
+        <v>1.7000000000000001E-2</v>
+      </c>
+      <c r="M34" s="46">
+        <v>3.8699999999999998E-2</v>
       </c>
     </row>
     <row r="35" spans="1:13" x14ac:dyDescent="0.25">
@@ -4931,10 +5159,10 @@
         <v>41</v>
       </c>
       <c r="B35" s="53">
-        <v>3.2100000000000002E-3</v>
+        <v>3.3E-3</v>
       </c>
       <c r="C35" s="53">
-        <v>6.6E-3</v>
+        <v>6.7400000000000003E-3</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>41</v>
@@ -4949,10 +5177,10 @@
         <v>41</v>
       </c>
       <c r="L35" s="46">
-        <v>1.42E-3</v>
+        <v>1.5E-3</v>
       </c>
       <c r="M35" s="46">
-        <v>2.1299999999999999E-3</v>
+        <v>2.2100000000000002E-3</v>
       </c>
     </row>
     <row r="36" spans="1:13" x14ac:dyDescent="0.25">
@@ -4960,10 +5188,10 @@
         <v>50</v>
       </c>
       <c r="B36" s="53">
-        <v>5.64E-3</v>
+        <v>5.5599999999999998E-3</v>
       </c>
       <c r="C36" s="53">
-        <v>8.0099999999999998E-3</v>
+        <v>7.8499999999999993E-3</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>50</v>
@@ -4978,10 +5206,10 @@
         <v>50</v>
       </c>
       <c r="L36" s="46">
-        <v>1.2999999999999999E-2</v>
+        <v>1.03E-2</v>
       </c>
       <c r="M36" s="46">
-        <v>1.5900000000000001E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
     </row>
   </sheetData>
@@ -4998,12 +5226,13 @@
     <mergeCell ref="Q14:S14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.5703125" bestFit="1" customWidth="1"/>
@@ -5011,20 +5240,20 @@
     <col min="4" max="4" width="12.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15.5703125" customWidth="1"/>
-    <col min="7" max="7" width="24.140625" customWidth="1"/>
-    <col min="8" max="8" width="23.7109375" customWidth="1"/>
+    <col min="7" max="7" width="4.140625" customWidth="1"/>
+    <col min="8" max="8" width="5.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A1" s="39" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="G2" s="14"/>
       <c r="H2" s="14"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>167</v>
       </c>
@@ -5044,13 +5273,19 @@
         <v>116</v>
       </c>
       <c r="G3" s="56" t="s">
+        <v>276</v>
+      </c>
+      <c r="H3" s="56" t="s">
         <v>277</v>
       </c>
-      <c r="H3" s="56" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I3" s="84" t="s">
+        <v>548</v>
+      </c>
+      <c r="J3" s="84" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="41">
         <v>0</v>
       </c>
@@ -5075,8 +5310,14 @@
       <c r="H4" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I4" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J4" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" s="41" t="s">
         <v>23</v>
       </c>
@@ -5101,9 +5342,15 @@
       <c r="H5" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" s="41" t="s">
+      <c r="I5" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J5" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="85" t="s">
         <v>32</v>
       </c>
       <c r="B6" s="17" t="s">
@@ -5127,8 +5374,14 @@
       <c r="H6" s="4">
         <v>1.7299999999999999E-2</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I6" s="46">
+        <v>3.1899999999999998E-2</v>
+      </c>
+      <c r="J6" s="46">
+        <v>4.0699999999999998E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" s="41" t="s">
         <v>41</v>
       </c>
@@ -5153,8 +5406,14 @@
       <c r="H7" s="4">
         <v>6.5399999999999998E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I7" s="46">
+        <v>4.7099999999999998E-3</v>
+      </c>
+      <c r="J7" s="46">
+        <v>3.2399999999999998E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" s="41" t="s">
         <v>50</v>
       </c>
@@ -5179,8 +5438,18 @@
       <c r="H8" s="4">
         <v>1.01E-3</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I8" s="46">
+        <v>4.7099999999999998E-3</v>
+      </c>
+      <c r="J8" s="46">
+        <v>8.5300000000000003E-4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>197</v>
       </c>
@@ -5200,13 +5469,19 @@
         <v>116</v>
       </c>
       <c r="G10" s="56" t="s">
+        <v>276</v>
+      </c>
+      <c r="H10" s="56" t="s">
         <v>277</v>
       </c>
-      <c r="H10" s="56" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I10" s="84" t="s">
+        <v>548</v>
+      </c>
+      <c r="J10" s="84" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" s="41">
         <v>0</v>
       </c>
@@ -5231,8 +5506,14 @@
       <c r="H11" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J11" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="41" t="s">
         <v>23</v>
       </c>
@@ -5257,9 +5538,15 @@
       <c r="H12" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A13" s="41" t="s">
+      <c r="I12" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J12" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="85" t="s">
         <v>32</v>
       </c>
       <c r="B13" s="17" t="s">
@@ -5283,8 +5570,14 @@
       <c r="H13" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I13" s="46">
+        <v>4.2599999999999999E-2</v>
+      </c>
+      <c r="J13" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" s="41" t="s">
         <v>41</v>
       </c>
@@ -5309,8 +5602,14 @@
       <c r="H14" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I14" s="46">
+        <v>4.5900000000000003E-2</v>
+      </c>
+      <c r="J14" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" s="41" t="s">
         <v>50</v>
       </c>
@@ -5335,8 +5634,18 @@
       <c r="H15" s="4">
         <v>3.7600000000000001E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I15" s="46">
+        <v>6.9300000000000004E-3</v>
+      </c>
+      <c r="J15" s="46">
+        <v>1.7999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I16" s="17"/>
+      <c r="J16" s="17"/>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>223</v>
       </c>
@@ -5356,13 +5665,19 @@
         <v>116</v>
       </c>
       <c r="G17" s="56" t="s">
+        <v>276</v>
+      </c>
+      <c r="H17" s="56" t="s">
         <v>277</v>
       </c>
-      <c r="H17" s="56" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I17" s="84" t="s">
+        <v>548</v>
+      </c>
+      <c r="J17" s="84" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A18" s="41">
         <v>0</v>
       </c>
@@ -5387,8 +5702,14 @@
       <c r="H18" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I18" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J18" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A19" s="41" t="s">
         <v>23</v>
       </c>
@@ -5413,9 +5734,15 @@
       <c r="H19" s="4">
         <v>3.1199999999999999E-2</v>
       </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="41" t="s">
+      <c r="I19" s="46">
+        <v>1.66E-2</v>
+      </c>
+      <c r="J19" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="85" t="s">
         <v>32</v>
       </c>
       <c r="B20" s="17" t="s">
@@ -5439,8 +5766,14 @@
       <c r="H20" s="4">
         <v>6.5399999999999998E-3</v>
       </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I20" s="46">
+        <v>1.66E-2</v>
+      </c>
+      <c r="J20" s="46">
+        <v>2.4160000000000001E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" s="41" t="s">
         <v>41</v>
       </c>
@@ -5465,8 +5798,14 @@
       <c r="H21" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I21" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J21" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="41" t="s">
         <v>50</v>
       </c>
@@ -5491,8 +5830,18 @@
       <c r="H22" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I22" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J22" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I23" s="17"/>
+      <c r="J23" s="17"/>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>243</v>
       </c>
@@ -5512,13 +5861,19 @@
         <v>116</v>
       </c>
       <c r="G24" s="56" t="s">
+        <v>276</v>
+      </c>
+      <c r="H24" s="56" t="s">
         <v>277</v>
       </c>
-      <c r="H24" s="56" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I24" s="84" t="s">
+        <v>548</v>
+      </c>
+      <c r="J24" s="84" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="41">
         <v>0</v>
       </c>
@@ -5543,8 +5898,14 @@
       <c r="H25" s="17" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I25" s="17" t="s">
+        <v>22</v>
+      </c>
+      <c r="J25" s="17" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="41" t="s">
         <v>23</v>
       </c>
@@ -5569,9 +5930,15 @@
       <c r="H26" s="42" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A27" s="41" t="s">
+      <c r="I26" s="42" t="s">
+        <v>22</v>
+      </c>
+      <c r="J26" s="42" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="85" t="s">
         <v>32</v>
       </c>
       <c r="B27" s="17" t="s">
@@ -5595,8 +5962,14 @@
       <c r="H27" s="4">
         <v>1.4200000000000001E-2</v>
       </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I27" s="4">
+        <v>3.6799999999999999E-2</v>
+      </c>
+      <c r="J27" s="4">
+        <v>1.5900000000000001E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="41" t="s">
         <v>41</v>
       </c>
@@ -5621,8 +5994,14 @@
       <c r="H28" s="4">
         <v>1.0699999999999999E-2</v>
       </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I28" s="4">
+        <v>2.01E-2</v>
+      </c>
+      <c r="J28" s="4">
+        <v>1.35E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="41" t="s">
         <v>50</v>
       </c>
@@ -5646,6 +6025,12 @@
       </c>
       <c r="H29" s="4">
         <v>7.5599999999999999E-3</v>
+      </c>
+      <c r="I29" s="4">
+        <v>7.5700000000000003E-3</v>
+      </c>
+      <c r="J29" s="4">
+        <v>8.3000000000000001E-3</v>
       </c>
     </row>
   </sheetData>
@@ -5655,12 +6040,459 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
+  <dimension ref="A1:H19"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>363</v>
+        <v>550</v>
+      </c>
+      <c r="B1" t="s">
+        <v>551</v>
+      </c>
+      <c r="C1" t="s">
+        <v>552</v>
+      </c>
+      <c r="D1" t="s">
+        <v>553</v>
+      </c>
+      <c r="E1" t="s">
+        <v>554</v>
+      </c>
+      <c r="F1" t="s">
+        <v>555</v>
+      </c>
+      <c r="G1" t="s">
+        <v>556</v>
+      </c>
+      <c r="H1" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C2" t="s">
+        <v>560</v>
+      </c>
+      <c r="D2" s="86">
+        <v>0.22800000000000001</v>
+      </c>
+      <c r="E2" s="86">
+        <v>0.114565</v>
+      </c>
+      <c r="F2" s="86">
+        <v>8.6185719999999997E-3</v>
+      </c>
+      <c r="G2" s="86">
+        <v>1.7972849999999999E-2</v>
+      </c>
+      <c r="H2" s="43">
+        <v>4.65E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>561</v>
+      </c>
+      <c r="B3" t="s">
+        <v>559</v>
+      </c>
+      <c r="C3" t="s">
+        <v>560</v>
+      </c>
+      <c r="D3" s="86">
+        <v>-2.85439</v>
+      </c>
+      <c r="E3" s="86">
+        <v>1.33979</v>
+      </c>
+      <c r="F3" s="86">
+        <v>4.0185790000000004E-3</v>
+      </c>
+      <c r="G3" s="86">
+        <v>1.370909E-2</v>
+      </c>
+      <c r="H3" s="43">
+        <v>3.3300000000000003E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>562</v>
+      </c>
+      <c r="B4" t="s">
+        <v>559</v>
+      </c>
+      <c r="C4" t="s">
+        <v>560</v>
+      </c>
+      <c r="D4" s="86">
+        <v>-1.5124E-2</v>
+      </c>
+      <c r="E4" s="86">
+        <v>8.1206E-2</v>
+      </c>
+      <c r="F4" s="86">
+        <v>3.029282E-5</v>
+      </c>
+      <c r="G4" s="86">
+        <v>0.42957109999999998</v>
+      </c>
+      <c r="H4">
+        <v>0.85199999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>167</v>
+      </c>
+      <c r="B5" t="s">
+        <v>559</v>
+      </c>
+      <c r="C5" t="s">
+        <v>563</v>
+      </c>
+      <c r="D5" s="86">
+        <v>0.97745000000000004</v>
+      </c>
+      <c r="E5" s="86">
+        <v>1.073529</v>
+      </c>
+      <c r="F5" s="86">
+        <v>3.174577E-3</v>
+      </c>
+      <c r="G5" s="86">
+        <v>8.1997019999999997E-3</v>
+      </c>
+      <c r="H5">
+        <v>0.36299999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>223</v>
+      </c>
+      <c r="B6" t="s">
+        <v>559</v>
+      </c>
+      <c r="C6" t="s">
+        <v>564</v>
+      </c>
+      <c r="D6" s="86">
+        <v>5.7932000000000001E-3</v>
+      </c>
+      <c r="E6" s="86">
+        <v>5.4758999999999997E-3</v>
+      </c>
+      <c r="F6" s="86">
+        <v>3.4004780000000002E-3</v>
+      </c>
+      <c r="G6" s="86">
+        <v>1.8681349999999999E-2</v>
+      </c>
+      <c r="H6" s="86">
+        <v>0.29099999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>243</v>
+      </c>
+      <c r="B7" t="s">
+        <v>559</v>
+      </c>
+      <c r="C7" t="s">
+        <v>564</v>
+      </c>
+      <c r="D7" s="86">
+        <v>-1.15222</v>
+      </c>
+      <c r="E7" s="86">
+        <v>0.89183000000000001</v>
+      </c>
+      <c r="F7" s="86">
+        <v>5.752788E-3</v>
+      </c>
+      <c r="G7" s="86">
+        <v>1.7773810000000001E-2</v>
+      </c>
+      <c r="H7">
+        <v>0.19739999999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" s="87" t="s">
+        <v>197</v>
+      </c>
+      <c r="B8" s="87" t="s">
+        <v>559</v>
+      </c>
+      <c r="C8" t="s">
+        <v>564</v>
+      </c>
+      <c r="D8" s="86">
+        <v>0.1664659</v>
+      </c>
+      <c r="E8" s="86">
+        <v>7.2288099999999994E-2</v>
+      </c>
+      <c r="F8" s="86">
+        <v>1.706742E-2</v>
+      </c>
+      <c r="G8" s="86">
+        <v>2.4799419999999999E-2</v>
+      </c>
+      <c r="H8" s="43">
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>562</v>
+      </c>
+      <c r="B9" t="s">
+        <v>565</v>
+      </c>
+      <c r="C9" t="s">
+        <v>560</v>
+      </c>
+      <c r="D9" s="86">
+        <v>0.67669900000000005</v>
+      </c>
+      <c r="E9" s="86">
+        <v>9.1203000000000006E-2</v>
+      </c>
+      <c r="F9" s="86">
+        <v>5.2065960000000001E-2</v>
+      </c>
+      <c r="G9" s="86">
+        <v>0.4816067</v>
+      </c>
+      <c r="H9" s="88">
+        <v>1.1700000000000001E-13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>167</v>
+      </c>
+      <c r="B10" t="s">
+        <v>565</v>
+      </c>
+      <c r="C10" t="s">
+        <v>564</v>
+      </c>
+      <c r="D10" s="86">
+        <v>1.2246490000000001</v>
+      </c>
+      <c r="E10" s="86">
+        <v>1.1910959999999999</v>
+      </c>
+      <c r="F10" s="86">
+        <v>4.0445749999999999E-3</v>
+      </c>
+      <c r="G10" s="86">
+        <v>9.0697009999999995E-3</v>
+      </c>
+      <c r="H10">
+        <v>0.30499999999999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>223</v>
+      </c>
+      <c r="B11" t="s">
+        <v>565</v>
+      </c>
+      <c r="C11" t="s">
+        <v>564</v>
+      </c>
+      <c r="D11" s="86">
+        <v>5.9179000000000002E-3</v>
+      </c>
+      <c r="E11" s="86">
+        <v>6.0410999999999998E-3</v>
+      </c>
+      <c r="F11" s="86">
+        <v>2.9169700000000001E-3</v>
+      </c>
+      <c r="G11" s="86">
+        <v>1.819784E-2</v>
+      </c>
+      <c r="H11">
+        <v>0.32800000000000001</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>243</v>
+      </c>
+      <c r="B12" t="s">
+        <v>565</v>
+      </c>
+      <c r="C12" t="s">
+        <v>564</v>
+      </c>
+      <c r="D12" s="86">
+        <v>-0.62470000000000003</v>
+      </c>
+      <c r="E12" s="86">
+        <v>0.98080000000000001</v>
+      </c>
+      <c r="F12" s="86">
+        <v>1.404326E-3</v>
+      </c>
+      <c r="G12" s="86">
+        <v>1.3425350000000001E-2</v>
+      </c>
+      <c r="H12">
+        <v>0.52470000000000006</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A13" s="87" t="s">
+        <v>197</v>
+      </c>
+      <c r="B13" s="87" t="s">
+        <v>565</v>
+      </c>
+      <c r="C13" t="s">
+        <v>564</v>
+      </c>
+      <c r="D13" s="86">
+        <v>3.1223000000000001E-2</v>
+      </c>
+      <c r="E13" s="86">
+        <v>7.9596E-2</v>
+      </c>
+      <c r="F13" s="86">
+        <v>5.0365040000000005E-4</v>
+      </c>
+      <c r="G13" s="86">
+        <v>8.2356430000000008E-3</v>
+      </c>
+      <c r="H13">
+        <v>0.69499999999999995</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>558</v>
+      </c>
+      <c r="B14" t="s">
+        <v>565</v>
+      </c>
+      <c r="C14" t="s">
+        <v>560</v>
+      </c>
+      <c r="D14" s="86">
+        <v>-1.0381E-2</v>
+      </c>
+      <c r="E14" s="86">
+        <v>0.11691799999999999</v>
+      </c>
+      <c r="F14" s="86">
+        <v>1.708297E-5</v>
+      </c>
+      <c r="G14" s="86">
+        <v>9.3713600000000005E-3</v>
+      </c>
+      <c r="H14" s="86">
+        <v>0.92</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>558</v>
+      </c>
+      <c r="B15" t="s">
+        <v>565</v>
+      </c>
+      <c r="C15" t="s">
+        <v>564</v>
+      </c>
+      <c r="D15" s="86">
+        <v>-0.52913299999999996</v>
+      </c>
+      <c r="E15" s="86">
+        <v>0.23084099999999999</v>
+      </c>
+      <c r="F15" s="86">
+        <v>3.70587E-2</v>
+      </c>
+      <c r="G15" s="86">
+        <v>5.280435E-2</v>
+      </c>
+      <c r="H15" s="89">
+        <v>2.1899999999999999E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>561</v>
+      </c>
+      <c r="B16" t="s">
+        <v>565</v>
+      </c>
+      <c r="C16" t="s">
+        <v>560</v>
+      </c>
+      <c r="D16" s="86">
+        <v>0.17679</v>
+      </c>
+      <c r="E16" s="86">
+        <v>1.3722099999999999</v>
+      </c>
+      <c r="F16" s="86">
+        <v>1.475601E-5</v>
+      </c>
+      <c r="G16" s="86">
+        <v>9.7052690000000007E-3</v>
+      </c>
+      <c r="H16" s="86">
+        <v>0.89749999999999996</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>561</v>
+      </c>
+      <c r="B17" t="s">
+        <v>565</v>
+      </c>
+      <c r="C17" t="s">
+        <v>564</v>
+      </c>
+      <c r="D17" s="86">
+        <v>5.0827</v>
+      </c>
+      <c r="E17" s="86">
+        <v>2.6116999999999999</v>
+      </c>
+      <c r="F17" s="86">
+        <v>1.088867E-2</v>
+      </c>
+      <c r="G17" s="86">
+        <v>1.6727720000000001E-2</v>
+      </c>
+      <c r="H17" s="51">
+        <v>5.2499999999999998E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C19" t="s">
+        <v>567</v>
       </c>
     </row>
   </sheetData>
